--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,4806 +490,4806 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501051</t>
+          <t>0022501063</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612737</v>
+        <v>1610612752</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6021</v>
+        <v>0.5145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501052</t>
+          <t>0022501064</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612754</v>
+        <v>1610612765</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612747</v>
+        <v>1610612740</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2186</v>
+        <v>0.7344000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501053</t>
+          <t>0022501065</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612741</v>
+        <v>1610612758</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>0.572</v>
+        <v>0.7725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501054</t>
+          <t>0022501066</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4763</v>
+        <v>0.2241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501055</t>
+          <t>0022501067</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612739</v>
+        <v>1610612738</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612748</v>
+        <v>1610612737</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7083</v>
+        <v>0.6737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501056</t>
+          <t>0022501068</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612763</v>
+        <v>1610612739</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612759</v>
+        <v>1610612748</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2067</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501057</t>
+          <t>0022501069</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612762</v>
+        <v>1610612763</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6633</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501058</t>
+          <t>0022501070</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612750</v>
+        <v>1610612760</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5998</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501059</t>
+          <t>0022501071</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612743</v>
+        <v>1610612761</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8357</v>
+        <v>0.7081</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501060</t>
+          <t>0022501072</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612744</v>
+        <v>1610612743</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612751</v>
+        <v>1610612762</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8532999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501061</t>
+          <t>0022501073</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612757</v>
+        <v>1610612744</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612749</v>
+        <v>1610612764</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M12" t="n">
-        <v>0.71</v>
+        <v>0.8166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501062</t>
+          <t>0022501074</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612761</v>
+        <v>1610612742</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6332</v>
+        <v>0.7229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501063</t>
+          <t>0022501075</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612766</v>
+        <v>1610612747</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612752</v>
+        <v>1610612751</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5157</v>
+        <v>0.8458</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501064</t>
+          <t>0022501076</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612765</v>
+        <v>1610612749</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.2185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501065</t>
+          <t>0022501077</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612758</v>
+        <v>1610612755</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7715</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501066</t>
+          <t>0022501078</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612754</v>
+        <v>1610612737</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612746</v>
+        <v>1610612758</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2256</v>
+        <v>0.8280999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501067</t>
+          <t>0022501079</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612738</v>
+        <v>1610612763</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612737</v>
+        <v>1610612741</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6737</v>
+        <v>0.5175999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501068</t>
+          <t>0022501080</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612748</v>
+        <v>1610612765</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7083</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501069</t>
+          <t>0022501081</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612763</v>
+        <v>1610612756</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3213</v>
+        <v>0.7907999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501070</t>
+          <t>0022501082</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612760</v>
+        <v>1610612749</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612741</v>
+        <v>1610612746</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8225</v>
+        <v>0.2699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501071</t>
+          <t>0022501083</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612761</v>
+        <v>1610612754</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612740</v>
+        <v>1610612748</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7091</v>
+        <v>0.2632</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501072</t>
+          <t>0022501084</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.5031</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501073</t>
+          <t>0022501085</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8133</v>
+        <v>0.4871</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501074</t>
+          <t>0022501086</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612757</v>
+        <v>1610612761</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612742</v>
+        <v>1610612753</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7229</v>
+        <v>0.6322</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501075</t>
+          <t>0022501087</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612747</v>
+        <v>1610612757</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8458</v>
+        <v>0.8173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501076</t>
+          <t>0022501088</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612749</v>
+        <v>1610612740</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612759</v>
+        <v>1610612745</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2326</v>
+        <v>0.4414</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501077</t>
+          <t>0022501089</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612766</v>
+        <v>1610612760</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612755</v>
+        <v>1610612752</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.6916</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501078</t>
+          <t>0022501090</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612737</v>
+        <v>1610612743</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612758</v>
+        <v>1610612744</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8265</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501079</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612763</v>
+        <v>1610612748</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612741</v>
+        <v>1610612755</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4814</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501080</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5184</v>
+        <v>0.4825</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501081</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="C32" t="n">
+        <v>1610612763</v>
+      </c>
+      <c r="D32" t="n">
         <v>1610612756</v>
       </c>
-      <c r="D32" t="n">
-        <v>1610612762</v>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Grizzlies</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Suns</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>PHX</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.3604</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501082</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612749</v>
+        <v>1610612759</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612746</v>
+        <v>1610612741</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2812</v>
+        <v>0.8061</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501083</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612754</v>
+        <v>1610612742</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2641</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501084</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612751</v>
+        <v>1610612762</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612758</v>
+        <v>1610612739</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5016</v>
+        <v>0.2085</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501085</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612766</v>
+        <v>1610612760</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4882</v>
+        <v>0.7413</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501086</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6412</v>
+        <v>0.8673</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501087</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612757</v>
+        <v>1610612749</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612764</v>
+        <v>1610612742</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8154</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501088</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612745</v>
+        <v>1610612756</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4414</v>
+        <v>0.5645</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501089</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612760</v>
+        <v>1610612751</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612752</v>
+        <v>1610612766</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6899</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612743</v>
+        <v>1610612765</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612744</v>
+        <v>1610612761</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7571</v>
+        <v>0.6724</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612748</v>
+        <v>1610612745</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612755</v>
+        <v>1610612752</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6987</v>
+        <v>0.4339</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4825</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612763</v>
+        <v>1610612746</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612756</v>
+        <v>1610612757</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3609</v>
+        <v>0.6891</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612759</v>
+        <v>1610612763</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612741</v>
+        <v>1610612752</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M45" t="n">
-        <v>0.792</v>
+        <v>0.2151</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612742</v>
+        <v>1610612764</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612750</v>
+        <v>1610612755</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M46" t="n">
-        <v>0.289</v>
+        <v>0.2675</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612762</v>
+        <v>1610612748</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612739</v>
+        <v>1610612738</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2085</v>
+        <v>0.4168</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612760</v>
+        <v>1610612753</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612765</v>
+        <v>1610612737</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7413</v>
+        <v>0.4253</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612764</v>
+        <v>1610612758</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8673</v>
+        <v>0.7984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5857</v>
+        <v>0.7036</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612753</v>
+        <v>1610612745</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612756</v>
+        <v>1610612749</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5645</v>
+        <v>0.8062</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612751</v>
+        <v>1610612762</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612766</v>
+        <v>1610612743</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1918</v>
+        <v>0.2114</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612765</v>
+        <v>1610612744</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6647</v>
+        <v>0.3248</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612752</v>
+        <v>1610612756</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4339</v>
+        <v>0.6651</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5663</v>
+        <v>0.6392</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612746</v>
+        <v>1610612760</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612757</v>
+        <v>1610612747</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M56" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6963</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612763</v>
+        <v>1610612744</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2153</v>
+        <v>0.3257</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612764</v>
+        <v>1610612757</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612755</v>
+        <v>1610612740</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3192</v>
+        <v>0.6392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612748</v>
+        <v>1610612746</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612738</v>
+        <v>1610612759</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4168</v>
+        <v>0.4916</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612737</v>
+        <v>1610612754</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4253</v>
+        <v>0.8307</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612758</v>
+        <v>1610612750</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8072</v>
+        <v>0.4658</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612741</v>
+        <v>1610612751</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612754</v>
+        <v>1610612737</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M62" t="n">
-        <v>0.714</v>
+        <v>0.2062</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612745</v>
+        <v>1610612752</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M63" t="n">
-        <v>0.784</v>
+        <v>0.8192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C64" t="n">
+        <v>1610612745</v>
+      </c>
+      <c r="D64" t="n">
         <v>1610612762</v>
       </c>
-      <c r="D64" t="n">
-        <v>1610612743</v>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Rockets</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Jazz</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>UTA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M64" t="n">
-        <v>0.2114</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612744</v>
+        <v>1610612763</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3248</v>
+        <v>0.3276</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612756</v>
+        <v>1610612738</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M66" t="n">
-        <v>0.6651</v>
+        <v>0.2214</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612765</v>
+        <v>1610612742</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612750</v>
+        <v>1610612753</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M67" t="n">
-        <v>0.6335</v>
+        <v>0.4124</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612760</v>
+        <v>1610612758</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612747</v>
+        <v>1610612740</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M68" t="n">
-        <v>0.6932</v>
+        <v>0.4144</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612744</v>
+        <v>1610612748</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612739</v>
+        <v>1610612764</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M69" t="n">
-        <v>0.325</v>
+        <v>0.8396</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612757</v>
+        <v>1610612743</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6392</v>
+        <v>0.5147</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612746</v>
+        <v>1610612755</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612759</v>
+        <v>1610612765</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4916</v>
+        <v>0.4013</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612766</v>
+        <v>1610612738</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612754</v>
+        <v>1610612761</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M72" t="n">
-        <v>0.828</v>
+        <v>0.7356</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612755</v>
+        <v>1610612751</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612750</v>
+        <v>1610612764</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M73" t="n">
-        <v>0.4033</v>
+        <v>0.6002</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612737</v>
+        <v>1610612756</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M74" t="n">
-        <v>0.2062</v>
+        <v>0.4755</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612752</v>
+        <v>1610612749</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612741</v>
+        <v>1610612763</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M75" t="n">
-        <v>0.8032</v>
+        <v>0.5677</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612762</v>
+        <v>1610612754</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8073</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612763</v>
+        <v>1610612750</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M77" t="n">
-        <v>0.3163</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612749</v>
+        <v>1610612740</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612738</v>
+        <v>1610612753</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M78" t="n">
-        <v>0.2328</v>
+        <v>0.5413</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612742</v>
+        <v>1610612760</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612753</v>
+        <v>1610612762</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M79" t="n">
-        <v>0.4164</v>
+        <v>0.8532</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612758</v>
+        <v>1610612742</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612740</v>
+        <v>1610612747</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M80" t="n">
-        <v>0.4144</v>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612748</v>
+        <v>1610612758</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612764</v>
+        <v>1610612746</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8396</v>
+        <v>0.2386</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612743</v>
+        <v>1610612744</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612759</v>
+        <v>1610612745</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5324</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612755</v>
+        <v>1610612737</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612765</v>
+        <v>1610612752</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M83" t="n">
-        <v>0.3783</v>
+        <v>0.4881</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612738</v>
+        <v>1610612753</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612761</v>
+        <v>1610612765</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K84" t="n">
         <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M84" t="n">
-        <v>0.7265</v>
+        <v>0.4502</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612764</v>
+        <v>1610612739</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K85" t="n">
         <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M85" t="n">
-        <v>0.6002</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612741</v>
+        <v>1610612759</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612756</v>
+        <v>1610612755</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5007</v>
+        <v>0.8018999999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612763</v>
+        <v>1610612757</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M87" t="n">
-        <v>0.602</v>
+        <v>0.7406</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612739</v>
+        <v>1610612764</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K88" t="n">
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M88" t="n">
-        <v>0.852</v>
+        <v>0.3275</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612750</v>
+        <v>1610612738</v>
       </c>
       <c r="D89" t="n">
         <v>1610612766</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5309,258 +5309,258 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.6444</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612740</v>
+        <v>1610612751</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612753</v>
+        <v>1610612749</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M90" t="n">
-        <v>0.5413</v>
+        <v>0.4561</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612760</v>
+        <v>1610612761</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612762</v>
+        <v>1610612748</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K91" t="n">
         <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8532</v>
+        <v>0.5572</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612747</v>
+        <v>1610612750</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M92" t="n">
-        <v>0.2321</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612758</v>
+        <v>1610612740</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612746</v>
+        <v>1610612762</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K93" t="n">
         <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M93" t="n">
-        <v>0.2386</v>
+        <v>0.7218</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C94" t="n">
         <v>1610612744</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612745</v>
+        <v>1610612758</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5596,1595 +5596,1595 @@
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M94" t="n">
-        <v>0.479</v>
+        <v>0.7557</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612752</v>
+        <v>1610612760</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4881</v>
+        <v>0.4508</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612753</v>
+        <v>1610612746</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612765</v>
+        <v>1610612742</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M96" t="n">
-        <v>0.4502</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612763</v>
+        <v>1610612756</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612739</v>
+        <v>1610612745</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M97" t="n">
-        <v>0.215</v>
+        <v>0.5347</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612759</v>
+        <v>1610612739</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612755</v>
+        <v>1610612737</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K98" t="n">
         <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M98" t="n">
-        <v>0.8092</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612743</v>
+        <v>1610612753</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612757</v>
+        <v>1610612750</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K99" t="n">
         <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M99" t="n">
-        <v>0.7622</v>
+        <v>0.5006</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612764</v>
+        <v>1610612765</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612741</v>
+        <v>1610612749</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K100" t="n">
         <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M100" t="n">
-        <v>0.3021</v>
+        <v>0.8023</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612738</v>
+        <v>1610612759</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612766</v>
+        <v>1610612757</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M101" t="n">
-        <v>0.6444</v>
+        <v>0.7702</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612751</v>
+        <v>1610612743</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K102" t="n">
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M102" t="n">
-        <v>0.4097</v>
+        <v>0.8352000000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612761</v>
+        <v>1610612746</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612748</v>
+        <v>1610612760</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K103" t="n">
         <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M103" t="n">
-        <v>0.5715</v>
+        <v>0.4175</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612754</v>
+        <v>1610612756</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612750</v>
+        <v>1610612742</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M104" t="n">
-        <v>0.2598</v>
+        <v>0.7741</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612740</v>
+        <v>1610612761</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612762</v>
+        <v>1610612748</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K105" t="n">
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M105" t="n">
-        <v>0.7218</v>
+        <v>0.5572</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612758</v>
+        <v>1610612741</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K106" t="n">
         <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M106" t="n">
-        <v>0.7557</v>
+        <v>0.3275</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612747</v>
+        <v>1610612751</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612760</v>
+        <v>1610612754</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K107" t="n">
         <v>1</v>
       </c>
       <c r="L107" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M107" t="n">
-        <v>0.455</v>
+        <v>0.5185999999999999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612746</v>
+        <v>1610612752</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612742</v>
+        <v>1610612738</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K108" t="n">
         <v>1</v>
       </c>
       <c r="L108" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M108" t="n">
-        <v>0.8149</v>
+        <v>0.5709</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612756</v>
+        <v>1610612745</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612745</v>
+        <v>1610612755</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K109" t="n">
         <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M109" t="n">
-        <v>0.5354</v>
+        <v>0.6825</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612739</v>
+        <v>1610612744</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K110" t="n">
         <v>1</v>
       </c>
       <c r="L110" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M110" t="n">
-        <v>0.663</v>
+        <v>0.3303</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612750</v>
+        <v>1610612765</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K111" t="n">
         <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M111" t="n">
-        <v>0.4737</v>
+        <v>0.5533</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K112" t="n">
         <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M112" t="n">
-        <v>0.7886</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C113" t="n">
-        <v>1610612759</v>
+        <v>1610612737</v>
       </c>
       <c r="D113" t="n">
-        <v>1610612757</v>
+        <v>1610612739</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K113" t="n">
         <v>1</v>
       </c>
       <c r="L113" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M113" t="n">
-        <v>0.7692</v>
+        <v>0.5008</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C114" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="D114" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K114" t="n">
         <v>1</v>
       </c>
       <c r="L114" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M114" t="n">
-        <v>0.8431</v>
+        <v>0.7933</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C115" t="n">
-        <v>1610612746</v>
+        <v>1610612754</v>
       </c>
       <c r="D115" t="n">
-        <v>1610612760</v>
+        <v>1610612755</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K115" t="n">
         <v>1</v>
       </c>
       <c r="L115" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M115" t="n">
-        <v>0.4175</v>
+        <v>0.3819</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C116" t="n">
-        <v>1610612756</v>
+        <v>1610612752</v>
       </c>
       <c r="D116" t="n">
-        <v>1610612742</v>
+        <v>1610612761</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K116" t="n">
         <v>1</v>
       </c>
       <c r="L116" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M116" t="n">
-        <v>0.7741</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C117" t="n">
-        <v>1610612761</v>
+        <v>1610612741</v>
       </c>
       <c r="D117" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K117" t="n">
         <v>1</v>
       </c>
       <c r="L117" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M117" t="n">
-        <v>0.5715</v>
+        <v>0.5175</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C118" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="D118" t="n">
-        <v>1610612741</v>
+        <v>1610612750</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K118" t="n">
         <v>1</v>
       </c>
       <c r="L118" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M118" t="n">
-        <v>0.3021</v>
+        <v>0.5717</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C119" t="n">
+        <v>1610612749</v>
+      </c>
+      <c r="D119" t="n">
         <v>1610612751</v>
       </c>
-      <c r="D119" t="n">
-        <v>1610612754</v>
-      </c>
       <c r="E119" t="inlineStr">
         <is>
+          <t>Bucks</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>Nets</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Pacers</t>
-        </is>
-      </c>
       <c r="G119" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
           <t>BKN</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K119" t="n">
         <v>1</v>
       </c>
       <c r="L119" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M119" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.6821</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C120" t="n">
-        <v>1610612752</v>
+        <v>1610612759</v>
       </c>
       <c r="D120" t="n">
-        <v>1610612738</v>
+        <v>1610612742</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K120" t="n">
         <v>1</v>
       </c>
       <c r="L120" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M120" t="n">
-        <v>0.5709</v>
+        <v>0.8357</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C121" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="D121" t="n">
-        <v>1610612755</v>
+        <v>1610612763</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K121" t="n">
         <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M121" t="n">
-        <v>0.7034</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C122" t="n">
-        <v>1610612744</v>
+        <v>1610612743</v>
       </c>
       <c r="D122" t="n">
-        <v>1610612747</v>
+        <v>1610612760</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K122" t="n">
         <v>1</v>
       </c>
       <c r="L122" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M122" t="n">
-        <v>0.3244</v>
+        <v>0.4659</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C123" t="n">
-        <v>1610612766</v>
+        <v>1610612757</v>
       </c>
       <c r="D123" t="n">
-        <v>1610612765</v>
+        <v>1610612746</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -7194,52 +7194,52 @@
         <v>171</v>
       </c>
       <c r="M123" t="n">
-        <v>0.5524</v>
+        <v>0.4378</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B124" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C124" t="n">
-        <v>1610612764</v>
+        <v>1610612758</v>
       </c>
       <c r="D124" t="n">
-        <v>1610612748</v>
+        <v>1610612744</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -7249,52 +7249,52 @@
         <v>171</v>
       </c>
       <c r="M124" t="n">
-        <v>0.224</v>
+        <v>0.3602</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B125" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C125" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="D125" t="n">
-        <v>1610612739</v>
+        <v>1610612756</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -7304,23 +7304,23 @@
         <v>171</v>
       </c>
       <c r="M125" t="n">
-        <v>0.5008</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C126" t="n">
         <v>1610612738</v>
       </c>
       <c r="D126" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7356,660 +7356,660 @@
         <v>1</v>
       </c>
       <c r="L126" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M126" t="n">
-        <v>0.7933</v>
+        <v>0.7868000000000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C127" t="n">
-        <v>1610612754</v>
+        <v>1610612739</v>
       </c>
       <c r="D127" t="n">
-        <v>1610612755</v>
+        <v>1610612764</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K127" t="n">
         <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M127" t="n">
-        <v>0.436</v>
+        <v>0.8592</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C128" t="n">
-        <v>1610612752</v>
+        <v>1610612754</v>
       </c>
       <c r="D128" t="n">
-        <v>1610612761</v>
+        <v>1610612765</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K128" t="n">
         <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M128" t="n">
-        <v>0.726</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C129" t="n">
-        <v>1610612741</v>
+        <v>1610612748</v>
       </c>
       <c r="D129" t="n">
-        <v>1610612753</v>
+        <v>1610612737</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K129" t="n">
         <v>1</v>
       </c>
       <c r="L129" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M129" t="n">
-        <v>0.5371</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C130" t="n">
-        <v>1610612745</v>
+        <v>1610612752</v>
       </c>
       <c r="D130" t="n">
-        <v>1610612750</v>
+        <v>1610612766</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K130" t="n">
         <v>1</v>
       </c>
       <c r="L130" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M130" t="n">
-        <v>0.5534</v>
+        <v>0.6504</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C131" t="n">
+        <v>1610612755</v>
+      </c>
+      <c r="D131" t="n">
         <v>1610612749</v>
       </c>
-      <c r="D131" t="n">
-        <v>1610612751</v>
-      </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>76ers</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>Bucks</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Nets</t>
-        </is>
-      </c>
       <c r="G131" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K131" t="n">
         <v>1</v>
       </c>
       <c r="L131" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M131" t="n">
-        <v>0.706</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C132" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="D132" t="n">
-        <v>1610612742</v>
+        <v>1610612751</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K132" t="n">
         <v>1</v>
       </c>
       <c r="L132" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M132" t="n">
-        <v>0.8314</v>
+        <v>0.8305</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C133" t="n">
-        <v>1610612762</v>
+        <v>1610612742</v>
       </c>
       <c r="D133" t="n">
-        <v>1610612763</v>
+        <v>1610612741</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K133" t="n">
         <v>1</v>
       </c>
       <c r="L133" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M133" t="n">
-        <v>0.528</v>
+        <v>0.4974</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C134" t="n">
-        <v>1610612743</v>
+        <v>1610612745</v>
       </c>
       <c r="D134" t="n">
-        <v>1610612760</v>
+        <v>1610612763</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K134" t="n">
         <v>1</v>
       </c>
       <c r="L134" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M134" t="n">
-        <v>0.491</v>
+        <v>0.7944</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C135" t="n">
-        <v>1610612757</v>
+        <v>1610612750</v>
       </c>
       <c r="D135" t="n">
-        <v>1610612746</v>
+        <v>1610612740</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K135" t="n">
         <v>1</v>
       </c>
       <c r="L135" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M135" t="n">
-        <v>0.4378</v>
+        <v>0.7122000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C136" t="n">
-        <v>1610612758</v>
+        <v>1610612760</v>
       </c>
       <c r="D136" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K136" t="n">
         <v>1</v>
       </c>
       <c r="L136" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M136" t="n">
-        <v>0.3619</v>
+        <v>0.8008999999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C137" t="n">
-        <v>1610612747</v>
+        <v>1610612759</v>
       </c>
       <c r="D137" t="n">
-        <v>1610612756</v>
+        <v>1610612743</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K137" t="n">
         <v>1</v>
       </c>
       <c r="L137" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M137" t="n">
-        <v>0.6807</v>
+        <v>0.6395999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B138" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C138" t="n">
-        <v>1610612738</v>
+        <v>1610612747</v>
       </c>
       <c r="D138" t="n">
-        <v>1610612753</v>
+        <v>1610612762</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -8019,52 +8019,52 @@
         <v>173</v>
       </c>
       <c r="M138" t="n">
-        <v>0.7857</v>
+        <v>0.8488</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B139" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C139" t="n">
-        <v>1610612739</v>
+        <v>1610612746</v>
       </c>
       <c r="D139" t="n">
-        <v>1610612764</v>
+        <v>1610612744</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -8074,52 +8074,52 @@
         <v>173</v>
       </c>
       <c r="M139" t="n">
-        <v>0.8592</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B140" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C140" t="n">
-        <v>1610612754</v>
+        <v>1610612757</v>
       </c>
       <c r="D140" t="n">
-        <v>1610612765</v>
+        <v>1610612758</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -8129,666 +8129,6 @@
         <v>173</v>
       </c>
       <c r="M140" t="n">
-        <v>0.263</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>0022501189</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C141" t="n">
-        <v>1610612748</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1610612737</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Hawks</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Kaseya Center</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="K141" t="n">
-        <v>1</v>
-      </c>
-      <c r="L141" t="n">
-        <v>173</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0.515</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>0022501190</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C142" t="n">
-        <v>1610612752</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1610612766</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Knicks</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Hornets</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Madison Square Garden</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="K142" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" t="n">
-        <v>173</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0.6504</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>0022501191</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C143" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1610612749</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Bucks</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Xfinity Mobile Arena</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="K143" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" t="n">
-        <v>173</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0.6636</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>0022501192</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C144" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1610612751</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Nets</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Scotiabank Arena</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="K144" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" t="n">
-        <v>173</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0.8305</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>0022501193</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C145" t="n">
-        <v>1610612742</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1610612741</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Mavericks</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Bulls</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>CHI</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>American Airlines Center</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="K145" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" t="n">
-        <v>173</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0.4654</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>0022501194</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C146" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1610612763</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Grizzlies</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Toyota Center</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="K146" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" t="n">
-        <v>173</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0.7944</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>0022501195</t>
-        </is>
-      </c>
-      <c r="B147" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C147" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1610612740</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Pelicans</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Target Center</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="K147" t="n">
-        <v>1</v>
-      </c>
-      <c r="L147" t="n">
-        <v>173</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0.7374000000000001</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B148" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C148" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K148" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" t="n">
-        <v>173</v>
-      </c>
-      <c r="M148" t="n">
-        <v>0.8008999999999999</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B149" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C149" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K149" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" t="n">
-        <v>173</v>
-      </c>
-      <c r="M149" t="n">
-        <v>0.6142</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B150" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C150" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K150" t="n">
-        <v>1</v>
-      </c>
-      <c r="L150" t="n">
-        <v>173</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0.8488</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B151" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C151" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K151" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" t="n">
-        <v>173</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0.6931</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C152" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K152" t="n">
-        <v>1</v>
-      </c>
-      <c r="L152" t="n">
-        <v>173</v>
-      </c>
-      <c r="M152" t="n">
         <v>0.777</v>
       </c>
     </row>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M140"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,211 +490,211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501063</t>
+          <t>0022501066</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612766</v>
+        <v>1610612754</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612752</v>
+        <v>1610612746</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5145</v>
+        <v>0.2216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501064</t>
+          <t>0022501067</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612740</v>
+        <v>1610612737</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.6751</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501065</t>
+          <t>0022501068</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612753</v>
+        <v>1610612739</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612758</v>
+        <v>1610612748</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7725</v>
+        <v>0.6971000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501066</t>
+          <t>0022501069</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612754</v>
+        <v>1610612763</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -704,52 +704,52 @@
         <v>157</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2241</v>
+        <v>0.3236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501067</t>
+          <t>0022501070</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612738</v>
+        <v>1610612760</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612737</v>
+        <v>1610612741</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -759,52 +759,52 @@
         <v>157</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6737</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501068</t>
+          <t>0022501071</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612748</v>
+        <v>1610612740</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -814,52 +814,52 @@
         <v>157</v>
       </c>
       <c r="M7" t="n">
-        <v>0.71</v>
+        <v>0.7418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501069</t>
+          <t>0022501072</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612763</v>
+        <v>1610612743</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -869,52 +869,52 @@
         <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>0.32</v>
+        <v>0.8515</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501070</t>
+          <t>0022501073</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612741</v>
+        <v>1610612764</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -924,52 +924,52 @@
         <v>157</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501071</t>
+          <t>0022501074</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612761</v>
+        <v>1610612757</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -979,52 +979,52 @@
         <v>157</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7587</v>
+        <v>0.7256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501072</t>
+          <t>0022501075</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612762</v>
+        <v>1610612751</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1034,217 +1034,217 @@
         <v>157</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8512</v>
+        <v>0.8452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501073</t>
+          <t>0022501076</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612744</v>
+        <v>1610612749</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612764</v>
+        <v>1610612759</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8166</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501074</t>
+          <t>0022501077</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612757</v>
+        <v>1610612766</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612742</v>
+        <v>1610612755</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7229</v>
+        <v>0.7274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501075</t>
+          <t>0022501078</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612747</v>
+        <v>1610612737</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612751</v>
+        <v>1610612758</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8458</v>
+        <v>0.7974</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501076</t>
+          <t>0022501079</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612759</v>
+        <v>1610612741</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1254,52 +1254,52 @@
         <v>158</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2185</v>
+        <v>0.4985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501077</t>
+          <t>0022501080</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612755</v>
+        <v>1610612765</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1309,52 +1309,52 @@
         <v>158</v>
       </c>
       <c r="M16" t="n">
-        <v>0.733</v>
+        <v>0.4937</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501078</t>
+          <t>0022501081</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612737</v>
+        <v>1610612756</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1364,217 +1364,217 @@
         <v>158</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8031</v>
+        <v>0.8374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501079</t>
+          <t>0022501082</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612741</v>
+        <v>1610612746</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5131</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501080</t>
+          <t>0022501083</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612750</v>
+        <v>1610612754</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612765</v>
+        <v>1610612748</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5205</v>
+        <v>0.2745</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501081</t>
+          <t>0022501084</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612756</v>
+        <v>1610612751</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8341</v>
+        <v>0.5437</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501082</t>
+          <t>0022501085</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612749</v>
+        <v>1610612766</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612746</v>
+        <v>1610612738</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1584,52 +1584,52 @@
         <v>159</v>
       </c>
       <c r="M21" t="n">
-        <v>0.241</v>
+        <v>0.4525</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501083</t>
+          <t>0022501086</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612754</v>
+        <v>1610612761</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1639,52 +1639,52 @@
         <v>159</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2632</v>
+        <v>0.6325</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501084</t>
+          <t>0022501087</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612751</v>
+        <v>1610612757</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612758</v>
+        <v>1610612764</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1694,52 +1694,52 @@
         <v>159</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5588</v>
+        <v>0.8018</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501085</t>
+          <t>0022501088</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612766</v>
+        <v>1610612740</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612738</v>
+        <v>1610612745</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1749,52 +1749,52 @@
         <v>159</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4456</v>
+        <v>0.4282</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501086</t>
+          <t>0022501089</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612761</v>
+        <v>1610612760</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612753</v>
+        <v>1610612752</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1804,52 +1804,52 @@
         <v>159</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6393</v>
+        <v>0.6911</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501087</t>
+          <t>0022501090</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612757</v>
+        <v>1610612743</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612764</v>
+        <v>1610612744</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1859,217 +1859,217 @@
         <v>159</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8173</v>
+        <v>0.7558</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501088</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612740</v>
+        <v>1610612748</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612745</v>
+        <v>1610612755</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4414</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501089</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612760</v>
+        <v>1610612737</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6916</v>
+        <v>0.5516</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612743</v>
+        <v>1610612763</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M29" t="n">
-        <v>0.743</v>
+        <v>0.3552</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612748</v>
+        <v>1610612759</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612755</v>
+        <v>1610612741</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,52 +2079,52 @@
         <v>160</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6135</v>
+        <v>0.8257</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612737</v>
+        <v>1610612742</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612738</v>
+        <v>1610612750</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2134,52 +2134,52 @@
         <v>160</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5443</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612763</v>
+        <v>1610612762</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612756</v>
+        <v>1610612739</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2189,52 +2189,52 @@
         <v>160</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3604</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612759</v>
+        <v>1610612760</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2244,52 +2244,52 @@
         <v>160</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8061</v>
+        <v>0.6747</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612742</v>
+        <v>1610612747</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612750</v>
+        <v>1610612764</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2299,217 +2299,217 @@
         <v>160</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2752</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612762</v>
+        <v>1610612749</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612739</v>
+        <v>1610612742</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2085</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612760</v>
+        <v>1610612753</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612765</v>
+        <v>1610612756</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6985</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612747</v>
+        <v>1610612751</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8948</v>
+        <v>0.1922</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612749</v>
+        <v>1610612765</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612742</v>
+        <v>1610612761</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2519,52 +2519,52 @@
         <v>161</v>
       </c>
       <c r="M38" t="n">
-        <v>0.622</v>
+        <v>0.6397</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612753</v>
+        <v>1610612745</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612756</v>
+        <v>1610612752</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2574,52 +2574,52 @@
         <v>161</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6193</v>
+        <v>0.4391</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612751</v>
+        <v>1610612747</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612766</v>
+        <v>1610612739</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2629,52 +2629,52 @@
         <v>161</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1899</v>
+        <v>0.5683</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612765</v>
+        <v>1610612746</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612761</v>
+        <v>1610612757</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2684,27 +2684,27 @@
         <v>161</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.7047</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612745</v>
+        <v>1610612763</v>
       </c>
       <c r="D42" t="n">
         <v>1610612752</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2724,177 +2724,177 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4339</v>
+        <v>0.2547</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612747</v>
+        <v>1610612764</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612739</v>
+        <v>1610612755</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5655</v>
+        <v>0.3107</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612757</v>
+        <v>1610612738</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6891</v>
+        <v>0.4294</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612763</v>
+        <v>1610612753</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612752</v>
+        <v>1610612737</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2904,52 +2904,52 @@
         <v>162</v>
       </c>
       <c r="M45" t="n">
-        <v>0.253</v>
+        <v>0.4031</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612764</v>
+        <v>1610612761</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612755</v>
+        <v>1610612758</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2959,52 +2959,52 @@
         <v>162</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2675</v>
+        <v>0.7588</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3014,52 +3014,52 @@
         <v>162</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4168</v>
+        <v>0.6859</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612753</v>
+        <v>1610612745</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612737</v>
+        <v>1610612749</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3069,52 +3069,52 @@
         <v>162</v>
       </c>
       <c r="M48" t="n">
-        <v>0.384</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612761</v>
+        <v>1610612762</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612758</v>
+        <v>1610612743</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3124,52 +3124,52 @@
         <v>162</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7723</v>
+        <v>0.2053</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612741</v>
+        <v>1610612744</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612754</v>
+        <v>1610612759</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3179,217 +3179,217 @@
         <v>162</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7058</v>
+        <v>0.2824</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612749</v>
+        <v>1610612756</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8275</v>
+        <v>0.6639</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612762</v>
+        <v>1610612765</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612743</v>
+        <v>1610612750</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2114</v>
+        <v>0.6318</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612744</v>
+        <v>1610612760</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3248</v>
+        <v>0.6899</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612766</v>
+        <v>1610612744</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612756</v>
+        <v>1610612739</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3399,52 +3399,52 @@
         <v>163</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6651</v>
+        <v>0.3055</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612765</v>
+        <v>1610612757</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612750</v>
+        <v>1610612740</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3454,52 +3454,52 @@
         <v>163</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6335</v>
+        <v>0.6613</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612747</v>
+        <v>1610612759</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3509,217 +3509,217 @@
         <v>163</v>
       </c>
       <c r="M56" t="n">
-        <v>0.6963</v>
+        <v>0.5339</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612739</v>
+        <v>1610612754</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2965</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612757</v>
+        <v>1610612755</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612740</v>
+        <v>1610612750</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6392</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612746</v>
+        <v>1610612751</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612759</v>
+        <v>1610612737</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M59" t="n">
-        <v>0.5495</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3729,52 +3729,52 @@
         <v>164</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8056</v>
+        <v>0.8153</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612755</v>
+        <v>1610612745</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612750</v>
+        <v>1610612762</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3784,52 +3784,52 @@
         <v>164</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>164</v>
       </c>
       <c r="M62" t="n">
-        <v>0.2062</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612752</v>
+        <v>1610612749</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612741</v>
+        <v>1610612738</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,52 +3894,52 @@
         <v>164</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.2246</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612745</v>
+        <v>1610612742</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612762</v>
+        <v>1610612753</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3949,52 +3949,52 @@
         <v>164</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8055</v>
+        <v>0.3984</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612763</v>
+        <v>1610612758</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612761</v>
+        <v>1610612740</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4004,382 +4004,382 @@
         <v>164</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3276</v>
+        <v>0.4772</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612738</v>
+        <v>1610612764</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M66" t="n">
-        <v>0.2214</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612742</v>
+        <v>1610612743</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612753</v>
+        <v>1610612759</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4124</v>
+        <v>0.5062</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612758</v>
+        <v>1610612755</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612740</v>
+        <v>1610612765</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4664</v>
+        <v>0.3607</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612748</v>
+        <v>1610612738</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612764</v>
+        <v>1610612761</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8419</v>
+        <v>0.7511</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612759</v>
+        <v>1610612764</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5147</v>
+        <v>0.6267</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612755</v>
+        <v>1610612741</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612765</v>
+        <v>1610612756</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M71" t="n">
-        <v>0.3588</v>
+        <v>0.4511</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612738</v>
+        <v>1610612749</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612761</v>
+        <v>1610612763</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4389,52 +4389,52 @@
         <v>166</v>
       </c>
       <c r="M72" t="n">
-        <v>0.7356</v>
+        <v>0.5985</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612751</v>
+        <v>1610612739</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612764</v>
+        <v>1610612754</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4444,52 +4444,52 @@
         <v>166</v>
       </c>
       <c r="M73" t="n">
-        <v>0.6567</v>
+        <v>0.8512</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612741</v>
+        <v>1610612750</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4499,52 +4499,52 @@
         <v>166</v>
       </c>
       <c r="M74" t="n">
-        <v>0.4784</v>
+        <v>0.5469000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612749</v>
+        <v>1610612740</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612763</v>
+        <v>1610612753</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>166</v>
       </c>
       <c r="M75" t="n">
-        <v>0.5677</v>
+        <v>0.5364</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612739</v>
+        <v>1610612760</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,52 +4609,52 @@
         <v>166</v>
       </c>
       <c r="M76" t="n">
-        <v>0.852</v>
+        <v>0.8518</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612750</v>
+        <v>1610612742</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612766</v>
+        <v>1610612747</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4664,52 +4664,52 @@
         <v>166</v>
       </c>
       <c r="M77" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612740</v>
+        <v>1610612758</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612753</v>
+        <v>1610612746</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,52 +4719,52 @@
         <v>166</v>
       </c>
       <c r="M78" t="n">
-        <v>0.5413</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612762</v>
+        <v>1610612745</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4774,217 +4774,217 @@
         <v>166</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8532</v>
+        <v>0.4814</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612742</v>
+        <v>1610612737</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612747</v>
+        <v>1610612752</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M80" t="n">
-        <v>0.2321</v>
+        <v>0.4931</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612758</v>
+        <v>1610612753</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612746</v>
+        <v>1610612765</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M81" t="n">
-        <v>0.2386</v>
+        <v>0.3834</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612744</v>
+        <v>1610612763</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M82" t="n">
-        <v>0.479</v>
+        <v>0.2311</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612737</v>
+        <v>1610612759</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4994,52 +4994,52 @@
         <v>167</v>
       </c>
       <c r="M83" t="n">
-        <v>0.4881</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612753</v>
+        <v>1610612743</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612765</v>
+        <v>1610612757</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5049,217 +5049,217 @@
         <v>167</v>
       </c>
       <c r="M84" t="n">
-        <v>0.3998</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612763</v>
+        <v>1610612764</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612739</v>
+        <v>1610612741</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K85" t="n">
         <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2294</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612759</v>
+        <v>1610612738</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612755</v>
+        <v>1610612766</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.6474</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612757</v>
+        <v>1610612749</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M87" t="n">
-        <v>0.7406</v>
+        <v>0.4043</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612764</v>
+        <v>1610612761</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612741</v>
+        <v>1610612748</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -5269,52 +5269,52 @@
         <v>168</v>
       </c>
       <c r="M88" t="n">
-        <v>0.3179</v>
+        <v>0.5512</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -5324,52 +5324,52 @@
         <v>168</v>
       </c>
       <c r="M89" t="n">
-        <v>0.6444</v>
+        <v>0.257</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612751</v>
+        <v>1610612740</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612749</v>
+        <v>1610612762</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5379,52 +5379,52 @@
         <v>168</v>
       </c>
       <c r="M90" t="n">
-        <v>0.4561</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612761</v>
+        <v>1610612744</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612748</v>
+        <v>1610612758</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5434,52 +5434,52 @@
         <v>168</v>
       </c>
       <c r="M91" t="n">
-        <v>0.5572</v>
+        <v>0.7455000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612750</v>
+        <v>1610612760</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5489,52 +5489,52 @@
         <v>168</v>
       </c>
       <c r="M92" t="n">
-        <v>0.2581</v>
+        <v>0.4678</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612740</v>
+        <v>1610612746</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612762</v>
+        <v>1610612742</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5544,52 +5544,52 @@
         <v>168</v>
       </c>
       <c r="M93" t="n">
-        <v>0.7197</v>
+        <v>0.8241000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612758</v>
+        <v>1610612745</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5599,217 +5599,217 @@
         <v>168</v>
       </c>
       <c r="M94" t="n">
-        <v>0.7557</v>
+        <v>0.5438</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612760</v>
+        <v>1610612737</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4508</v>
+        <v>0.6752</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612746</v>
+        <v>1610612753</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612742</v>
+        <v>1610612750</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M96" t="n">
-        <v>0.8167</v>
+        <v>0.5364</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612756</v>
+        <v>1610612765</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M97" t="n">
-        <v>0.5347</v>
+        <v>0.8421</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612739</v>
+        <v>1610612759</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612737</v>
+        <v>1610612757</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5819,52 +5819,52 @@
         <v>169</v>
       </c>
       <c r="M98" t="n">
-        <v>0.663</v>
+        <v>0.7891</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612753</v>
+        <v>1610612743</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612750</v>
+        <v>1610612763</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5874,52 +5874,52 @@
         <v>169</v>
       </c>
       <c r="M99" t="n">
-        <v>0.5333</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612765</v>
+        <v>1610612746</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612749</v>
+        <v>1610612760</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -5929,52 +5929,52 @@
         <v>169</v>
       </c>
       <c r="M100" t="n">
-        <v>0.8464</v>
+        <v>0.4502</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612759</v>
+        <v>1610612756</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612757</v>
+        <v>1610612742</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5984,217 +5984,217 @@
         <v>169</v>
       </c>
       <c r="M101" t="n">
-        <v>0.7702</v>
+        <v>0.8028</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612743</v>
+        <v>1610612761</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612763</v>
+        <v>1610612748</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K102" t="n">
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M102" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.5512</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612746</v>
+        <v>1610612764</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612760</v>
+        <v>1610612741</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K103" t="n">
         <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M103" t="n">
-        <v>0.414</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612756</v>
+        <v>1610612751</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M104" t="n">
-        <v>0.7982</v>
+        <v>0.4893</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612761</v>
+        <v>1610612752</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612748</v>
+        <v>1610612738</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -6204,52 +6204,52 @@
         <v>170</v>
       </c>
       <c r="M105" t="n">
-        <v>0.5572</v>
+        <v>0.5823</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612741</v>
+        <v>1610612755</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -6259,52 +6259,52 @@
         <v>170</v>
       </c>
       <c r="M106" t="n">
-        <v>0.3179</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612751</v>
+        <v>1610612744</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -6314,217 +6314,217 @@
         <v>170</v>
       </c>
       <c r="M107" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612752</v>
+        <v>1610612766</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K108" t="n">
         <v>1</v>
       </c>
       <c r="L108" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M108" t="n">
-        <v>0.5709</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612745</v>
+        <v>1610612764</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K109" t="n">
         <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M109" t="n">
-        <v>0.6825</v>
+        <v>0.2483</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612744</v>
+        <v>1610612737</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K110" t="n">
         <v>1</v>
       </c>
       <c r="L110" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M110" t="n">
-        <v>0.3303</v>
+        <v>0.4912</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612766</v>
+        <v>1610612738</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612765</v>
+        <v>1610612740</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -6534,52 +6534,52 @@
         <v>171</v>
       </c>
       <c r="M111" t="n">
-        <v>0.5533</v>
+        <v>0.7672</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612764</v>
+        <v>1610612754</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -6589,52 +6589,52 @@
         <v>171</v>
       </c>
       <c r="M112" t="n">
-        <v>0.2375</v>
+        <v>0.3758</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C113" t="n">
-        <v>1610612737</v>
+        <v>1610612752</v>
       </c>
       <c r="D113" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -6644,52 +6644,52 @@
         <v>171</v>
       </c>
       <c r="M113" t="n">
-        <v>0.5008</v>
+        <v>0.7519</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B114" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C114" t="n">
-        <v>1610612738</v>
+        <v>1610612741</v>
       </c>
       <c r="D114" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -6699,52 +6699,52 @@
         <v>171</v>
       </c>
       <c r="M114" t="n">
-        <v>0.7647</v>
+        <v>0.4559</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B115" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C115" t="n">
-        <v>1610612754</v>
+        <v>1610612745</v>
       </c>
       <c r="D115" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -6754,52 +6754,52 @@
         <v>171</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3774</v>
+        <v>0.5009</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B116" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C116" t="n">
-        <v>1610612752</v>
+        <v>1610612749</v>
       </c>
       <c r="D116" t="n">
-        <v>1610612761</v>
+        <v>1610612751</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -6809,52 +6809,52 @@
         <v>171</v>
       </c>
       <c r="M116" t="n">
-        <v>0.7494</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B117" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C117" t="n">
-        <v>1610612741</v>
+        <v>1610612759</v>
       </c>
       <c r="D117" t="n">
-        <v>1610612753</v>
+        <v>1610612742</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -6864,52 +6864,52 @@
         <v>171</v>
       </c>
       <c r="M117" t="n">
-        <v>0.4679</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C118" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="D118" t="n">
-        <v>1610612750</v>
+        <v>1610612763</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -6919,52 +6919,52 @@
         <v>171</v>
       </c>
       <c r="M118" t="n">
-        <v>0.5021</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C119" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="D119" t="n">
-        <v>1610612751</v>
+        <v>1610612760</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -6974,52 +6974,52 @@
         <v>171</v>
       </c>
       <c r="M119" t="n">
-        <v>0.7375</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C120" t="n">
-        <v>1610612759</v>
+        <v>1610612757</v>
       </c>
       <c r="D120" t="n">
-        <v>1610612742</v>
+        <v>1610612746</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -7029,52 +7029,52 @@
         <v>171</v>
       </c>
       <c r="M120" t="n">
-        <v>0.8357</v>
+        <v>0.4186</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C121" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="D121" t="n">
-        <v>1610612763</v>
+        <v>1610612744</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -7084,52 +7084,52 @@
         <v>171</v>
       </c>
       <c r="M121" t="n">
-        <v>0.5322</v>
+        <v>0.4219</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B122" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C122" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="D122" t="n">
-        <v>1610612760</v>
+        <v>1610612756</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -7139,217 +7139,217 @@
         <v>171</v>
       </c>
       <c r="M122" t="n">
-        <v>0.4659</v>
+        <v>0.6338</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C123" t="n">
-        <v>1610612757</v>
+        <v>1610612738</v>
       </c>
       <c r="D123" t="n">
-        <v>1610612746</v>
+        <v>1610612753</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K123" t="n">
         <v>1</v>
       </c>
       <c r="L123" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M123" t="n">
-        <v>0.4378</v>
+        <v>0.7836</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C124" t="n">
-        <v>1610612758</v>
+        <v>1610612739</v>
       </c>
       <c r="D124" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K124" t="n">
         <v>1</v>
       </c>
       <c r="L124" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M124" t="n">
-        <v>0.4181</v>
+        <v>0.8612</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C125" t="n">
-        <v>1610612747</v>
+        <v>1610612754</v>
       </c>
       <c r="D125" t="n">
-        <v>1610612756</v>
+        <v>1610612765</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K125" t="n">
         <v>1</v>
       </c>
       <c r="L125" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M125" t="n">
-        <v>0.6332</v>
+        <v>0.2662</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B126" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C126" t="n">
-        <v>1610612738</v>
+        <v>1610612748</v>
       </c>
       <c r="D126" t="n">
-        <v>1610612753</v>
+        <v>1610612737</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -7359,52 +7359,52 @@
         <v>173</v>
       </c>
       <c r="M126" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.5433</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B127" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C127" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="D127" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -7414,52 +7414,52 @@
         <v>173</v>
       </c>
       <c r="M127" t="n">
-        <v>0.8592</v>
+        <v>0.6536</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B128" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C128" t="n">
-        <v>1610612754</v>
+        <v>1610612755</v>
       </c>
       <c r="D128" t="n">
-        <v>1610612765</v>
+        <v>1610612749</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -7469,52 +7469,52 @@
         <v>173</v>
       </c>
       <c r="M128" t="n">
-        <v>0.2619</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B129" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C129" t="n">
-        <v>1610612748</v>
+        <v>1610612761</v>
       </c>
       <c r="D129" t="n">
-        <v>1610612737</v>
+        <v>1610612751</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -7524,52 +7524,52 @@
         <v>173</v>
       </c>
       <c r="M129" t="n">
-        <v>0.515</v>
+        <v>0.8288</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B130" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C130" t="n">
-        <v>1610612752</v>
+        <v>1610612742</v>
       </c>
       <c r="D130" t="n">
-        <v>1610612766</v>
+        <v>1610612741</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -7579,52 +7579,52 @@
         <v>173</v>
       </c>
       <c r="M130" t="n">
-        <v>0.6504</v>
+        <v>0.5027</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B131" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C131" t="n">
-        <v>1610612755</v>
+        <v>1610612745</v>
       </c>
       <c r="D131" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -7634,52 +7634,52 @@
         <v>173</v>
       </c>
       <c r="M131" t="n">
-        <v>0.714</v>
+        <v>0.7954</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B132" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C132" t="n">
-        <v>1610612761</v>
+        <v>1610612750</v>
       </c>
       <c r="D132" t="n">
-        <v>1610612751</v>
+        <v>1610612740</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -7689,52 +7689,52 @@
         <v>173</v>
       </c>
       <c r="M132" t="n">
-        <v>0.8305</v>
+        <v>0.7441</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B133" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C133" t="n">
-        <v>1610612742</v>
+        <v>1610612760</v>
       </c>
       <c r="D133" t="n">
-        <v>1610612741</v>
+        <v>1610612756</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -7744,52 +7744,52 @@
         <v>173</v>
       </c>
       <c r="M133" t="n">
-        <v>0.4808</v>
+        <v>0.7999000000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B134" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C134" t="n">
-        <v>1610612745</v>
+        <v>1610612759</v>
       </c>
       <c r="D134" t="n">
-        <v>1610612763</v>
+        <v>1610612743</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K134" t="n">
@@ -7799,52 +7799,52 @@
         <v>173</v>
       </c>
       <c r="M134" t="n">
-        <v>0.7944</v>
+        <v>0.6498</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0022501195</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B135" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C135" t="n">
-        <v>1610612750</v>
+        <v>1610612747</v>
       </c>
       <c r="D135" t="n">
-        <v>1610612740</v>
+        <v>1610612762</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -7854,52 +7854,52 @@
         <v>173</v>
       </c>
       <c r="M135" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0022501196</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B136" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C136" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="D136" t="n">
-        <v>1610612756</v>
+        <v>1610612744</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -7909,52 +7909,52 @@
         <v>173</v>
       </c>
       <c r="M136" t="n">
-        <v>0.8021</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0022501197</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B137" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C137" t="n">
-        <v>1610612759</v>
+        <v>1610612757</v>
       </c>
       <c r="D137" t="n">
-        <v>1610612743</v>
+        <v>1610612758</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -7964,172 +7964,7 @@
         <v>173</v>
       </c>
       <c r="M137" t="n">
-        <v>0.6395999999999999</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B138" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C138" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K138" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" t="n">
-        <v>173</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0.8488</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B139" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C139" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K139" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" t="n">
-        <v>173</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0.6968</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C140" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K140" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" t="n">
-        <v>173</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0.777</v>
+        <v>0.7779</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,182 +490,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501066</t>
+          <t>0022501076</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612746</v>
+        <v>1610612759</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2216</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501067</t>
+          <t>0022501077</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612738</v>
+        <v>1610612766</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612737</v>
+        <v>1610612755</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6751</v>
+        <v>0.7282999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501068</t>
+          <t>0022501078</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612739</v>
+        <v>1610612737</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612748</v>
+        <v>1610612758</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501069</t>
+          <t>0022501079</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C5" t="n">
         <v>1610612763</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,2285 +701,2285 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3236</v>
+        <v>0.5106000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501070</t>
+          <t>0022501080</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612760</v>
+        <v>1610612750</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M6" t="n">
-        <v>0.834</v>
+        <v>0.4861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501071</t>
+          <t>0022501081</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612740</v>
+        <v>1610612762</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7418</v>
+        <v>0.7924</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501072</t>
+          <t>0022501082</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612743</v>
+        <v>1610612749</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612762</v>
+        <v>1610612746</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8515</v>
+        <v>0.2445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501073</t>
+          <t>0022501083</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612744</v>
+        <v>1610612754</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612764</v>
+        <v>1610612748</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7977</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501074</t>
+          <t>0022501084</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612757</v>
+        <v>1610612751</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612742</v>
+        <v>1610612758</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7256</v>
+        <v>0.5663</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501075</t>
+          <t>0022501085</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612747</v>
+        <v>1610612766</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612751</v>
+        <v>1610612738</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8452</v>
+        <v>0.4569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501076</t>
+          <t>0022501086</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612749</v>
+        <v>1610612761</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612759</v>
+        <v>1610612753</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2125</v>
+        <v>0.6248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501077</t>
+          <t>0022501087</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612766</v>
+        <v>1610612757</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612755</v>
+        <v>1610612764</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7274</v>
+        <v>0.8018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501078</t>
+          <t>0022501088</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612758</v>
+        <v>1610612745</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7974</v>
+        <v>0.4365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501079</t>
+          <t>0022501089</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612763</v>
+        <v>1610612760</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612741</v>
+        <v>1610612752</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4985</v>
+        <v>0.7063</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501080</t>
+          <t>0022501090</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612750</v>
+        <v>1610612743</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612765</v>
+        <v>1610612744</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4937</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501081</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612756</v>
+        <v>1610612748</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612762</v>
+        <v>1610612755</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8374</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501082</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612749</v>
+        <v>1610612737</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612746</v>
+        <v>1610612738</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" t="n">
-        <v>0.243</v>
+        <v>0.5598</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501083</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612754</v>
+        <v>1610612763</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612748</v>
+        <v>1610612756</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2745</v>
+        <v>0.3823</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501084</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612751</v>
+        <v>1610612759</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612758</v>
+        <v>1610612741</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5437</v>
+        <v>0.8257</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501085</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612766</v>
+        <v>1610612742</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612738</v>
+        <v>1610612750</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4525</v>
+        <v>0.3218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501086</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612761</v>
+        <v>1610612762</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612753</v>
+        <v>1610612739</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6325</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501087</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612757</v>
+        <v>1610612760</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612764</v>
+        <v>1610612765</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8018</v>
+        <v>0.6704</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501088</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612740</v>
+        <v>1610612747</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612745</v>
+        <v>1610612764</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4282</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501089</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612760</v>
+        <v>1610612749</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612752</v>
+        <v>1610612742</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6911</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46110</v>
+        <v>46112</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612743</v>
+        <v>1610612753</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7558</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612748</v>
+        <v>1610612751</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612755</v>
+        <v>1610612766</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="n">
-        <v>0.617</v>
+        <v>0.1949</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612737</v>
+        <v>1610612765</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5516</v>
+        <v>0.6414</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612763</v>
+        <v>1610612745</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612756</v>
+        <v>1610612752</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3552</v>
+        <v>0.4391</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612741</v>
+        <v>1610612739</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8257</v>
+        <v>0.5454</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612742</v>
+        <v>1610612746</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612750</v>
+        <v>1610612757</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M31" t="n">
-        <v>0.294</v>
+        <v>0.7047</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612762</v>
+        <v>1610612763</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M32" t="n">
-        <v>0.21</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612760</v>
+        <v>1610612764</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612765</v>
+        <v>1610612755</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6747</v>
+        <v>0.3144</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612747</v>
+        <v>1610612748</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8939</v>
+        <v>0.4515</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612749</v>
+        <v>1610612753</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612742</v>
+        <v>1610612737</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6496</v>
+        <v>0.3951</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612756</v>
+        <v>1610612758</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6083</v>
+        <v>0.7716</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612766</v>
+        <v>1610612754</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1922</v>
+        <v>0.6859</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612765</v>
+        <v>1610612745</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612761</v>
+        <v>1610612749</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6397</v>
+        <v>0.8068</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612752</v>
+        <v>1610612743</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4391</v>
+        <v>0.2053</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612747</v>
+        <v>1610612744</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612739</v>
+        <v>1610612759</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5683</v>
+        <v>0.2582</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612757</v>
+        <v>1610612756</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7047</v>
+        <v>0.6593</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612763</v>
+        <v>1610612765</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612752</v>
+        <v>1610612750</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2547</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612764</v>
+        <v>1610612760</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612755</v>
+        <v>1610612747</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3107</v>
+        <v>0.7116</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612748</v>
+        <v>1610612744</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4294</v>
+        <v>0.2906</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612753</v>
+        <v>1610612757</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4031</v>
+        <v>0.6475</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612761</v>
+        <v>1610612746</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612758</v>
+        <v>1610612759</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7588</v>
+        <v>0.5339</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612741</v>
+        <v>1610612766</v>
       </c>
       <c r="D47" t="n">
         <v>1610612754</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2999,427 +2999,427 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6859</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612745</v>
+        <v>1610612755</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612749</v>
+        <v>1610612750</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.5245</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612762</v>
+        <v>1610612751</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612743</v>
+        <v>1610612737</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2053</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612744</v>
+        <v>1610612752</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612759</v>
+        <v>1610612741</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2824</v>
+        <v>0.8153</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612756</v>
+        <v>1610612762</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6639</v>
+        <v>0.8052</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612765</v>
+        <v>1610612763</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612750</v>
+        <v>1610612761</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6318</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612760</v>
+        <v>1610612749</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612747</v>
+        <v>1610612738</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6899</v>
+        <v>0.2261</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612744</v>
+        <v>1610612742</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612739</v>
+        <v>1610612753</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3055</v>
+        <v>0.4023</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612757</v>
+        <v>1610612758</v>
       </c>
       <c r="D55" t="n">
         <v>1610612740</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3439,148 +3439,148 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6613</v>
+        <v>0.4367</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612759</v>
+        <v>1610612764</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5339</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612766</v>
+        <v>1610612743</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612754</v>
+        <v>1610612759</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8034</v>
+        <v>0.5029</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C58" t="n">
         <v>1610612755</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612750</v>
+        <v>1610612765</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3616,605 +3616,605 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5135</v>
+        <v>0.3464</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612751</v>
+        <v>1610612738</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2132</v>
+        <v>0.7399</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612752</v>
+        <v>1610612751</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612741</v>
+        <v>1610612764</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8153</v>
+        <v>0.6323</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612762</v>
+        <v>1610612756</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.4511</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C62" t="n">
+        <v>1610612749</v>
+      </c>
+      <c r="D62" t="n">
         <v>1610612763</v>
       </c>
-      <c r="D62" t="n">
-        <v>1610612761</v>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Bucks</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Grizzlies</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>MEM</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M62" t="n">
-        <v>0.34</v>
+        <v>0.5948</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612749</v>
+        <v>1610612739</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M63" t="n">
-        <v>0.2246</v>
+        <v>0.8532999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612742</v>
+        <v>1610612750</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3984</v>
+        <v>0.5457</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612758</v>
+        <v>1610612740</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4772</v>
+        <v>0.5405</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612748</v>
+        <v>1610612760</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612764</v>
+        <v>1610612762</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8359</v>
+        <v>0.8518</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612743</v>
+        <v>1610612742</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M67" t="n">
-        <v>0.5062</v>
+        <v>0.2341</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612755</v>
+        <v>1610612758</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612765</v>
+        <v>1610612746</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M68" t="n">
-        <v>0.3607</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612738</v>
+        <v>1610612744</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612761</v>
+        <v>1610612745</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4224,962 +4224,962 @@
         <v>166</v>
       </c>
       <c r="M69" t="n">
-        <v>0.7511</v>
+        <v>0.4736</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612751</v>
+        <v>1610612737</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612764</v>
+        <v>1610612752</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6267</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612741</v>
+        <v>1610612753</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612756</v>
+        <v>1610612765</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4511</v>
+        <v>0.3734</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612763</v>
+        <v>1610612739</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M72" t="n">
-        <v>0.5985</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612739</v>
+        <v>1610612759</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612754</v>
+        <v>1610612755</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8512</v>
+        <v>0.8083</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612750</v>
+        <v>1610612743</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612766</v>
+        <v>1610612757</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M74" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.7542</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612740</v>
+        <v>1610612764</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612753</v>
+        <v>1610612741</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M75" t="n">
-        <v>0.5364</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612760</v>
+        <v>1610612738</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612762</v>
+        <v>1610612766</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8518</v>
+        <v>0.6377</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612742</v>
+        <v>1610612751</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612747</v>
+        <v>1610612749</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M77" t="n">
-        <v>0.231</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612758</v>
+        <v>1610612761</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M78" t="n">
-        <v>0.221</v>
+        <v>0.5485</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612744</v>
+        <v>1610612754</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>0.4814</v>
+        <v>0.2647</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612752</v>
+        <v>1610612762</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>0.4931</v>
+        <v>0.7206</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612765</v>
+        <v>1610612758</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M81" t="n">
-        <v>0.3834</v>
+        <v>0.7455000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612763</v>
+        <v>1610612747</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612739</v>
+        <v>1610612760</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M82" t="n">
-        <v>0.2311</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612759</v>
+        <v>1610612746</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612755</v>
+        <v>1610612742</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8075</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612743</v>
+        <v>1610612756</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612757</v>
+        <v>1610612745</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K84" t="n">
         <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M84" t="n">
-        <v>0.7565</v>
+        <v>0.5462</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612764</v>
+        <v>1610612739</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612741</v>
+        <v>1610612737</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K85" t="n">
         <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M85" t="n">
-        <v>0.3711</v>
+        <v>0.6863</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612738</v>
+        <v>1610612753</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M86" t="n">
-        <v>0.6474</v>
+        <v>0.5545</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612751</v>
+        <v>1610612765</v>
       </c>
       <c r="D87" t="n">
         <v>1610612749</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5199,1167 +5199,1167 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M87" t="n">
-        <v>0.4043</v>
+        <v>0.8443000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612748</v>
+        <v>1610612757</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K88" t="n">
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M88" t="n">
-        <v>0.5512</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612754</v>
+        <v>1610612743</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612750</v>
+        <v>1610612763</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M89" t="n">
-        <v>0.257</v>
+        <v>0.8358</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612740</v>
+        <v>1610612746</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612762</v>
+        <v>1610612760</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M90" t="n">
-        <v>0.72</v>
+        <v>0.4437</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612758</v>
+        <v>1610612742</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K91" t="n">
         <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.8001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612760</v>
+        <v>1610612748</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M92" t="n">
-        <v>0.4678</v>
+        <v>0.5485</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612746</v>
+        <v>1610612764</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612742</v>
+        <v>1610612741</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K93" t="n">
         <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M93" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612756</v>
+        <v>1610612751</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612745</v>
+        <v>1610612754</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5438</v>
+        <v>0.4959</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612737</v>
+        <v>1610612738</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M95" t="n">
-        <v>0.6752</v>
+        <v>0.5828</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612753</v>
+        <v>1610612745</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612750</v>
+        <v>1610612755</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M96" t="n">
-        <v>0.5364</v>
+        <v>0.6899</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612765</v>
+        <v>1610612744</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612749</v>
+        <v>1610612747</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M97" t="n">
-        <v>0.8421</v>
+        <v>0.3223</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612759</v>
+        <v>1610612766</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612757</v>
+        <v>1610612765</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K98" t="n">
         <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M98" t="n">
-        <v>0.7891</v>
+        <v>0.5411</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612743</v>
+        <v>1610612764</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612763</v>
+        <v>1610612748</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K99" t="n">
         <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M99" t="n">
-        <v>0.8425</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612746</v>
+        <v>1610612737</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612760</v>
+        <v>1610612739</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K100" t="n">
         <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M100" t="n">
-        <v>0.4502</v>
+        <v>0.4639</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612756</v>
+        <v>1610612738</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M101" t="n">
-        <v>0.8028</v>
+        <v>0.7597</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612761</v>
+        <v>1610612754</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K102" t="n">
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M102" t="n">
-        <v>0.5512</v>
+        <v>0.3812</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612764</v>
+        <v>1610612752</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612741</v>
+        <v>1610612761</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K103" t="n">
         <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M103" t="n">
-        <v>0.3711</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612754</v>
+        <v>1610612753</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4893</v>
+        <v>0.4559</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612752</v>
+        <v>1610612745</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612738</v>
+        <v>1610612750</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K105" t="n">
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M105" t="n">
-        <v>0.5823</v>
+        <v>0.5048</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612755</v>
+        <v>1610612751</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K106" t="n">
         <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M106" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612744</v>
+        <v>1610612759</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612747</v>
+        <v>1610612742</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K107" t="n">
         <v>1</v>
       </c>
       <c r="L107" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M107" t="n">
-        <v>0.3288</v>
+        <v>0.8428</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612766</v>
+        <v>1610612762</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612765</v>
+        <v>1610612763</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -6369,52 +6369,52 @@
         <v>171</v>
       </c>
       <c r="M108" t="n">
-        <v>0.548</v>
+        <v>0.5278</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612764</v>
+        <v>1610612743</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612748</v>
+        <v>1610612760</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -6424,52 +6424,52 @@
         <v>171</v>
       </c>
       <c r="M109" t="n">
-        <v>0.2483</v>
+        <v>0.4791</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612737</v>
+        <v>1610612757</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612739</v>
+        <v>1610612746</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -6479,52 +6479,52 @@
         <v>171</v>
       </c>
       <c r="M110" t="n">
-        <v>0.4912</v>
+        <v>0.4225</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612738</v>
+        <v>1610612758</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612740</v>
+        <v>1610612744</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -6534,52 +6534,52 @@
         <v>171</v>
       </c>
       <c r="M111" t="n">
-        <v>0.7672</v>
+        <v>0.4236</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612755</v>
+        <v>1610612756</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -6589,602 +6589,602 @@
         <v>171</v>
       </c>
       <c r="M112" t="n">
-        <v>0.3758</v>
+        <v>0.6211</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C113" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="D113" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K113" t="n">
         <v>1</v>
       </c>
       <c r="L113" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M113" t="n">
-        <v>0.7519</v>
+        <v>0.7679</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C114" t="n">
-        <v>1610612741</v>
+        <v>1610612739</v>
       </c>
       <c r="D114" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K114" t="n">
         <v>1</v>
       </c>
       <c r="L114" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M114" t="n">
-        <v>0.4559</v>
+        <v>0.8612</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C115" t="n">
-        <v>1610612745</v>
+        <v>1610612754</v>
       </c>
       <c r="D115" t="n">
-        <v>1610612750</v>
+        <v>1610612765</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K115" t="n">
         <v>1</v>
       </c>
       <c r="L115" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M115" t="n">
-        <v>0.5009</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C116" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="D116" t="n">
-        <v>1610612751</v>
+        <v>1610612737</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K116" t="n">
         <v>1</v>
       </c>
       <c r="L116" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M116" t="n">
-        <v>0.7609</v>
+        <v>0.5389</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C117" t="n">
-        <v>1610612759</v>
+        <v>1610612752</v>
       </c>
       <c r="D117" t="n">
-        <v>1610612742</v>
+        <v>1610612766</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K117" t="n">
         <v>1</v>
       </c>
       <c r="L117" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M117" t="n">
-        <v>0.8472</v>
+        <v>0.6523</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C118" t="n">
-        <v>1610612762</v>
+        <v>1610612755</v>
       </c>
       <c r="D118" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K118" t="n">
         <v>1</v>
       </c>
       <c r="L118" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M118" t="n">
-        <v>0.5334</v>
+        <v>0.6973</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C119" t="n">
-        <v>1610612743</v>
+        <v>1610612761</v>
       </c>
       <c r="D119" t="n">
-        <v>1610612760</v>
+        <v>1610612751</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K119" t="n">
         <v>1</v>
       </c>
       <c r="L119" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M119" t="n">
-        <v>0.4914</v>
+        <v>0.8288</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C120" t="n">
-        <v>1610612757</v>
+        <v>1610612742</v>
       </c>
       <c r="D120" t="n">
-        <v>1610612746</v>
+        <v>1610612741</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K120" t="n">
         <v>1</v>
       </c>
       <c r="L120" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M120" t="n">
-        <v>0.4186</v>
+        <v>0.5072</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C121" t="n">
-        <v>1610612758</v>
+        <v>1610612745</v>
       </c>
       <c r="D121" t="n">
-        <v>1610612744</v>
+        <v>1610612763</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K121" t="n">
         <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M121" t="n">
-        <v>0.4219</v>
+        <v>0.7917999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C122" t="n">
-        <v>1610612747</v>
+        <v>1610612750</v>
       </c>
       <c r="D122" t="n">
-        <v>1610612756</v>
+        <v>1610612740</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K122" t="n">
         <v>1</v>
       </c>
       <c r="L122" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M122" t="n">
-        <v>0.6338</v>
+        <v>0.7203000000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C123" t="n">
-        <v>1610612738</v>
+        <v>1610612760</v>
       </c>
       <c r="D123" t="n">
-        <v>1610612753</v>
+        <v>1610612756</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -7194,52 +7194,52 @@
         <v>173</v>
       </c>
       <c r="M123" t="n">
-        <v>0.7836</v>
+        <v>0.8089</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B124" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C124" t="n">
-        <v>1610612739</v>
+        <v>1610612759</v>
       </c>
       <c r="D124" t="n">
-        <v>1610612764</v>
+        <v>1610612743</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -7249,52 +7249,52 @@
         <v>173</v>
       </c>
       <c r="M124" t="n">
-        <v>0.8612</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B125" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C125" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="D125" t="n">
-        <v>1610612765</v>
+        <v>1610612762</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -7304,52 +7304,52 @@
         <v>173</v>
       </c>
       <c r="M125" t="n">
-        <v>0.2662</v>
+        <v>0.8551</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B126" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C126" t="n">
-        <v>1610612748</v>
+        <v>1610612746</v>
       </c>
       <c r="D126" t="n">
-        <v>1610612737</v>
+        <v>1610612744</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -7359,52 +7359,52 @@
         <v>173</v>
       </c>
       <c r="M126" t="n">
-        <v>0.5433</v>
+        <v>0.7099</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B127" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C127" t="n">
-        <v>1610612752</v>
+        <v>1610612757</v>
       </c>
       <c r="D127" t="n">
-        <v>1610612766</v>
+        <v>1610612758</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -7414,557 +7414,7 @@
         <v>173</v>
       </c>
       <c r="M127" t="n">
-        <v>0.6536</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>0022501191</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C128" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="D128" t="n">
-        <v>1610612749</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Bucks</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Xfinity Mobile Arena</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="K128" t="n">
-        <v>1</v>
-      </c>
-      <c r="L128" t="n">
-        <v>173</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0.703</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>0022501192</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C129" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="D129" t="n">
-        <v>1610612751</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Nets</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Scotiabank Arena</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="K129" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" t="n">
-        <v>173</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0.8288</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>0022501193</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C130" t="n">
-        <v>1610612742</v>
-      </c>
-      <c r="D130" t="n">
-        <v>1610612741</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Mavericks</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Bulls</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>CHI</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>American Airlines Center</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="K130" t="n">
-        <v>1</v>
-      </c>
-      <c r="L130" t="n">
-        <v>173</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0.5027</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>0022501194</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C131" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="D131" t="n">
-        <v>1610612763</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Grizzlies</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Toyota Center</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="K131" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" t="n">
-        <v>173</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0.7954</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>0022501195</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C132" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1610612740</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Pelicans</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Target Center</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="K132" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" t="n">
-        <v>173</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0.7441</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C133" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D133" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" t="n">
-        <v>173</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0.7999000000000001</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C134" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D134" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K134" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" t="n">
-        <v>173</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0.6498</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B135" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C135" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K135" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" t="n">
-        <v>173</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0.8571</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C136" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K136" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" t="n">
-        <v>173</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0.7078</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B137" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C137" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K137" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" t="n">
-        <v>173</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0.7779</v>
+        <v>0.7826</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -539,7 +539,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2125</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="3">
@@ -649,7 +649,7 @@
         <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>0.829</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -704,7 +704,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5161</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         <v>158</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4861</v>
+        <v>0.4596</v>
       </c>
     </row>
     <row r="7">
@@ -814,7 +814,7 @@
         <v>158</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7924</v>
+        <v>0.8384</v>
       </c>
     </row>
     <row r="8">
@@ -869,7 +869,7 @@
         <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2445</v>
+        <v>0.2414</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
         <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2763</v>
+        <v>0.2861</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>159</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5663</v>
+        <v>0.5679</v>
       </c>
     </row>
     <row r="11">
@@ -1034,7 +1034,7 @@
         <v>159</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4569</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="12">
@@ -1089,7 +1089,7 @@
         <v>159</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6248</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="13">
@@ -1144,7 +1144,7 @@
         <v>159</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8018</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="14">
@@ -1199,7 +1199,7 @@
         <v>159</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4365</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="15">
@@ -1254,7 +1254,7 @@
         <v>159</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7063</v>
+        <v>0.6971000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1309,7 +1309,7 @@
         <v>159</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7607</v>
+        <v>0.7598</v>
       </c>
     </row>
     <row r="17">
@@ -1364,7 +1364,7 @@
         <v>160</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6028</v>
       </c>
     </row>
     <row r="18">
@@ -1419,7 +1419,7 @@
         <v>160</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5598</v>
+        <v>0.5387</v>
       </c>
     </row>
     <row r="19">
@@ -1529,7 +1529,7 @@
         <v>160</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8257</v>
+        <v>0.8315</v>
       </c>
     </row>
     <row r="21">
@@ -1584,7 +1584,7 @@
         <v>160</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3218</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="22">
@@ -1639,7 +1639,7 @@
         <v>160</v>
       </c>
       <c r="M22" t="n">
-        <v>0.21</v>
+        <v>0.2006</v>
       </c>
     </row>
     <row r="23">
@@ -1694,7 +1694,7 @@
         <v>160</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6704</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="24">
@@ -1749,7 +1749,7 @@
         <v>160</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8939</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="25">
@@ -1804,7 +1804,7 @@
         <v>161</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6473</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="26">
@@ -1914,7 +1914,7 @@
         <v>161</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1949</v>
+        <v>0.1984</v>
       </c>
     </row>
     <row r="28">
@@ -1969,7 +1969,7 @@
         <v>161</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6414</v>
+        <v>0.6456</v>
       </c>
     </row>
     <row r="29">
@@ -2024,7 +2024,7 @@
         <v>161</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4391</v>
+        <v>0.4384</v>
       </c>
     </row>
     <row r="30">
@@ -2079,7 +2079,7 @@
         <v>161</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5454</v>
+        <v>0.5621</v>
       </c>
     </row>
     <row r="31">
@@ -2134,7 +2134,7 @@
         <v>161</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7047</v>
+        <v>0.7117</v>
       </c>
     </row>
     <row r="32">
@@ -2189,7 +2189,7 @@
         <v>162</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2664</v>
+        <v>0.2731</v>
       </c>
     </row>
     <row r="33">
@@ -2244,7 +2244,7 @@
         <v>162</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3144</v>
+        <v>0.3084</v>
       </c>
     </row>
     <row r="34">
@@ -2299,7 +2299,7 @@
         <v>162</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4515</v>
+        <v>0.4289</v>
       </c>
     </row>
     <row r="35">
@@ -2354,7 +2354,7 @@
         <v>162</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3951</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="36">
@@ -2409,7 +2409,7 @@
         <v>162</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7716</v>
+        <v>0.7843</v>
       </c>
     </row>
     <row r="37">
@@ -2464,7 +2464,7 @@
         <v>162</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6859</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="38">
@@ -2519,7 +2519,7 @@
         <v>162</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8068</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2574,7 +2574,7 @@
         <v>162</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2053</v>
+        <v>0.1911</v>
       </c>
     </row>
     <row r="40">
@@ -2629,7 +2629,7 @@
         <v>162</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2582</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="41">
@@ -2684,7 +2684,7 @@
         <v>163</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6593</v>
+        <v>0.6576</v>
       </c>
     </row>
     <row r="42">
@@ -2739,7 +2739,7 @@
         <v>163</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6375</v>
+        <v>0.6627</v>
       </c>
     </row>
     <row r="43">
@@ -2794,7 +2794,7 @@
         <v>163</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7116</v>
+        <v>0.6834</v>
       </c>
     </row>
     <row r="44">
@@ -2849,7 +2849,7 @@
         <v>163</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2906</v>
+        <v>0.2934</v>
       </c>
     </row>
     <row r="45">
@@ -2904,7 +2904,7 @@
         <v>163</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6475</v>
+        <v>0.6292</v>
       </c>
     </row>
     <row r="46">
@@ -2959,7 +2959,7 @@
         <v>163</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5339</v>
+        <v>0.5358000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3014,7 +3014,7 @@
         <v>164</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8034</v>
+        <v>0.7934</v>
       </c>
     </row>
     <row r="48">
@@ -3069,7 +3069,7 @@
         <v>164</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5245</v>
+        <v>0.5361</v>
       </c>
     </row>
     <row r="49">
@@ -3124,7 +3124,7 @@
         <v>164</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2132</v>
+        <v>0.2114</v>
       </c>
     </row>
     <row r="50">
@@ -3179,7 +3179,7 @@
         <v>164</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8153</v>
+        <v>0.8191000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3289,7 +3289,7 @@
         <v>164</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3575</v>
+        <v>0.3541</v>
       </c>
     </row>
     <row r="53">
@@ -3344,7 +3344,7 @@
         <v>164</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2261</v>
+        <v>0.2198</v>
       </c>
     </row>
     <row r="54">
@@ -3399,7 +3399,7 @@
         <v>164</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4023</v>
+        <v>0.4241</v>
       </c>
     </row>
     <row r="55">
@@ -3454,7 +3454,7 @@
         <v>164</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4367</v>
+        <v>0.4378</v>
       </c>
     </row>
     <row r="56">
@@ -3509,7 +3509,7 @@
         <v>165</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8359</v>
+        <v>0.8287</v>
       </c>
     </row>
     <row r="57">
@@ -3564,7 +3564,7 @@
         <v>165</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5029</v>
+        <v>0.5138</v>
       </c>
     </row>
     <row r="58">
@@ -3674,7 +3674,7 @@
         <v>166</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7399</v>
+        <v>0.7401</v>
       </c>
     </row>
     <row r="60">
@@ -3729,7 +3729,7 @@
         <v>166</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6323</v>
+        <v>0.6355</v>
       </c>
     </row>
     <row r="61">
@@ -3784,7 +3784,7 @@
         <v>166</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4511</v>
+        <v>0.4361</v>
       </c>
     </row>
     <row r="62">
@@ -3839,7 +3839,7 @@
         <v>166</v>
       </c>
       <c r="M62" t="n">
-        <v>0.5948</v>
+        <v>0.5982</v>
       </c>
     </row>
     <row r="63">
@@ -3894,7 +3894,7 @@
         <v>166</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8522999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3949,7 +3949,7 @@
         <v>166</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5457</v>
+        <v>0.5291</v>
       </c>
     </row>
     <row r="65">
@@ -4004,7 +4004,7 @@
         <v>166</v>
       </c>
       <c r="M65" t="n">
-        <v>0.5405</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="66">
@@ -4059,7 +4059,7 @@
         <v>166</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8518</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="67">
@@ -4114,7 +4114,7 @@
         <v>166</v>
       </c>
       <c r="M67" t="n">
-        <v>0.2341</v>
+        <v>0.2345</v>
       </c>
     </row>
     <row r="68">
@@ -4169,7 +4169,7 @@
         <v>166</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2145</v>
+        <v>0.2098</v>
       </c>
     </row>
     <row r="69">
@@ -4224,7 +4224,7 @@
         <v>166</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4736</v>
+        <v>0.4802</v>
       </c>
     </row>
     <row r="70">
@@ -4279,7 +4279,7 @@
         <v>167</v>
       </c>
       <c r="M70" t="n">
-        <v>0.496</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="71">
@@ -4389,7 +4389,7 @@
         <v>167</v>
       </c>
       <c r="M72" t="n">
-        <v>0.2262</v>
+        <v>0.2264</v>
       </c>
     </row>
     <row r="73">
@@ -4444,7 +4444,7 @@
         <v>167</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8083</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="74">
@@ -4499,7 +4499,7 @@
         <v>167</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7542</v>
+        <v>0.7683</v>
       </c>
     </row>
     <row r="75">
@@ -4554,7 +4554,7 @@
         <v>168</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3711</v>
+        <v>0.3791</v>
       </c>
     </row>
     <row r="76">
@@ -4609,7 +4609,7 @@
         <v>168</v>
       </c>
       <c r="M76" t="n">
-        <v>0.6377</v>
+        <v>0.6566</v>
       </c>
     </row>
     <row r="77">
@@ -4664,7 +4664,7 @@
         <v>168</v>
       </c>
       <c r="M77" t="n">
-        <v>0.4085</v>
+        <v>0.4013</v>
       </c>
     </row>
     <row r="78">
@@ -4719,7 +4719,7 @@
         <v>168</v>
       </c>
       <c r="M78" t="n">
-        <v>0.5485</v>
+        <v>0.5633</v>
       </c>
     </row>
     <row r="79">
@@ -4774,7 +4774,7 @@
         <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>0.2647</v>
+        <v>0.3053</v>
       </c>
     </row>
     <row r="80">
@@ -4829,7 +4829,7 @@
         <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7206</v>
+        <v>0.7199</v>
       </c>
     </row>
     <row r="81">
@@ -4884,7 +4884,7 @@
         <v>168</v>
       </c>
       <c r="M81" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7635999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -4939,7 +4939,7 @@
         <v>168</v>
       </c>
       <c r="M82" t="n">
-        <v>0.45</v>
+        <v>0.4699</v>
       </c>
     </row>
     <row r="83">
@@ -4994,7 +4994,7 @@
         <v>168</v>
       </c>
       <c r="M83" t="n">
-        <v>0.824</v>
+        <v>0.8179</v>
       </c>
     </row>
     <row r="84">
@@ -5049,7 +5049,7 @@
         <v>168</v>
       </c>
       <c r="M84" t="n">
-        <v>0.5462</v>
+        <v>0.5381</v>
       </c>
     </row>
     <row r="85">
@@ -5104,7 +5104,7 @@
         <v>169</v>
       </c>
       <c r="M85" t="n">
-        <v>0.6863</v>
+        <v>0.6782</v>
       </c>
     </row>
     <row r="86">
@@ -5159,7 +5159,7 @@
         <v>169</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5545</v>
+        <v>0.5677</v>
       </c>
     </row>
     <row r="87">
@@ -5269,7 +5269,7 @@
         <v>169</v>
       </c>
       <c r="M88" t="n">
-        <v>0.784</v>
+        <v>0.7913</v>
       </c>
     </row>
     <row r="89">
@@ -5324,7 +5324,7 @@
         <v>169</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8358</v>
+        <v>0.8381999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5379,7 +5379,7 @@
         <v>169</v>
       </c>
       <c r="M90" t="n">
-        <v>0.4437</v>
+        <v>0.4253</v>
       </c>
     </row>
     <row r="91">
@@ -5434,7 +5434,7 @@
         <v>169</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8001</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="92">
@@ -5489,7 +5489,7 @@
         <v>170</v>
       </c>
       <c r="M92" t="n">
-        <v>0.5485</v>
+        <v>0.5633</v>
       </c>
     </row>
     <row r="93">
@@ -5544,7 +5544,7 @@
         <v>170</v>
       </c>
       <c r="M93" t="n">
-        <v>0.3711</v>
+        <v>0.3791</v>
       </c>
     </row>
     <row r="94">
@@ -5599,7 +5599,7 @@
         <v>170</v>
       </c>
       <c r="M94" t="n">
-        <v>0.4959</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="95">
@@ -5654,7 +5654,7 @@
         <v>170</v>
       </c>
       <c r="M95" t="n">
-        <v>0.5828</v>
+        <v>0.5671</v>
       </c>
     </row>
     <row r="96">
@@ -5709,7 +5709,7 @@
         <v>170</v>
       </c>
       <c r="M96" t="n">
-        <v>0.6899</v>
+        <v>0.6908</v>
       </c>
     </row>
     <row r="97">
@@ -5764,7 +5764,7 @@
         <v>170</v>
       </c>
       <c r="M97" t="n">
-        <v>0.3223</v>
+        <v>0.3218</v>
       </c>
     </row>
     <row r="98">
@@ -5874,7 +5874,7 @@
         <v>171</v>
       </c>
       <c r="M99" t="n">
-        <v>0.2525</v>
+        <v>0.2611</v>
       </c>
     </row>
     <row r="100">
@@ -5929,7 +5929,7 @@
         <v>171</v>
       </c>
       <c r="M100" t="n">
-        <v>0.4639</v>
+        <v>0.4489</v>
       </c>
     </row>
     <row r="101">
@@ -5984,7 +5984,7 @@
         <v>171</v>
       </c>
       <c r="M101" t="n">
-        <v>0.7597</v>
+        <v>0.7764</v>
       </c>
     </row>
     <row r="102">
@@ -6039,7 +6039,7 @@
         <v>171</v>
       </c>
       <c r="M102" t="n">
-        <v>0.3812</v>
+        <v>0.3809</v>
       </c>
     </row>
     <row r="103">
@@ -6094,7 +6094,7 @@
         <v>171</v>
       </c>
       <c r="M103" t="n">
-        <v>0.7453</v>
+        <v>0.7462</v>
       </c>
     </row>
     <row r="104">
@@ -6149,7 +6149,7 @@
         <v>171</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4559</v>
+        <v>0.4395</v>
       </c>
     </row>
     <row r="105">
@@ -6204,7 +6204,7 @@
         <v>171</v>
       </c>
       <c r="M105" t="n">
-        <v>0.5048</v>
+        <v>0.5326</v>
       </c>
     </row>
     <row r="106">
@@ -6259,7 +6259,7 @@
         <v>171</v>
       </c>
       <c r="M106" t="n">
-        <v>0.76</v>
+        <v>0.7695</v>
       </c>
     </row>
     <row r="107">
@@ -6314,7 +6314,7 @@
         <v>171</v>
       </c>
       <c r="M107" t="n">
-        <v>0.8428</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="108">
@@ -6369,7 +6369,7 @@
         <v>171</v>
       </c>
       <c r="M108" t="n">
-        <v>0.5278</v>
+        <v>0.5192</v>
       </c>
     </row>
     <row r="109">
@@ -6424,7 +6424,7 @@
         <v>171</v>
       </c>
       <c r="M109" t="n">
-        <v>0.4791</v>
+        <v>0.4911</v>
       </c>
     </row>
     <row r="110">
@@ -6479,7 +6479,7 @@
         <v>171</v>
       </c>
       <c r="M110" t="n">
-        <v>0.4225</v>
+        <v>0.3833</v>
       </c>
     </row>
     <row r="111">
@@ -6534,7 +6534,7 @@
         <v>171</v>
       </c>
       <c r="M111" t="n">
-        <v>0.4236</v>
+        <v>0.3668</v>
       </c>
     </row>
     <row r="112">
@@ -6589,7 +6589,7 @@
         <v>171</v>
       </c>
       <c r="M112" t="n">
-        <v>0.6211</v>
+        <v>0.6471</v>
       </c>
     </row>
     <row r="113">
@@ -6644,7 +6644,7 @@
         <v>173</v>
       </c>
       <c r="M113" t="n">
-        <v>0.7679</v>
+        <v>0.7747000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6699,7 +6699,7 @@
         <v>173</v>
       </c>
       <c r="M114" t="n">
-        <v>0.8612</v>
+        <v>0.8581</v>
       </c>
     </row>
     <row r="115">
@@ -6754,7 +6754,7 @@
         <v>173</v>
       </c>
       <c r="M115" t="n">
-        <v>0.2574</v>
+        <v>0.2596</v>
       </c>
     </row>
     <row r="116">
@@ -6809,7 +6809,7 @@
         <v>173</v>
       </c>
       <c r="M116" t="n">
-        <v>0.5389</v>
+        <v>0.5402</v>
       </c>
     </row>
     <row r="117">
@@ -6864,7 +6864,7 @@
         <v>173</v>
       </c>
       <c r="M117" t="n">
-        <v>0.6523</v>
+        <v>0.6506</v>
       </c>
     </row>
     <row r="118">
@@ -6919,7 +6919,7 @@
         <v>173</v>
       </c>
       <c r="M118" t="n">
-        <v>0.6973</v>
+        <v>0.6971000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -6974,7 +6974,7 @@
         <v>173</v>
       </c>
       <c r="M119" t="n">
-        <v>0.8288</v>
+        <v>0.8308</v>
       </c>
     </row>
     <row r="120">
@@ -7029,7 +7029,7 @@
         <v>173</v>
       </c>
       <c r="M120" t="n">
-        <v>0.5072</v>
+        <v>0.5286999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7084,7 +7084,7 @@
         <v>173</v>
       </c>
       <c r="M121" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7893</v>
       </c>
     </row>
     <row r="122">
@@ -7139,7 +7139,7 @@
         <v>173</v>
       </c>
       <c r="M122" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="123">
@@ -7194,7 +7194,7 @@
         <v>173</v>
       </c>
       <c r="M123" t="n">
-        <v>0.8089</v>
+        <v>0.8028</v>
       </c>
     </row>
     <row r="124">
@@ -7249,7 +7249,7 @@
         <v>173</v>
       </c>
       <c r="M124" t="n">
-        <v>0.6573</v>
+        <v>0.6308</v>
       </c>
     </row>
     <row r="125">
@@ -7304,7 +7304,7 @@
         <v>173</v>
       </c>
       <c r="M125" t="n">
-        <v>0.8551</v>
+        <v>0.8555</v>
       </c>
     </row>
     <row r="126">
@@ -7359,7 +7359,7 @@
         <v>173</v>
       </c>
       <c r="M126" t="n">
-        <v>0.7099</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="127">
@@ -7414,7 +7414,7 @@
         <v>173</v>
       </c>
       <c r="M127" t="n">
-        <v>0.7826</v>
+        <v>0.7832</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,46 +490,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501076</t>
+          <t>0022501077</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612749</v>
+        <v>1610612766</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612759</v>
+        <v>1610612755</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -539,52 +539,52 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>0.214</v>
+        <v>0.7002</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501077</t>
+          <t>0022501078</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612766</v>
+        <v>1610612737</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612755</v>
+        <v>1610612758</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -594,52 +594,52 @@
         <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.8048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501078</t>
+          <t>0022501079</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612737</v>
+        <v>1610612763</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612758</v>
+        <v>1610612741</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -649,52 +649,52 @@
         <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5364</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501079</t>
+          <t>0022501080</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612763</v>
+        <v>1610612750</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -704,52 +704,52 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5161</v>
+        <v>0.4666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501080</t>
+          <t>0022501081</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>46109</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612750</v>
+        <v>1610612756</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612765</v>
+        <v>1610612762</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -759,107 +759,107 @@
         <v>158</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4596</v>
+        <v>0.8405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501081</t>
+          <t>0022501082</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612756</v>
+        <v>1610612749</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612762</v>
+        <v>1610612746</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8384</v>
+        <v>0.2904</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501082</t>
+          <t>0022501083</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612749</v>
+        <v>1610612754</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612746</v>
+        <v>1610612748</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -869,52 +869,52 @@
         <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2414</v>
+        <v>0.2945</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501083</t>
+          <t>0022501084</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612748</v>
+        <v>1610612758</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -924,52 +924,52 @@
         <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2861</v>
+        <v>0.5712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501084</t>
+          <t>0022501085</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612751</v>
+        <v>1610612766</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612758</v>
+        <v>1610612738</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -979,52 +979,52 @@
         <v>159</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5679</v>
+        <v>0.4393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501085</t>
+          <t>0022501086</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612766</v>
+        <v>1610612761</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612738</v>
+        <v>1610612753</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1034,52 +1034,52 @@
         <v>159</v>
       </c>
       <c r="M11" t="n">
-        <v>0.442</v>
+        <v>0.5797</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501086</t>
+          <t>0022501087</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612761</v>
+        <v>1610612757</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1089,52 +1089,52 @@
         <v>159</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6216</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501087</t>
+          <t>0022501088</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612757</v>
+        <v>1610612740</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1144,52 +1144,52 @@
         <v>159</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7995</v>
+        <v>0.4008</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501088</t>
+          <t>0022501089</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612740</v>
+        <v>1610612760</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612745</v>
+        <v>1610612752</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1199,52 +1199,52 @@
         <v>159</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4316</v>
+        <v>0.6483</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501089</t>
+          <t>0022501090</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612760</v>
+        <v>1610612743</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612752</v>
+        <v>1610612744</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1254,107 +1254,107 @@
         <v>159</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.7782</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612743</v>
+        <v>1610612748</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7598</v>
+        <v>0.5854</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612748</v>
+        <v>1610612737</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612755</v>
+        <v>1610612738</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1364,52 +1364,52 @@
         <v>160</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6028</v>
+        <v>0.5133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612737</v>
+        <v>1610612763</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1419,52 +1419,52 @@
         <v>160</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5387</v>
+        <v>0.4106</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612763</v>
+        <v>1610612759</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612756</v>
+        <v>1610612741</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1474,52 +1474,52 @@
         <v>160</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3823</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612759</v>
+        <v>1610612742</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612741</v>
+        <v>1610612750</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1529,52 +1529,52 @@
         <v>160</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8315</v>
+        <v>0.3235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612742</v>
+        <v>1610612762</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612750</v>
+        <v>1610612739</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1584,52 +1584,52 @@
         <v>160</v>
       </c>
       <c r="M21" t="n">
-        <v>0.349</v>
+        <v>0.2091</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612762</v>
+        <v>1610612760</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612739</v>
+        <v>1610612765</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1639,52 +1639,52 @@
         <v>160</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2006</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612760</v>
+        <v>1610612747</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1694,107 +1694,107 @@
         <v>160</v>
       </c>
       <c r="M23" t="n">
-        <v>0.658</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612747</v>
+        <v>1610612749</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612764</v>
+        <v>1610612742</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8943</v>
+        <v>0.6262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612749</v>
+        <v>1610612753</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612742</v>
+        <v>1610612756</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1804,52 +1804,52 @@
         <v>161</v>
       </c>
       <c r="M25" t="n">
-        <v>0.644</v>
+        <v>0.5749</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1859,52 +1859,52 @@
         <v>161</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6083</v>
+        <v>0.2107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612751</v>
+        <v>1610612765</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612766</v>
+        <v>1610612761</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1914,52 +1914,52 @@
         <v>161</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1984</v>
+        <v>0.6091</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612765</v>
+        <v>1610612745</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612761</v>
+        <v>1610612752</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1969,52 +1969,52 @@
         <v>161</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6456</v>
+        <v>0.4662</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612745</v>
+        <v>1610612747</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2024,52 +2024,52 @@
         <v>161</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4384</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612739</v>
+        <v>1610612757</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,107 +2079,107 @@
         <v>161</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5621</v>
+        <v>0.7383999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612746</v>
+        <v>1610612763</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612757</v>
+        <v>1610612752</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7117</v>
+        <v>0.2956</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612763</v>
+        <v>1610612764</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2189,52 +2189,52 @@
         <v>162</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2731</v>
+        <v>0.3048</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612764</v>
+        <v>1610612748</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612755</v>
+        <v>1610612738</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2244,52 +2244,52 @@
         <v>162</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3084</v>
+        <v>0.4274</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612738</v>
+        <v>1610612737</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2299,52 +2299,52 @@
         <v>162</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4289</v>
+        <v>0.4251</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612737</v>
+        <v>1610612758</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2354,52 +2354,52 @@
         <v>162</v>
       </c>
       <c r="M35" t="n">
-        <v>0.409</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612761</v>
+        <v>1610612741</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612758</v>
+        <v>1610612754</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2409,52 +2409,52 @@
         <v>162</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7843</v>
+        <v>0.6858</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612741</v>
+        <v>1610612745</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2464,52 +2464,52 @@
         <v>162</v>
       </c>
       <c r="M37" t="n">
-        <v>0.679</v>
+        <v>0.8166</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2519,52 +2519,52 @@
         <v>162</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.1992</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612762</v>
+        <v>1610612744</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612743</v>
+        <v>1610612759</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2574,107 +2574,107 @@
         <v>162</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1911</v>
+        <v>0.3068</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612759</v>
+        <v>1610612756</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M40" t="n">
-        <v>0.284</v>
+        <v>0.6359</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612766</v>
+        <v>1610612765</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612756</v>
+        <v>1610612750</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2684,52 +2684,52 @@
         <v>163</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6576</v>
+        <v>0.6361</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612765</v>
+        <v>1610612760</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612750</v>
+        <v>1610612747</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2739,52 +2739,52 @@
         <v>163</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6627</v>
+        <v>0.6634</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2794,52 +2794,52 @@
         <v>163</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6834</v>
+        <v>0.3214</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612739</v>
+        <v>1610612740</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2849,52 +2849,52 @@
         <v>163</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2934</v>
+        <v>0.5967</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2904,107 +2904,107 @@
         <v>163</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6292</v>
+        <v>0.4781</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612754</v>
+        <v>1610612750</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3014,52 +3014,52 @@
         <v>164</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7934</v>
+        <v>0.5244</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612755</v>
+        <v>1610612751</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3069,52 +3069,52 @@
         <v>164</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5361</v>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612751</v>
+        <v>1610612752</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612737</v>
+        <v>1610612741</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3124,52 +3124,52 @@
         <v>164</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2114</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612752</v>
+        <v>1610612745</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612741</v>
+        <v>1610612762</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3179,52 +3179,52 @@
         <v>164</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612745</v>
+        <v>1610612763</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612762</v>
+        <v>1610612761</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3234,52 +3234,52 @@
         <v>164</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8052</v>
+        <v>0.4008</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612761</v>
+        <v>1610612738</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3289,52 +3289,52 @@
         <v>164</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3541</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612738</v>
+        <v>1610612753</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3344,52 +3344,52 @@
         <v>164</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2198</v>
+        <v>0.4012</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612742</v>
+        <v>1610612758</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612753</v>
+        <v>1610612740</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3399,107 +3399,107 @@
         <v>164</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4241</v>
+        <v>0.4345</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612758</v>
+        <v>1610612748</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612740</v>
+        <v>1610612764</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4378</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612748</v>
+        <v>1610612743</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612764</v>
+        <v>1610612759</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3509,52 +3509,52 @@
         <v>165</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8287</v>
+        <v>0.5139</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612743</v>
+        <v>1610612755</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612759</v>
+        <v>1610612765</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3564,107 +3564,107 @@
         <v>165</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5138</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612755</v>
+        <v>1610612738</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3464</v>
+        <v>0.7319</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612738</v>
+        <v>1610612751</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612761</v>
+        <v>1610612764</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3674,52 +3674,52 @@
         <v>166</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7401</v>
+        <v>0.6433</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612764</v>
+        <v>1610612756</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3729,52 +3729,52 @@
         <v>166</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6355</v>
+        <v>0.4289</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612741</v>
+        <v>1610612749</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612756</v>
+        <v>1610612763</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3784,52 +3784,52 @@
         <v>166</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4361</v>
+        <v>0.5584</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612749</v>
+        <v>1610612739</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612763</v>
+        <v>1610612754</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>166</v>
       </c>
       <c r="M62" t="n">
-        <v>0.5982</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612754</v>
+        <v>1610612766</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,52 +3894,52 @@
         <v>166</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.5226</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612750</v>
+        <v>1610612740</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3949,52 +3949,52 @@
         <v>166</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5291</v>
+        <v>0.4792</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612740</v>
+        <v>1610612760</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612753</v>
+        <v>1610612762</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4004,52 +4004,52 @@
         <v>166</v>
       </c>
       <c r="M65" t="n">
-        <v>0.5333</v>
+        <v>0.8585</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612760</v>
+        <v>1610612742</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612762</v>
+        <v>1610612747</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4059,52 +4059,52 @@
         <v>166</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8529</v>
+        <v>0.2669</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612742</v>
+        <v>1610612758</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4114,52 +4114,52 @@
         <v>166</v>
       </c>
       <c r="M67" t="n">
-        <v>0.2345</v>
+        <v>0.2207</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612758</v>
+        <v>1610612744</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4169,107 +4169,107 @@
         <v>166</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2098</v>
+        <v>0.4772</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612744</v>
+        <v>1610612737</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612745</v>
+        <v>1610612752</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4802</v>
+        <v>0.4623</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612737</v>
+        <v>1610612753</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612752</v>
+        <v>1610612765</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4279,52 +4279,52 @@
         <v>167</v>
       </c>
       <c r="M70" t="n">
-        <v>0.494</v>
+        <v>0.3455</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612753</v>
+        <v>1610612763</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612765</v>
+        <v>1610612739</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4334,52 +4334,52 @@
         <v>167</v>
       </c>
       <c r="M71" t="n">
-        <v>0.3734</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612763</v>
+        <v>1610612759</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612739</v>
+        <v>1610612755</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4389,52 +4389,52 @@
         <v>167</v>
       </c>
       <c r="M72" t="n">
-        <v>0.2264</v>
+        <v>0.8098</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612759</v>
+        <v>1610612743</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612755</v>
+        <v>1610612757</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4444,107 +4444,107 @@
         <v>167</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8075</v>
+        <v>0.7847</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612743</v>
+        <v>1610612764</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612757</v>
+        <v>1610612741</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7683</v>
+        <v>0.3922</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612741</v>
+        <v>1610612766</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>168</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3791</v>
+        <v>0.6389</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612738</v>
+        <v>1610612751</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,52 +4609,52 @@
         <v>168</v>
       </c>
       <c r="M76" t="n">
-        <v>0.6566</v>
+        <v>0.4442</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612751</v>
+        <v>1610612761</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4664,52 +4664,52 @@
         <v>168</v>
       </c>
       <c r="M77" t="n">
-        <v>0.4013</v>
+        <v>0.5542</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612761</v>
+        <v>1610612754</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,52 +4719,52 @@
         <v>168</v>
       </c>
       <c r="M78" t="n">
-        <v>0.5633</v>
+        <v>0.2861</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612754</v>
+        <v>1610612740</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612750</v>
+        <v>1610612762</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4774,52 +4774,52 @@
         <v>168</v>
       </c>
       <c r="M79" t="n">
-        <v>0.3053</v>
+        <v>0.7202</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612740</v>
+        <v>1610612744</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4829,52 +4829,52 @@
         <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7199</v>
+        <v>0.7745</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612744</v>
+        <v>1610612747</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612758</v>
+        <v>1610612760</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -4884,52 +4884,52 @@
         <v>168</v>
       </c>
       <c r="M81" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.4092</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612760</v>
+        <v>1610612742</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -4939,52 +4939,52 @@
         <v>168</v>
       </c>
       <c r="M82" t="n">
-        <v>0.4699</v>
+        <v>0.8328</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612746</v>
+        <v>1610612756</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612742</v>
+        <v>1610612745</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4994,107 +4994,107 @@
         <v>168</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8179</v>
+        <v>0.5032</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612756</v>
+        <v>1610612739</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612745</v>
+        <v>1610612737</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K84" t="n">
         <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M84" t="n">
-        <v>0.5381</v>
+        <v>0.6806</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612739</v>
+        <v>1610612753</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612737</v>
+        <v>1610612750</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5104,52 +5104,52 @@
         <v>169</v>
       </c>
       <c r="M85" t="n">
-        <v>0.6782</v>
+        <v>0.5292</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612753</v>
+        <v>1610612765</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612750</v>
+        <v>1610612749</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -5159,52 +5159,52 @@
         <v>169</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5677</v>
+        <v>0.8431</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612765</v>
+        <v>1610612759</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612749</v>
+        <v>1610612757</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -5214,52 +5214,52 @@
         <v>169</v>
       </c>
       <c r="M87" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612759</v>
+        <v>1610612743</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612757</v>
+        <v>1610612763</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -5269,52 +5269,52 @@
         <v>169</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7913</v>
+        <v>0.8542</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612743</v>
+        <v>1610612746</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612763</v>
+        <v>1610612760</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -5324,52 +5324,52 @@
         <v>169</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.4006</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612746</v>
+        <v>1610612756</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612760</v>
+        <v>1610612742</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5379,107 +5379,107 @@
         <v>169</v>
       </c>
       <c r="M90" t="n">
-        <v>0.4253</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612742</v>
+        <v>1610612748</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K91" t="n">
         <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7925</v>
+        <v>0.5542</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612761</v>
+        <v>1610612764</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5489,52 +5489,52 @@
         <v>170</v>
       </c>
       <c r="M92" t="n">
-        <v>0.5633</v>
+        <v>0.3922</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612741</v>
+        <v>1610612754</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5544,52 +5544,52 @@
         <v>170</v>
       </c>
       <c r="M93" t="n">
-        <v>0.3791</v>
+        <v>0.4921</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612751</v>
+        <v>1610612752</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612754</v>
+        <v>1610612738</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5599,52 +5599,52 @@
         <v>170</v>
       </c>
       <c r="M94" t="n">
-        <v>0.481</v>
+        <v>0.5389</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612752</v>
+        <v>1610612745</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612738</v>
+        <v>1610612755</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5654,52 +5654,52 @@
         <v>170</v>
       </c>
       <c r="M95" t="n">
-        <v>0.5671</v>
+        <v>0.6594</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612745</v>
+        <v>1610612744</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612755</v>
+        <v>1610612747</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -5709,107 +5709,107 @@
         <v>170</v>
       </c>
       <c r="M96" t="n">
-        <v>0.6908</v>
+        <v>0.4157</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M97" t="n">
-        <v>0.3218</v>
+        <v>0.5002</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612766</v>
+        <v>1610612764</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612765</v>
+        <v>1610612748</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5819,52 +5819,52 @@
         <v>171</v>
       </c>
       <c r="M98" t="n">
-        <v>0.5411</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612764</v>
+        <v>1610612737</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612748</v>
+        <v>1610612739</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5874,52 +5874,52 @@
         <v>171</v>
       </c>
       <c r="M99" t="n">
-        <v>0.2611</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612737</v>
+        <v>1610612738</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612739</v>
+        <v>1610612740</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -5929,52 +5929,52 @@
         <v>171</v>
       </c>
       <c r="M100" t="n">
-        <v>0.4489</v>
+        <v>0.7697000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612740</v>
+        <v>1610612755</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5984,52 +5984,52 @@
         <v>171</v>
       </c>
       <c r="M101" t="n">
-        <v>0.7764</v>
+        <v>0.3737</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612754</v>
+        <v>1610612752</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6039,52 +6039,52 @@
         <v>171</v>
       </c>
       <c r="M102" t="n">
-        <v>0.3809</v>
+        <v>0.6967</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612752</v>
+        <v>1610612741</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6094,52 +6094,52 @@
         <v>171</v>
       </c>
       <c r="M103" t="n">
-        <v>0.7462</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612741</v>
+        <v>1610612745</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612753</v>
+        <v>1610612750</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -6149,52 +6149,52 @@
         <v>171</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4395</v>
+        <v>0.5151</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612750</v>
+        <v>1610612751</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -6204,52 +6204,52 @@
         <v>171</v>
       </c>
       <c r="M105" t="n">
-        <v>0.5326</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612749</v>
+        <v>1610612759</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612751</v>
+        <v>1610612742</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -6259,52 +6259,52 @@
         <v>171</v>
       </c>
       <c r="M106" t="n">
-        <v>0.7695</v>
+        <v>0.8448</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612759</v>
+        <v>1610612762</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -6314,52 +6314,52 @@
         <v>171</v>
       </c>
       <c r="M107" t="n">
-        <v>0.842</v>
+        <v>0.4769</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612762</v>
+        <v>1610612743</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612763</v>
+        <v>1610612760</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -6369,52 +6369,52 @@
         <v>171</v>
       </c>
       <c r="M108" t="n">
-        <v>0.5192</v>
+        <v>0.4585</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612743</v>
+        <v>1610612757</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -6424,52 +6424,52 @@
         <v>171</v>
       </c>
       <c r="M109" t="n">
-        <v>0.4911</v>
+        <v>0.4628</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612757</v>
+        <v>1610612758</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612746</v>
+        <v>1610612744</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -6479,52 +6479,52 @@
         <v>171</v>
       </c>
       <c r="M110" t="n">
-        <v>0.3833</v>
+        <v>0.3913</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612758</v>
+        <v>1610612747</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -6534,107 +6534,107 @@
         <v>171</v>
       </c>
       <c r="M111" t="n">
-        <v>0.3668</v>
+        <v>0.6859</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612747</v>
+        <v>1610612738</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K112" t="n">
         <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M112" t="n">
-        <v>0.6471</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C113" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="D113" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -6644,52 +6644,52 @@
         <v>173</v>
       </c>
       <c r="M113" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.8507</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B114" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C114" t="n">
-        <v>1610612739</v>
+        <v>1610612754</v>
       </c>
       <c r="D114" t="n">
-        <v>1610612764</v>
+        <v>1610612765</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -6699,52 +6699,52 @@
         <v>173</v>
       </c>
       <c r="M114" t="n">
-        <v>0.8581</v>
+        <v>0.2519</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B115" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C115" t="n">
-        <v>1610612754</v>
+        <v>1610612748</v>
       </c>
       <c r="D115" t="n">
-        <v>1610612765</v>
+        <v>1610612737</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -6754,52 +6754,52 @@
         <v>173</v>
       </c>
       <c r="M115" t="n">
-        <v>0.2596</v>
+        <v>0.5317</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B116" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C116" t="n">
-        <v>1610612748</v>
+        <v>1610612752</v>
       </c>
       <c r="D116" t="n">
-        <v>1610612737</v>
+        <v>1610612766</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -6809,52 +6809,52 @@
         <v>173</v>
       </c>
       <c r="M116" t="n">
-        <v>0.5402</v>
+        <v>0.6147</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B117" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C117" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="D117" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -6864,52 +6864,52 @@
         <v>173</v>
       </c>
       <c r="M117" t="n">
-        <v>0.6506</v>
+        <v>0.7186</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C118" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="D118" t="n">
-        <v>1610612749</v>
+        <v>1610612751</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -6919,52 +6919,52 @@
         <v>173</v>
       </c>
       <c r="M118" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.8367</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C119" t="n">
-        <v>1610612761</v>
+        <v>1610612742</v>
       </c>
       <c r="D119" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -6974,52 +6974,52 @@
         <v>173</v>
       </c>
       <c r="M119" t="n">
-        <v>0.8308</v>
+        <v>0.5106000000000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C120" t="n">
-        <v>1610612742</v>
+        <v>1610612745</v>
       </c>
       <c r="D120" t="n">
-        <v>1610612741</v>
+        <v>1610612763</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -7029,52 +7029,52 @@
         <v>173</v>
       </c>
       <c r="M120" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C121" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="D121" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -7084,52 +7084,52 @@
         <v>173</v>
       </c>
       <c r="M121" t="n">
-        <v>0.7893</v>
+        <v>0.6766</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0022501195</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B122" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C122" t="n">
-        <v>1610612750</v>
+        <v>1610612760</v>
       </c>
       <c r="D122" t="n">
-        <v>1610612740</v>
+        <v>1610612756</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -7139,52 +7139,52 @@
         <v>173</v>
       </c>
       <c r="M122" t="n">
-        <v>0.6784</v>
+        <v>0.8016</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0022501196</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C123" t="n">
-        <v>1610612760</v>
+        <v>1610612759</v>
       </c>
       <c r="D123" t="n">
-        <v>1610612756</v>
+        <v>1610612743</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -7194,52 +7194,52 @@
         <v>173</v>
       </c>
       <c r="M123" t="n">
-        <v>0.8028</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0022501197</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B124" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C124" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="D124" t="n">
-        <v>1610612743</v>
+        <v>1610612762</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -7249,52 +7249,52 @@
         <v>173</v>
       </c>
       <c r="M124" t="n">
-        <v>0.6308</v>
+        <v>0.8632</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0022501198</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B125" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C125" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D125" t="n">
-        <v>1610612762</v>
+        <v>1610612744</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -7304,52 +7304,52 @@
         <v>173</v>
       </c>
       <c r="M125" t="n">
-        <v>0.8555</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0022501199</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B126" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C126" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="D126" t="n">
-        <v>1610612744</v>
+        <v>1610612758</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -7359,62 +7359,7 @@
         <v>173</v>
       </c>
       <c r="M126" t="n">
-        <v>0.6995</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C127" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D127" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K127" t="n">
-        <v>1</v>
-      </c>
-      <c r="L127" t="n">
-        <v>173</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0.7832</v>
+        <v>0.7618</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,321 +490,321 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501077</t>
+          <t>0022501082</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612755</v>
+        <v>1610612746</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7002</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501078</t>
+          <t>0022501083</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612737</v>
+        <v>1610612754</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612758</v>
+        <v>1610612748</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8048</v>
+        <v>0.3099</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501079</t>
+          <t>0022501084</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612763</v>
+        <v>1610612751</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612741</v>
+        <v>1610612758</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5364</v>
+        <v>0.5745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501080</t>
+          <t>0022501085</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612750</v>
+        <v>1610612766</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612765</v>
+        <v>1610612738</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4666</v>
+        <v>0.4223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501081</t>
+          <t>0022501086</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612762</v>
+        <v>1610612753</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8405</v>
+        <v>0.5797</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501082</t>
+          <t>0022501087</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612749</v>
+        <v>1610612757</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612746</v>
+        <v>1610612764</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -814,52 +814,52 @@
         <v>159</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2904</v>
+        <v>0.8162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501083</t>
+          <t>0022501088</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612754</v>
+        <v>1610612740</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612748</v>
+        <v>1610612745</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -869,52 +869,52 @@
         <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2945</v>
+        <v>0.4008</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501084</t>
+          <t>0022501089</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612751</v>
+        <v>1610612760</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612758</v>
+        <v>1610612752</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -924,52 +924,52 @@
         <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5712</v>
+        <v>0.6483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501085</t>
+          <t>0022501090</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612766</v>
+        <v>1610612743</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612738</v>
+        <v>1610612744</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -979,327 +979,327 @@
         <v>159</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4393</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501086</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612761</v>
+        <v>1610612748</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5797</v>
+        <v>0.5093</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501087</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612757</v>
+        <v>1610612737</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7866</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501088</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612745</v>
+        <v>1610612756</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4008</v>
+        <v>0.3759</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501089</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612760</v>
+        <v>1610612759</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612752</v>
+        <v>1610612741</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6483</v>
+        <v>0.8197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612743</v>
+        <v>1610612742</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612744</v>
+        <v>1610612750</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7782</v>
+        <v>0.3128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612748</v>
+        <v>1610612762</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612755</v>
+        <v>1610612739</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1309,52 +1309,52 @@
         <v>160</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5854</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612737</v>
+        <v>1610612760</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1364,52 +1364,52 @@
         <v>160</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5133</v>
+        <v>0.6687</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612763</v>
+        <v>1610612747</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612756</v>
+        <v>1610612764</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1419,327 +1419,327 @@
         <v>160</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4106</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612759</v>
+        <v>1610612749</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612741</v>
+        <v>1610612742</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8335</v>
+        <v>0.6137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612742</v>
+        <v>1610612753</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612750</v>
+        <v>1610612756</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3235</v>
+        <v>0.5554</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612762</v>
+        <v>1610612751</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612739</v>
+        <v>1610612766</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2091</v>
+        <v>0.2188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612760</v>
+        <v>1610612765</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6854</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612747</v>
+        <v>1610612745</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612764</v>
+        <v>1610612752</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8944</v>
+        <v>0.4687</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612749</v>
+        <v>1610612747</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612742</v>
+        <v>1610612739</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1749,52 +1749,52 @@
         <v>161</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6262</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612753</v>
+        <v>1610612746</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612756</v>
+        <v>1610612757</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1804,327 +1804,327 @@
         <v>161</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5749</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2107</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6091</v>
+        <v>0.2535</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612745</v>
+        <v>1610612748</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4662</v>
+        <v>0.4208</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612747</v>
+        <v>1610612753</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612739</v>
+        <v>1610612737</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M29" t="n">
-        <v>0.538</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612746</v>
+        <v>1610612761</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612757</v>
+        <v>1610612758</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7815</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612763</v>
+        <v>1610612741</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612752</v>
+        <v>1610612754</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2134,52 +2134,52 @@
         <v>162</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2956</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612755</v>
+        <v>1610612749</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2189,52 +2189,52 @@
         <v>162</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3048</v>
+        <v>0.8287</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612748</v>
+        <v>1610612762</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2244,52 +2244,52 @@
         <v>162</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4274</v>
+        <v>0.1962</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612753</v>
+        <v>1610612744</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612737</v>
+        <v>1610612759</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2299,327 +2299,327 @@
         <v>162</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4251</v>
+        <v>0.3009</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612758</v>
+        <v>1610612756</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7835</v>
+        <v>0.6156</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612754</v>
+        <v>1610612750</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6858</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612745</v>
+        <v>1610612760</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612749</v>
+        <v>1610612747</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8166</v>
+        <v>0.6634</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612762</v>
+        <v>1610612744</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1992</v>
+        <v>0.3234</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612759</v>
+        <v>1610612740</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3068</v>
+        <v>0.6024</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612766</v>
+        <v>1610612746</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612756</v>
+        <v>1610612759</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2629,327 +2629,327 @@
         <v>163</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6359</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612750</v>
+        <v>1610612754</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6361</v>
+        <v>0.7944</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612760</v>
+        <v>1610612755</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612747</v>
+        <v>1610612750</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6634</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612744</v>
+        <v>1610612751</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612739</v>
+        <v>1610612737</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3214</v>
+        <v>0.2307</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612757</v>
+        <v>1610612752</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612740</v>
+        <v>1610612741</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5967</v>
+        <v>0.7827</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612759</v>
+        <v>1610612762</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4781</v>
+        <v>0.8136</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612766</v>
+        <v>1610612763</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612754</v>
+        <v>1610612761</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2959,52 +2959,52 @@
         <v>164</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7948</v>
+        <v>0.3788</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612755</v>
+        <v>1610612749</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612750</v>
+        <v>1610612738</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3014,52 +3014,52 @@
         <v>164</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5244</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612751</v>
+        <v>1610612742</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612737</v>
+        <v>1610612753</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3069,52 +3069,52 @@
         <v>164</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2303</v>
+        <v>0.4012</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612752</v>
+        <v>1610612758</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3124,492 +3124,492 @@
         <v>164</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8113</v>
+        <v>0.4378</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612745</v>
+        <v>1610612748</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612762</v>
+        <v>1610612764</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8373</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612763</v>
+        <v>1610612743</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4008</v>
+        <v>0.5067</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612749</v>
+        <v>1610612755</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2155</v>
+        <v>0.3823</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612742</v>
+        <v>1610612738</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4012</v>
+        <v>0.7321</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612758</v>
+        <v>1610612751</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612740</v>
+        <v>1610612764</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4345</v>
+        <v>0.6501</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612764</v>
+        <v>1610612756</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M55" t="n">
-        <v>0.836</v>
+        <v>0.4565</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612743</v>
+        <v>1610612749</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612759</v>
+        <v>1610612763</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5139</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612755</v>
+        <v>1610612739</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612765</v>
+        <v>1610612754</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M57" t="n">
-        <v>0.322</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612738</v>
+        <v>1610612750</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3619,52 +3619,52 @@
         <v>166</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7319</v>
+        <v>0.5512</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612751</v>
+        <v>1610612740</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612764</v>
+        <v>1610612753</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3674,52 +3674,52 @@
         <v>166</v>
       </c>
       <c r="M59" t="n">
-        <v>0.6433</v>
+        <v>0.4814</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612741</v>
+        <v>1610612760</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612756</v>
+        <v>1610612762</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3729,52 +3729,52 @@
         <v>166</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4289</v>
+        <v>0.8577</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612763</v>
+        <v>1610612747</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3784,52 +3784,52 @@
         <v>166</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5584</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612739</v>
+        <v>1610612758</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612754</v>
+        <v>1610612746</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>166</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8439</v>
+        <v>0.2239</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612750</v>
+        <v>1610612744</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,602 +3894,602 @@
         <v>166</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5226</v>
+        <v>0.4772</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612740</v>
+        <v>1610612737</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612753</v>
+        <v>1610612752</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4792</v>
+        <v>0.4702</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612760</v>
+        <v>1610612753</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612762</v>
+        <v>1610612765</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8585</v>
+        <v>0.3428</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M66" t="n">
-        <v>0.2669</v>
+        <v>0.2153</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612758</v>
+        <v>1610612759</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612746</v>
+        <v>1610612755</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M67" t="n">
-        <v>0.2207</v>
+        <v>0.7627</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612744</v>
+        <v>1610612743</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612745</v>
+        <v>1610612757</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4772</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612737</v>
+        <v>1610612764</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612752</v>
+        <v>1610612741</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4623</v>
+        <v>0.3662</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612753</v>
+        <v>1610612738</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M70" t="n">
-        <v>0.3455</v>
+        <v>0.6591</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612763</v>
+        <v>1610612751</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612739</v>
+        <v>1610612749</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M71" t="n">
-        <v>0.233</v>
+        <v>0.4785</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M72" t="n">
-        <v>0.8098</v>
+        <v>0.5644</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612743</v>
+        <v>1610612754</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612757</v>
+        <v>1610612750</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7847</v>
+        <v>0.2637</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612764</v>
+        <v>1610612740</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612741</v>
+        <v>1610612762</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4499,52 +4499,52 @@
         <v>168</v>
       </c>
       <c r="M74" t="n">
-        <v>0.3922</v>
+        <v>0.7248</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612738</v>
+        <v>1610612744</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612766</v>
+        <v>1610612758</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>168</v>
       </c>
       <c r="M75" t="n">
-        <v>0.6389</v>
+        <v>0.7687</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612751</v>
+        <v>1610612747</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612749</v>
+        <v>1610612760</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,52 +4609,52 @@
         <v>168</v>
       </c>
       <c r="M76" t="n">
-        <v>0.4442</v>
+        <v>0.4092</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612761</v>
+        <v>1610612746</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612748</v>
+        <v>1610612742</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4664,52 +4664,52 @@
         <v>168</v>
       </c>
       <c r="M77" t="n">
-        <v>0.5542</v>
+        <v>0.8328</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612754</v>
+        <v>1610612756</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,327 +4719,327 @@
         <v>168</v>
       </c>
       <c r="M78" t="n">
-        <v>0.2861</v>
+        <v>0.5189</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612740</v>
+        <v>1610612739</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612762</v>
+        <v>1610612737</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M79" t="n">
-        <v>0.7202</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612758</v>
+        <v>1610612750</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7745</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612760</v>
+        <v>1610612749</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4092</v>
+        <v>0.8595</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612746</v>
+        <v>1610612759</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612742</v>
+        <v>1610612757</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M82" t="n">
-        <v>0.8328</v>
+        <v>0.7762</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612756</v>
+        <v>1610612743</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612745</v>
+        <v>1610612763</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M83" t="n">
-        <v>0.5032</v>
+        <v>0.8602</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612739</v>
+        <v>1610612746</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612737</v>
+        <v>1610612760</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5049,52 +5049,52 @@
         <v>169</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6806</v>
+        <v>0.4046</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612753</v>
+        <v>1610612756</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612750</v>
+        <v>1610612742</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5104,327 +5104,327 @@
         <v>169</v>
       </c>
       <c r="M85" t="n">
-        <v>0.5292</v>
+        <v>0.7984</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8431</v>
+        <v>0.5644</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612759</v>
+        <v>1610612764</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612757</v>
+        <v>1610612741</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M87" t="n">
-        <v>0.7941</v>
+        <v>0.3662</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612763</v>
+        <v>1610612754</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K88" t="n">
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M88" t="n">
-        <v>0.8542</v>
+        <v>0.4921</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612746</v>
+        <v>1610612752</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612760</v>
+        <v>1610612738</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M89" t="n">
-        <v>0.4006</v>
+        <v>0.5417</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612756</v>
+        <v>1610612745</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612742</v>
+        <v>1610612755</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M90" t="n">
-        <v>0.7889</v>
+        <v>0.6114000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612761</v>
+        <v>1610612744</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612748</v>
+        <v>1610612747</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5434,327 +5434,327 @@
         <v>170</v>
       </c>
       <c r="M91" t="n">
-        <v>0.5542</v>
+        <v>0.4157</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M92" t="n">
-        <v>0.3922</v>
+        <v>0.4859</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612754</v>
+        <v>1610612748</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K93" t="n">
         <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M93" t="n">
-        <v>0.4921</v>
+        <v>0.2567</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612752</v>
+        <v>1610612737</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5389</v>
+        <v>0.4788</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612745</v>
+        <v>1610612738</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612755</v>
+        <v>1610612740</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M95" t="n">
-        <v>0.6594</v>
+        <v>0.7697000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612744</v>
+        <v>1610612754</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M96" t="n">
-        <v>0.4157</v>
+        <v>0.3294</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5764,52 +5764,52 @@
         <v>171</v>
       </c>
       <c r="M97" t="n">
-        <v>0.5002</v>
+        <v>0.6948</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612764</v>
+        <v>1610612741</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5819,52 +5819,52 @@
         <v>171</v>
       </c>
       <c r="M98" t="n">
-        <v>0.2605</v>
+        <v>0.4491</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612737</v>
+        <v>1610612745</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5874,52 +5874,52 @@
         <v>171</v>
       </c>
       <c r="M99" t="n">
-        <v>0.473</v>
+        <v>0.4931</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612738</v>
+        <v>1610612749</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612740</v>
+        <v>1610612751</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -5929,52 +5929,52 @@
         <v>171</v>
       </c>
       <c r="M100" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612754</v>
+        <v>1610612759</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612755</v>
+        <v>1610612742</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5984,52 +5984,52 @@
         <v>171</v>
       </c>
       <c r="M101" t="n">
-        <v>0.3737</v>
+        <v>0.8444</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612752</v>
+        <v>1610612762</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612761</v>
+        <v>1610612763</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6039,52 +6039,52 @@
         <v>171</v>
       </c>
       <c r="M102" t="n">
-        <v>0.6967</v>
+        <v>0.4947</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612741</v>
+        <v>1610612743</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612753</v>
+        <v>1610612760</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6094,52 +6094,52 @@
         <v>171</v>
       </c>
       <c r="M103" t="n">
-        <v>0.414</v>
+        <v>0.4585</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612745</v>
+        <v>1610612757</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612750</v>
+        <v>1610612746</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -6149,52 +6149,52 @@
         <v>171</v>
       </c>
       <c r="M104" t="n">
-        <v>0.5151</v>
+        <v>0.4754</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612749</v>
+        <v>1610612758</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612751</v>
+        <v>1610612744</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -6204,52 +6204,52 @@
         <v>171</v>
       </c>
       <c r="M105" t="n">
-        <v>0.768</v>
+        <v>0.3931</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612742</v>
+        <v>1610612756</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -6259,327 +6259,327 @@
         <v>171</v>
       </c>
       <c r="M106" t="n">
-        <v>0.8448</v>
+        <v>0.6736</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612762</v>
+        <v>1610612738</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612763</v>
+        <v>1610612753</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K107" t="n">
         <v>1</v>
       </c>
       <c r="L107" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M107" t="n">
-        <v>0.4769</v>
+        <v>0.7917</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612760</v>
+        <v>1610612764</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K108" t="n">
         <v>1</v>
       </c>
       <c r="L108" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M108" t="n">
-        <v>0.4585</v>
+        <v>0.8507</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612757</v>
+        <v>1610612754</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612746</v>
+        <v>1610612765</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K109" t="n">
         <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M109" t="n">
-        <v>0.4628</v>
+        <v>0.2515</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612758</v>
+        <v>1610612748</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612744</v>
+        <v>1610612737</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K110" t="n">
         <v>1</v>
       </c>
       <c r="L110" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M110" t="n">
-        <v>0.3913</v>
+        <v>0.5239</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612747</v>
+        <v>1610612752</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K111" t="n">
         <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M111" t="n">
-        <v>0.6859</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612738</v>
+        <v>1610612755</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612753</v>
+        <v>1610612749</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -6589,52 +6589,52 @@
         <v>173</v>
       </c>
       <c r="M112" t="n">
-        <v>0.795</v>
+        <v>0.7667</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C113" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="D113" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -6644,52 +6644,52 @@
         <v>173</v>
       </c>
       <c r="M113" t="n">
-        <v>0.8507</v>
+        <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B114" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C114" t="n">
-        <v>1610612754</v>
+        <v>1610612742</v>
       </c>
       <c r="D114" t="n">
-        <v>1610612765</v>
+        <v>1610612741</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -6699,52 +6699,52 @@
         <v>173</v>
       </c>
       <c r="M114" t="n">
-        <v>0.2519</v>
+        <v>0.4967</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B115" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C115" t="n">
-        <v>1610612748</v>
+        <v>1610612745</v>
       </c>
       <c r="D115" t="n">
-        <v>1610612737</v>
+        <v>1610612763</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -6754,52 +6754,52 @@
         <v>173</v>
       </c>
       <c r="M115" t="n">
-        <v>0.5317</v>
+        <v>0.8174</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B116" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C116" t="n">
-        <v>1610612752</v>
+        <v>1610612750</v>
       </c>
       <c r="D116" t="n">
-        <v>1610612766</v>
+        <v>1610612740</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -6809,52 +6809,52 @@
         <v>173</v>
       </c>
       <c r="M116" t="n">
-        <v>0.6147</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B117" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C117" t="n">
-        <v>1610612755</v>
+        <v>1610612760</v>
       </c>
       <c r="D117" t="n">
-        <v>1610612749</v>
+        <v>1610612756</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -6864,52 +6864,52 @@
         <v>173</v>
       </c>
       <c r="M117" t="n">
-        <v>0.7186</v>
+        <v>0.7991</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C118" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="D118" t="n">
-        <v>1610612751</v>
+        <v>1610612743</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -6919,52 +6919,52 @@
         <v>173</v>
       </c>
       <c r="M118" t="n">
-        <v>0.8367</v>
+        <v>0.6246</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C119" t="n">
-        <v>1610612742</v>
+        <v>1610612747</v>
       </c>
       <c r="D119" t="n">
-        <v>1610612741</v>
+        <v>1610612762</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -6974,52 +6974,52 @@
         <v>173</v>
       </c>
       <c r="M119" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C120" t="n">
-        <v>1610612745</v>
+        <v>1610612746</v>
       </c>
       <c r="D120" t="n">
-        <v>1610612763</v>
+        <v>1610612744</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -7029,52 +7029,52 @@
         <v>173</v>
       </c>
       <c r="M120" t="n">
-        <v>0.7889</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0022501195</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C121" t="n">
-        <v>1610612750</v>
+        <v>1610612757</v>
       </c>
       <c r="D121" t="n">
-        <v>1610612740</v>
+        <v>1610612758</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -7084,282 +7084,7 @@
         <v>173</v>
       </c>
       <c r="M121" t="n">
-        <v>0.6766</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C122" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D122" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K122" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" t="n">
-        <v>173</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0.8016</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C123" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D123" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" t="n">
-        <v>173</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C124" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D124" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K124" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" t="n">
-        <v>173</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0.8632</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C125" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D125" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K125" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" t="n">
-        <v>173</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0.7355</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C126" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D126" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K126" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" t="n">
-        <v>173</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0.7618</v>
+        <v>0.774</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -539,7 +539,7 @@
         <v>159</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2477</v>
+        <v>0.2598</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>159</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3099</v>
+        <v>0.3066</v>
       </c>
     </row>
     <row r="4">
@@ -649,7 +649,7 @@
         <v>159</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5745</v>
+        <v>0.5825</v>
       </c>
     </row>
     <row r="5">
@@ -704,7 +704,7 @@
         <v>159</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4223</v>
+        <v>0.4334</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         <v>159</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5797</v>
+        <v>0.5864</v>
       </c>
     </row>
     <row r="7">
@@ -814,7 +814,7 @@
         <v>159</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8162</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="8">
@@ -869,7 +869,7 @@
         <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4008</v>
+        <v>0.3947</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
         <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6483</v>
+        <v>0.6499</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>159</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7766</v>
+        <v>0.7782</v>
       </c>
     </row>
     <row r="11">
@@ -1034,7 +1034,7 @@
         <v>160</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5093</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="12">
@@ -1089,7 +1089,7 @@
         <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>0.525</v>
+        <v>0.5179</v>
       </c>
     </row>
     <row r="13">
@@ -1144,7 +1144,7 @@
         <v>160</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3759</v>
+        <v>0.3766</v>
       </c>
     </row>
     <row r="14">
@@ -1199,7 +1199,7 @@
         <v>160</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8197</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="15">
@@ -1254,7 +1254,7 @@
         <v>160</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3128</v>
+        <v>0.3123</v>
       </c>
     </row>
     <row r="16">
@@ -1364,7 +1364,7 @@
         <v>160</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6687</v>
+        <v>0.6788</v>
       </c>
     </row>
     <row r="18">
@@ -1529,7 +1529,7 @@
         <v>161</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5554</v>
+        <v>0.5538999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1584,7 +1584,7 @@
         <v>161</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2188</v>
+        <v>0.2238</v>
       </c>
     </row>
     <row r="22">
@@ -1694,7 +1694,7 @@
         <v>161</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4687</v>
+        <v>0.4677</v>
       </c>
     </row>
     <row r="24">
@@ -1749,7 +1749,7 @@
         <v>161</v>
       </c>
       <c r="M24" t="n">
-        <v>0.538</v>
+        <v>0.5459000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1804,7 +1804,7 @@
         <v>161</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7191</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1914,7 +1914,7 @@
         <v>162</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2535</v>
+        <v>0.2549</v>
       </c>
     </row>
     <row r="28">
@@ -1969,7 +1969,7 @@
         <v>162</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4208</v>
+        <v>0.4293</v>
       </c>
     </row>
     <row r="29">
@@ -2024,7 +2024,7 @@
         <v>162</v>
       </c>
       <c r="M29" t="n">
-        <v>0.417</v>
+        <v>0.4434</v>
       </c>
     </row>
     <row r="30">
@@ -2079,7 +2079,7 @@
         <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7815</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="31">
@@ -2134,7 +2134,7 @@
         <v>162</v>
       </c>
       <c r="M31" t="n">
-        <v>0.715</v>
+        <v>0.6631</v>
       </c>
     </row>
     <row r="32">
@@ -2189,7 +2189,7 @@
         <v>162</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8287</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="33">
@@ -2244,7 +2244,7 @@
         <v>162</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1962</v>
+        <v>0.1929</v>
       </c>
     </row>
     <row r="34">
@@ -2299,7 +2299,7 @@
         <v>162</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3009</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
@@ -2354,7 +2354,7 @@
         <v>163</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6156</v>
+        <v>0.6207</v>
       </c>
     </row>
     <row r="36">
@@ -2409,7 +2409,7 @@
         <v>163</v>
       </c>
       <c r="M36" t="n">
-        <v>0.641</v>
+        <v>0.6397</v>
       </c>
     </row>
     <row r="37">
@@ -2464,7 +2464,7 @@
         <v>163</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6634</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="38">
@@ -2574,7 +2574,7 @@
         <v>163</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6024</v>
+        <v>0.6096</v>
       </c>
     </row>
     <row r="40">
@@ -2629,7 +2629,7 @@
         <v>163</v>
       </c>
       <c r="M40" t="n">
-        <v>0.476</v>
+        <v>0.4429</v>
       </c>
     </row>
     <row r="41">
@@ -2684,7 +2684,7 @@
         <v>164</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7944</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="42">
@@ -2794,7 +2794,7 @@
         <v>164</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2307</v>
+        <v>0.2462</v>
       </c>
     </row>
     <row r="44">
@@ -2849,7 +2849,7 @@
         <v>164</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7827</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2904,7 +2904,7 @@
         <v>164</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8136</v>
+        <v>0.8202</v>
       </c>
     </row>
     <row r="46">
@@ -2959,7 +2959,7 @@
         <v>164</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3788</v>
+        <v>0.3825</v>
       </c>
     </row>
     <row r="47">
@@ -3014,7 +3014,7 @@
         <v>164</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2124</v>
+        <v>0.2161</v>
       </c>
     </row>
     <row r="48">
@@ -3069,7 +3069,7 @@
         <v>164</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4012</v>
+        <v>0.4008</v>
       </c>
     </row>
     <row r="49">
@@ -3124,7 +3124,7 @@
         <v>164</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4378</v>
+        <v>0.4345</v>
       </c>
     </row>
     <row r="50">
@@ -3179,7 +3179,7 @@
         <v>165</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8373</v>
+        <v>0.8337</v>
       </c>
     </row>
     <row r="51">
@@ -3234,7 +3234,7 @@
         <v>165</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5067</v>
+        <v>0.5095</v>
       </c>
     </row>
     <row r="52">
@@ -3289,7 +3289,7 @@
         <v>165</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3823</v>
+        <v>0.3806</v>
       </c>
     </row>
     <row r="53">
@@ -3344,7 +3344,7 @@
         <v>166</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7321</v>
+        <v>0.7138</v>
       </c>
     </row>
     <row r="54">
@@ -3454,7 +3454,7 @@
         <v>166</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4565</v>
+        <v>0.4142</v>
       </c>
     </row>
     <row r="56">
@@ -3509,7 +3509,7 @@
         <v>166</v>
       </c>
       <c r="M56" t="n">
-        <v>0.554</v>
+        <v>0.5484</v>
       </c>
     </row>
     <row r="57">
@@ -3619,7 +3619,7 @@
         <v>166</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5512</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="59">
@@ -3674,7 +3674,7 @@
         <v>166</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4814</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="60">
@@ -3729,7 +3729,7 @@
         <v>166</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8577</v>
+        <v>0.8588</v>
       </c>
     </row>
     <row r="61">
@@ -3784,7 +3784,7 @@
         <v>166</v>
       </c>
       <c r="M61" t="n">
-        <v>0.27</v>
+        <v>0.2633</v>
       </c>
     </row>
     <row r="62">
@@ -3839,7 +3839,7 @@
         <v>166</v>
       </c>
       <c r="M62" t="n">
-        <v>0.2239</v>
+        <v>0.2402</v>
       </c>
     </row>
     <row r="63">
@@ -3949,7 +3949,7 @@
         <v>167</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4702</v>
+        <v>0.4442</v>
       </c>
     </row>
     <row r="65">
@@ -4004,7 +4004,7 @@
         <v>167</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3428</v>
+        <v>0.3424</v>
       </c>
     </row>
     <row r="66">
@@ -4059,7 +4059,7 @@
         <v>167</v>
       </c>
       <c r="M66" t="n">
-        <v>0.2153</v>
+        <v>0.2191</v>
       </c>
     </row>
     <row r="67">
@@ -4114,7 +4114,7 @@
         <v>167</v>
       </c>
       <c r="M67" t="n">
-        <v>0.7627</v>
+        <v>0.7645</v>
       </c>
     </row>
     <row r="68">
@@ -4169,7 +4169,7 @@
         <v>167</v>
       </c>
       <c r="M68" t="n">
-        <v>0.774</v>
+        <v>0.7824</v>
       </c>
     </row>
     <row r="69">
@@ -4224,7 +4224,7 @@
         <v>168</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3662</v>
+        <v>0.4057</v>
       </c>
     </row>
     <row r="70">
@@ -4279,7 +4279,7 @@
         <v>168</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6591</v>
+        <v>0.6338</v>
       </c>
     </row>
     <row r="71">
@@ -4334,7 +4334,7 @@
         <v>168</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4785</v>
+        <v>0.4837</v>
       </c>
     </row>
     <row r="72">
@@ -4444,7 +4444,7 @@
         <v>168</v>
       </c>
       <c r="M73" t="n">
-        <v>0.2637</v>
+        <v>0.2619</v>
       </c>
     </row>
     <row r="74">
@@ -4499,7 +4499,7 @@
         <v>168</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7248</v>
+        <v>0.7343</v>
       </c>
     </row>
     <row r="75">
@@ -4554,7 +4554,7 @@
         <v>168</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7687</v>
+        <v>0.7741</v>
       </c>
     </row>
     <row r="76">
@@ -4609,7 +4609,7 @@
         <v>168</v>
       </c>
       <c r="M76" t="n">
-        <v>0.4092</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="77">
@@ -4664,7 +4664,7 @@
         <v>168</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8328</v>
+        <v>0.8246</v>
       </c>
     </row>
     <row r="78">
@@ -4774,7 +4774,7 @@
         <v>169</v>
       </c>
       <c r="M79" t="n">
-        <v>0.665</v>
+        <v>0.6939</v>
       </c>
     </row>
     <row r="80">
@@ -4829,7 +4829,7 @@
         <v>169</v>
       </c>
       <c r="M80" t="n">
-        <v>0.5336</v>
+        <v>0.5328000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -4884,7 +4884,7 @@
         <v>169</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8595</v>
+        <v>0.8629</v>
       </c>
     </row>
     <row r="82">
@@ -4939,7 +4939,7 @@
         <v>169</v>
       </c>
       <c r="M82" t="n">
-        <v>0.7762</v>
+        <v>0.7829</v>
       </c>
     </row>
     <row r="83">
@@ -5049,7 +5049,7 @@
         <v>169</v>
       </c>
       <c r="M84" t="n">
-        <v>0.4046</v>
+        <v>0.3794</v>
       </c>
     </row>
     <row r="85">
@@ -5104,7 +5104,7 @@
         <v>169</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7984</v>
+        <v>0.7991</v>
       </c>
     </row>
     <row r="86">
@@ -5214,7 +5214,7 @@
         <v>170</v>
       </c>
       <c r="M87" t="n">
-        <v>0.3662</v>
+        <v>0.4057</v>
       </c>
     </row>
     <row r="88">
@@ -5269,7 +5269,7 @@
         <v>170</v>
       </c>
       <c r="M88" t="n">
-        <v>0.4921</v>
+        <v>0.4987</v>
       </c>
     </row>
     <row r="89">
@@ -5324,7 +5324,7 @@
         <v>170</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5417</v>
+        <v>0.5508999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5379,7 +5379,7 @@
         <v>170</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6111</v>
       </c>
     </row>
     <row r="91">
@@ -5434,7 +5434,7 @@
         <v>170</v>
       </c>
       <c r="M91" t="n">
-        <v>0.4157</v>
+        <v>0.4113</v>
       </c>
     </row>
     <row r="92">
@@ -5489,7 +5489,7 @@
         <v>171</v>
       </c>
       <c r="M92" t="n">
-        <v>0.4859</v>
+        <v>0.4851</v>
       </c>
     </row>
     <row r="93">
@@ -5544,7 +5544,7 @@
         <v>171</v>
       </c>
       <c r="M93" t="n">
-        <v>0.2567</v>
+        <v>0.2695</v>
       </c>
     </row>
     <row r="94">
@@ -5599,7 +5599,7 @@
         <v>171</v>
       </c>
       <c r="M94" t="n">
-        <v>0.4788</v>
+        <v>0.4635</v>
       </c>
     </row>
     <row r="95">
@@ -5654,7 +5654,7 @@
         <v>171</v>
       </c>
       <c r="M95" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7486</v>
       </c>
     </row>
     <row r="96">
@@ -5709,7 +5709,7 @@
         <v>171</v>
       </c>
       <c r="M96" t="n">
-        <v>0.3294</v>
+        <v>0.3298</v>
       </c>
     </row>
     <row r="97">
@@ -5764,7 +5764,7 @@
         <v>171</v>
       </c>
       <c r="M97" t="n">
-        <v>0.6948</v>
+        <v>0.6978</v>
       </c>
     </row>
     <row r="98">
@@ -5819,7 +5819,7 @@
         <v>171</v>
       </c>
       <c r="M98" t="n">
-        <v>0.4491</v>
+        <v>0.3985</v>
       </c>
     </row>
     <row r="99">
@@ -5929,7 +5929,7 @@
         <v>171</v>
       </c>
       <c r="M100" t="n">
-        <v>0.7392</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="101">
@@ -5984,7 +5984,7 @@
         <v>171</v>
       </c>
       <c r="M101" t="n">
-        <v>0.8444</v>
+        <v>0.8457</v>
       </c>
     </row>
     <row r="102">
@@ -6039,7 +6039,7 @@
         <v>171</v>
       </c>
       <c r="M102" t="n">
-        <v>0.4947</v>
+        <v>0.4809</v>
       </c>
     </row>
     <row r="103">
@@ -6149,7 +6149,7 @@
         <v>171</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4754</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="105">
@@ -6259,7 +6259,7 @@
         <v>171</v>
       </c>
       <c r="M106" t="n">
-        <v>0.6736</v>
+        <v>0.6834</v>
       </c>
     </row>
     <row r="107">
@@ -6314,7 +6314,7 @@
         <v>173</v>
       </c>
       <c r="M107" t="n">
-        <v>0.7917</v>
+        <v>0.7844</v>
       </c>
     </row>
     <row r="108">
@@ -6479,7 +6479,7 @@
         <v>173</v>
       </c>
       <c r="M110" t="n">
-        <v>0.5239</v>
+        <v>0.5363</v>
       </c>
     </row>
     <row r="111">
@@ -6534,7 +6534,7 @@
         <v>173</v>
       </c>
       <c r="M111" t="n">
-        <v>0.626</v>
+        <v>0.6246</v>
       </c>
     </row>
     <row r="112">
@@ -6589,7 +6589,7 @@
         <v>173</v>
       </c>
       <c r="M112" t="n">
-        <v>0.7667</v>
+        <v>0.7755</v>
       </c>
     </row>
     <row r="113">
@@ -6644,7 +6644,7 @@
         <v>173</v>
       </c>
       <c r="M113" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8282</v>
       </c>
     </row>
     <row r="114">
@@ -6699,7 +6699,7 @@
         <v>173</v>
       </c>
       <c r="M114" t="n">
-        <v>0.4967</v>
+        <v>0.5205</v>
       </c>
     </row>
     <row r="115">
@@ -6754,7 +6754,7 @@
         <v>173</v>
       </c>
       <c r="M115" t="n">
-        <v>0.8174</v>
+        <v>0.8141</v>
       </c>
     </row>
     <row r="116">
@@ -6809,7 +6809,7 @@
         <v>173</v>
       </c>
       <c r="M116" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6914</v>
       </c>
     </row>
     <row r="117">
@@ -6864,7 +6864,7 @@
         <v>173</v>
       </c>
       <c r="M117" t="n">
-        <v>0.7991</v>
+        <v>0.8021</v>
       </c>
     </row>
     <row r="118">
@@ -7029,7 +7029,7 @@
         <v>173</v>
       </c>
       <c r="M120" t="n">
-        <v>0.7355</v>
+        <v>0.7045</v>
       </c>
     </row>
     <row r="121">
@@ -7084,7 +7084,7 @@
         <v>173</v>
       </c>
       <c r="M121" t="n">
-        <v>0.774</v>
+        <v>0.7752</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,46 +490,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501082</t>
+          <t>0022501090</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>46110</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612746</v>
+        <v>1610612744</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -539,353 +539,353 @@
         <v>159</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2598</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501083</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612754</v>
+        <v>1610612748</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3066</v>
+        <v>0.5719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501084</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612751</v>
+        <v>1610612737</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612758</v>
+        <v>1610612738</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5825</v>
+        <v>0.4908</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501085</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612766</v>
+        <v>1610612763</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4334</v>
+        <v>0.3788</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501086</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612753</v>
+        <v>1610612741</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5864</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501087</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612757</v>
+        <v>1610612742</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612764</v>
+        <v>1610612750</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8082</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501088</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612740</v>
+        <v>1610612762</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3947</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501089</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C9" t="n">
         <v>1610612760</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612752</v>
+        <v>1610612765</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -921,360 +921,360 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6499</v>
+        <v>0.7044</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7782</v>
+        <v>0.8587</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612748</v>
+        <v>1610612749</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612755</v>
+        <v>1610612742</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M11" t="n">
-        <v>0.509</v>
+        <v>0.5769</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612737</v>
+        <v>1610612753</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5179</v>
+        <v>0.5649</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612763</v>
+        <v>1610612751</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3766</v>
+        <v>0.2139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612759</v>
+        <v>1610612765</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612741</v>
+        <v>1610612761</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8476</v>
+        <v>0.6484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612742</v>
+        <v>1610612745</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612750</v>
+        <v>1610612752</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3123</v>
+        <v>0.4432</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612762</v>
+        <v>1610612747</v>
       </c>
       <c r="D16" t="n">
         <v>1610612739</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1294,562 +1294,562 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M16" t="n">
-        <v>0.209</v>
+        <v>0.5879</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612765</v>
+        <v>1610612757</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6788</v>
+        <v>0.6882</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612747</v>
+        <v>1610612763</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612764</v>
+        <v>1610612752</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8944</v>
+        <v>0.2754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612749</v>
+        <v>1610612764</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612742</v>
+        <v>1610612755</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6137</v>
+        <v>0.2683</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612756</v>
+        <v>1610612738</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.4499</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612751</v>
+        <v>1610612753</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612766</v>
+        <v>1610612737</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2238</v>
+        <v>0.4327</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612761</v>
+        <v>1610612758</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M22" t="n">
-        <v>0.628</v>
+        <v>0.7786</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612752</v>
+        <v>1610612754</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4677</v>
+        <v>0.6317</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612747</v>
+        <v>1610612745</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612739</v>
+        <v>1610612749</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.8364</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612746</v>
+        <v>1610612762</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612757</v>
+        <v>1610612743</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.2119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612763</v>
+        <v>1610612744</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612752</v>
+        <v>1610612759</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1859,822 +1859,822 @@
         <v>162</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2666</v>
+        <v>0.3034</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612755</v>
+        <v>1610612756</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2549</v>
+        <v>0.6199</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612748</v>
+        <v>1610612765</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612738</v>
+        <v>1610612750</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4293</v>
+        <v>0.6601</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612753</v>
+        <v>1610612760</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612737</v>
+        <v>1610612747</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4434</v>
+        <v>0.6596</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612761</v>
+        <v>1610612744</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612758</v>
+        <v>1610612739</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M30" t="n">
-        <v>0.784</v>
+        <v>0.3503</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612741</v>
+        <v>1610612757</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612754</v>
+        <v>1610612740</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6631</v>
+        <v>0.6321</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612745</v>
+        <v>1610612746</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612749</v>
+        <v>1610612759</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8335</v>
+        <v>0.4465</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612762</v>
+        <v>1610612766</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612743</v>
+        <v>1610612754</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1929</v>
+        <v>0.7755</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612759</v>
+        <v>1610612750</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3</v>
+        <v>0.5609</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612766</v>
+        <v>1610612751</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612756</v>
+        <v>1610612737</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6207</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612765</v>
+        <v>1610612752</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612750</v>
+        <v>1610612741</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6397</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612760</v>
+        <v>1610612745</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612747</v>
+        <v>1610612762</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6622</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612744</v>
+        <v>1610612763</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3234</v>
+        <v>0.3948</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612757</v>
+        <v>1610612749</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612740</v>
+        <v>1610612738</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6096</v>
+        <v>0.2251</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612746</v>
+        <v>1610612742</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612759</v>
+        <v>1610612753</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4429</v>
+        <v>0.3971</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612766</v>
+        <v>1610612758</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612754</v>
+        <v>1610612740</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2684,657 +2684,657 @@
         <v>164</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7985</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612750</v>
+        <v>1610612764</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M42" t="n">
-        <v>0.54</v>
+        <v>0.8233</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612751</v>
+        <v>1610612743</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612737</v>
+        <v>1610612759</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2462</v>
+        <v>0.5041</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.3761</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612745</v>
+        <v>1610612738</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612762</v>
+        <v>1610612761</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8202</v>
+        <v>0.7151999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612763</v>
+        <v>1610612751</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612761</v>
+        <v>1610612764</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3825</v>
+        <v>0.6318</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2161</v>
+        <v>0.4079</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612742</v>
+        <v>1610612749</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612753</v>
+        <v>1610612763</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4008</v>
+        <v>0.5303</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612758</v>
+        <v>1610612739</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612740</v>
+        <v>1610612754</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4345</v>
+        <v>0.8264</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8337</v>
+        <v>0.5316</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612743</v>
+        <v>1610612740</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612759</v>
+        <v>1610612753</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5095</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612755</v>
+        <v>1610612760</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612765</v>
+        <v>1610612762</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3806</v>
+        <v>0.8526</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612738</v>
+        <v>1610612742</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3344,52 +3344,52 @@
         <v>166</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7138</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612751</v>
+        <v>1610612758</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612764</v>
+        <v>1610612746</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3399,52 +3399,52 @@
         <v>166</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6501</v>
+        <v>0.2264</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612741</v>
+        <v>1610612744</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612756</v>
+        <v>1610612745</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3454,767 +3454,767 @@
         <v>166</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4142</v>
+        <v>0.4678</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612749</v>
+        <v>1610612737</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612763</v>
+        <v>1610612752</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5484</v>
+        <v>0.4404</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612739</v>
+        <v>1610612753</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612754</v>
+        <v>1610612765</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8439</v>
+        <v>0.3427</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612750</v>
+        <v>1610612763</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612766</v>
+        <v>1610612739</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M58" t="n">
-        <v>0.546</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M59" t="n">
-        <v>0.477</v>
+        <v>0.7681</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612760</v>
+        <v>1610612743</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612762</v>
+        <v>1610612757</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8588</v>
+        <v>0.7633</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612742</v>
+        <v>1610612764</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612747</v>
+        <v>1610612741</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2633</v>
+        <v>0.3922</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612758</v>
+        <v>1610612738</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M62" t="n">
-        <v>0.2402</v>
+        <v>0.6142</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612744</v>
+        <v>1610612751</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M63" t="n">
-        <v>0.4772</v>
+        <v>0.5014999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612752</v>
+        <v>1610612748</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4442</v>
+        <v>0.5552</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612753</v>
+        <v>1610612754</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612765</v>
+        <v>1610612750</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3424</v>
+        <v>0.3003</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612739</v>
+        <v>1610612762</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M66" t="n">
-        <v>0.2191</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612759</v>
+        <v>1610612744</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612755</v>
+        <v>1610612758</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M67" t="n">
-        <v>0.7645</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612757</v>
+        <v>1610612760</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M68" t="n">
-        <v>0.7824</v>
+        <v>0.4265</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612764</v>
+        <v>1610612746</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612741</v>
+        <v>1610612742</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4224,52 +4224,52 @@
         <v>168</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4057</v>
+        <v>0.8303</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4279,302 +4279,302 @@
         <v>168</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6338</v>
+        <v>0.5392</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612751</v>
+        <v>1610612739</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612749</v>
+        <v>1610612737</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4837</v>
+        <v>0.6664</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M72" t="n">
-        <v>0.5644</v>
+        <v>0.5377</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612754</v>
+        <v>1610612765</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612750</v>
+        <v>1610612749</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M73" t="n">
-        <v>0.2619</v>
+        <v>0.8629</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612762</v>
+        <v>1610612757</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7343</v>
+        <v>0.7762</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612744</v>
+        <v>1610612743</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612758</v>
+        <v>1610612763</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7741</v>
+        <v>0.8489</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D76" t="n">
         <v>1610612760</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4594,42 +4594,42 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M76" t="n">
-        <v>0.4085</v>
+        <v>0.3882</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612746</v>
+        <v>1610612756</v>
       </c>
       <c r="D77" t="n">
         <v>1610612742</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4649,643 +4649,643 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8246</v>
+        <v>0.7969000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612745</v>
+        <v>1610612748</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M78" t="n">
-        <v>0.5189</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612739</v>
+        <v>1610612764</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612737</v>
+        <v>1610612741</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M79" t="n">
-        <v>0.6939</v>
+        <v>0.3919</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612750</v>
+        <v>1610612754</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M80" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.4681</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612765</v>
+        <v>1610612752</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612749</v>
+        <v>1610612738</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8629</v>
+        <v>0.5966</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612759</v>
+        <v>1610612745</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612757</v>
+        <v>1610612755</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M82" t="n">
-        <v>0.7829</v>
+        <v>0.6059</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612743</v>
+        <v>1610612744</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612763</v>
+        <v>1610612747</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8602</v>
+        <v>0.4075</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612760</v>
+        <v>1610612765</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K84" t="n">
         <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M84" t="n">
-        <v>0.3794</v>
+        <v>0.4946</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612756</v>
+        <v>1610612764</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612742</v>
+        <v>1610612748</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K85" t="n">
         <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7991</v>
+        <v>0.2757</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612748</v>
+        <v>1610612739</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5644</v>
+        <v>0.4926</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M87" t="n">
-        <v>0.4057</v>
+        <v>0.7368</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612754</v>
+        <v>1610612755</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K88" t="n">
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M88" t="n">
-        <v>0.4987</v>
+        <v>0.3726</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C89" t="n">
         <v>1610612752</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5321,165 +5321,165 @@
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6111</v>
+        <v>0.3892</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612744</v>
+        <v>1610612745</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612747</v>
+        <v>1610612750</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K91" t="n">
         <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M91" t="n">
-        <v>0.4113</v>
+        <v>0.4984</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612765</v>
+        <v>1610612751</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5489,52 +5489,52 @@
         <v>171</v>
       </c>
       <c r="M92" t="n">
-        <v>0.4851</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612764</v>
+        <v>1610612759</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612748</v>
+        <v>1610612742</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5544,52 +5544,52 @@
         <v>171</v>
       </c>
       <c r="M93" t="n">
-        <v>0.2695</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612737</v>
+        <v>1610612762</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612739</v>
+        <v>1610612763</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5599,52 +5599,52 @@
         <v>171</v>
       </c>
       <c r="M94" t="n">
-        <v>0.4635</v>
+        <v>0.5032</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612740</v>
+        <v>1610612760</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5654,52 +5654,52 @@
         <v>171</v>
       </c>
       <c r="M95" t="n">
-        <v>0.7486</v>
+        <v>0.4626</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612754</v>
+        <v>1610612757</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612755</v>
+        <v>1610612746</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -5709,52 +5709,52 @@
         <v>171</v>
       </c>
       <c r="M96" t="n">
-        <v>0.3298</v>
+        <v>0.4951</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612752</v>
+        <v>1610612758</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612761</v>
+        <v>1610612744</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5764,52 +5764,52 @@
         <v>171</v>
       </c>
       <c r="M97" t="n">
-        <v>0.6978</v>
+        <v>0.3759</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612741</v>
+        <v>1610612747</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612753</v>
+        <v>1610612756</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -5819,492 +5819,492 @@
         <v>171</v>
       </c>
       <c r="M98" t="n">
-        <v>0.3985</v>
+        <v>0.6782</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612745</v>
+        <v>1610612738</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612750</v>
+        <v>1610612753</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K99" t="n">
         <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M99" t="n">
-        <v>0.4931</v>
+        <v>0.7432</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612749</v>
+        <v>1610612739</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K100" t="n">
         <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M100" t="n">
-        <v>0.719</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612742</v>
+        <v>1610612765</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M101" t="n">
-        <v>0.8457</v>
+        <v>0.2735</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612762</v>
+        <v>1610612748</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612763</v>
+        <v>1610612737</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K102" t="n">
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M102" t="n">
-        <v>0.4809</v>
+        <v>0.5347</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612760</v>
+        <v>1610612766</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K103" t="n">
         <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M103" t="n">
-        <v>0.4585</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612757</v>
+        <v>1610612755</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612746</v>
+        <v>1610612749</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M104" t="n">
-        <v>0.496</v>
+        <v>0.8013</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612758</v>
+        <v>1610612761</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612744</v>
+        <v>1610612751</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K105" t="n">
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M105" t="n">
-        <v>0.3931</v>
+        <v>0.8314</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612747</v>
+        <v>1610612742</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612756</v>
+        <v>1610612741</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K106" t="n">
         <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M106" t="n">
-        <v>0.6834</v>
+        <v>0.5189</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612738</v>
+        <v>1610612745</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612753</v>
+        <v>1610612763</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -6314,52 +6314,52 @@
         <v>173</v>
       </c>
       <c r="M107" t="n">
-        <v>0.7844</v>
+        <v>0.8069</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612764</v>
+        <v>1610612740</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -6369,52 +6369,52 @@
         <v>173</v>
       </c>
       <c r="M108" t="n">
-        <v>0.8507</v>
+        <v>0.7193000000000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612754</v>
+        <v>1610612760</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612765</v>
+        <v>1610612756</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -6424,52 +6424,52 @@
         <v>173</v>
       </c>
       <c r="M109" t="n">
-        <v>0.2515</v>
+        <v>0.7962</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612748</v>
+        <v>1610612759</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612737</v>
+        <v>1610612743</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -6479,52 +6479,52 @@
         <v>173</v>
       </c>
       <c r="M110" t="n">
-        <v>0.5363</v>
+        <v>0.6325</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612752</v>
+        <v>1610612747</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612766</v>
+        <v>1610612762</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -6534,52 +6534,52 @@
         <v>173</v>
       </c>
       <c r="M111" t="n">
-        <v>0.6246</v>
+        <v>0.8599</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612755</v>
+        <v>1610612746</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612749</v>
+        <v>1610612744</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -6589,52 +6589,52 @@
         <v>173</v>
       </c>
       <c r="M112" t="n">
-        <v>0.7755</v>
+        <v>0.7069</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C113" t="n">
-        <v>1610612761</v>
+        <v>1610612757</v>
       </c>
       <c r="D113" t="n">
-        <v>1610612751</v>
+        <v>1610612758</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -6644,447 +6644,7 @@
         <v>173</v>
       </c>
       <c r="M113" t="n">
-        <v>0.8282</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>0022501193</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C114" t="n">
-        <v>1610612742</v>
-      </c>
-      <c r="D114" t="n">
-        <v>1610612741</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Mavericks</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Bulls</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>CHI</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>American Airlines Center</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" t="n">
-        <v>173</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0.5205</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>0022501194</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C115" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="D115" t="n">
-        <v>1610612763</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Grizzlies</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Toyota Center</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" t="n">
-        <v>173</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0.8141</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>0022501195</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C116" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="D116" t="n">
-        <v>1610612740</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Pelicans</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Target Center</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="K116" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" t="n">
-        <v>173</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0.6914</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C117" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D117" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K117" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" t="n">
-        <v>173</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0.8021</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C118" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D118" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K118" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" t="n">
-        <v>173</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0.6246</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C119" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D119" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K119" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" t="n">
-        <v>173</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0.8625</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C120" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" t="n">
-        <v>173</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0.7045</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C121" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K121" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" t="n">
-        <v>173</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0.7752</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,101 +490,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501090</t>
+          <t>0022501091</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612743</v>
+        <v>1610612748</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612744</v>
+        <v>1610612755</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>0.787</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501092</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612748</v>
+        <v>1610612737</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612755</v>
+        <v>1610612738</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -594,52 +594,52 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5719</v>
+        <v>0.5096000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501093</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612737</v>
+        <v>1610612763</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -649,52 +649,52 @@
         <v>160</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4908</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501094</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612763</v>
+        <v>1610612759</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612756</v>
+        <v>1610612741</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -704,52 +704,52 @@
         <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3788</v>
+        <v>0.8423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501095</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612759</v>
+        <v>1610612742</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612741</v>
+        <v>1610612750</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -759,52 +759,52 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8375</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501096</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612742</v>
+        <v>1610612762</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612750</v>
+        <v>1610612739</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -814,52 +814,52 @@
         <v>160</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3162</v>
+        <v>0.2092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501097</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612762</v>
+        <v>1610612760</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612739</v>
+        <v>1610612765</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -869,52 +869,52 @@
         <v>160</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2124</v>
+        <v>0.6926</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501098</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612760</v>
+        <v>1610612747</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -924,107 +924,107 @@
         <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7044</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022500652</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612747</v>
+        <v>1610612749</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612764</v>
+        <v>1610612742</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8587</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501099</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612749</v>
+        <v>1610612753</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612742</v>
+        <v>1610612756</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1034,52 +1034,52 @@
         <v>161</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5769</v>
+        <v>0.5474</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501100</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1089,52 +1089,52 @@
         <v>161</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5649</v>
+        <v>0.2216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501101</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612751</v>
+        <v>1610612765</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612766</v>
+        <v>1610612761</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1144,52 +1144,52 @@
         <v>161</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2139</v>
+        <v>0.5839</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501102</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612765</v>
+        <v>1610612745</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612761</v>
+        <v>1610612752</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1199,52 +1199,52 @@
         <v>161</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6484</v>
+        <v>0.4887</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501103</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612745</v>
+        <v>1610612747</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1254,52 +1254,52 @@
         <v>161</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4432</v>
+        <v>0.5876</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501104</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612739</v>
+        <v>1610612757</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1309,107 +1309,107 @@
         <v>161</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5879</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612746</v>
+        <v>1610612763</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612757</v>
+        <v>1610612752</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6882</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612763</v>
+        <v>1610612764</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1419,52 +1419,52 @@
         <v>162</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2754</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612764</v>
+        <v>1610612748</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612755</v>
+        <v>1610612738</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1474,52 +1474,52 @@
         <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2683</v>
+        <v>0.4124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612738</v>
+        <v>1610612737</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1529,52 +1529,52 @@
         <v>162</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4499</v>
+        <v>0.4239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612737</v>
+        <v>1610612758</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1584,52 +1584,52 @@
         <v>162</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4327</v>
+        <v>0.7996</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612761</v>
+        <v>1610612741</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612758</v>
+        <v>1610612754</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1639,52 +1639,52 @@
         <v>162</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7786</v>
+        <v>0.6574</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612741</v>
+        <v>1610612745</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612754</v>
+        <v>1610612749</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1694,52 +1694,52 @@
         <v>162</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6317</v>
+        <v>0.8322000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1749,52 +1749,52 @@
         <v>162</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8364</v>
+        <v>0.2082</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612762</v>
+        <v>1610612744</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612743</v>
+        <v>1610612759</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1804,107 +1804,107 @@
         <v>162</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2119</v>
+        <v>0.2927</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612759</v>
+        <v>1610612756</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3034</v>
+        <v>0.6189</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612766</v>
+        <v>1610612765</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612756</v>
+        <v>1610612750</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1914,52 +1914,52 @@
         <v>163</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6199</v>
+        <v>0.6297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612765</v>
+        <v>1610612760</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612750</v>
+        <v>1610612747</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1969,52 +1969,52 @@
         <v>163</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6601</v>
+        <v>0.6283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2024,52 +2024,52 @@
         <v>163</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6596</v>
+        <v>0.3385</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612744</v>
+        <v>1610612757</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612739</v>
+        <v>1610612740</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,52 +2079,52 @@
         <v>163</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3503</v>
+        <v>0.6332</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2134,107 +2134,107 @@
         <v>163</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6321</v>
+        <v>0.4484</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4465</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612754</v>
+        <v>1610612750</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2244,52 +2244,52 @@
         <v>164</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7755</v>
+        <v>0.5615</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612755</v>
+        <v>1610612751</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2299,52 +2299,52 @@
         <v>164</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5609</v>
+        <v>0.2449</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612751</v>
+        <v>1610612752</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612737</v>
+        <v>1610612741</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2354,52 +2354,52 @@
         <v>164</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2428</v>
+        <v>0.8101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612752</v>
+        <v>1610612745</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612741</v>
+        <v>1610612762</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2409,52 +2409,52 @@
         <v>164</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8244</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612745</v>
+        <v>1610612763</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612762</v>
+        <v>1610612761</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2464,52 +2464,52 @@
         <v>164</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.3706</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612763</v>
+        <v>1610612749</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612761</v>
+        <v>1610612738</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2519,52 +2519,52 @@
         <v>164</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3948</v>
+        <v>0.2194</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612738</v>
+        <v>1610612753</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2574,52 +2574,52 @@
         <v>164</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2251</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612742</v>
+        <v>1610612758</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612753</v>
+        <v>1610612740</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2629,107 +2629,107 @@
         <v>164</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3971</v>
+        <v>0.4645</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612758</v>
+        <v>1610612748</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612740</v>
+        <v>1610612764</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4333</v>
+        <v>0.8253</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612748</v>
+        <v>1610612743</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612764</v>
+        <v>1610612759</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2739,52 +2739,52 @@
         <v>165</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8233</v>
+        <v>0.5097</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612743</v>
+        <v>1610612755</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612759</v>
+        <v>1610612765</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2794,107 +2794,107 @@
         <v>165</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5041</v>
+        <v>0.4423</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612755</v>
+        <v>1610612738</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3761</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612738</v>
+        <v>1610612751</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612761</v>
+        <v>1610612764</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2904,52 +2904,52 @@
         <v>166</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.6559</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612764</v>
+        <v>1610612756</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2959,52 +2959,52 @@
         <v>166</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6318</v>
+        <v>0.4068</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612741</v>
+        <v>1610612749</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612756</v>
+        <v>1610612763</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3014,52 +3014,52 @@
         <v>166</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4079</v>
+        <v>0.5608</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612749</v>
+        <v>1610612739</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612763</v>
+        <v>1610612754</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3069,52 +3069,52 @@
         <v>166</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5303</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612739</v>
+        <v>1610612750</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612754</v>
+        <v>1610612766</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3124,52 +3124,52 @@
         <v>166</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8264</v>
+        <v>0.5328000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612750</v>
+        <v>1610612740</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3179,52 +3179,52 @@
         <v>166</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5316</v>
+        <v>0.4829</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612740</v>
+        <v>1610612760</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612753</v>
+        <v>1610612762</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3234,52 +3234,52 @@
         <v>166</v>
       </c>
       <c r="M51" t="n">
-        <v>0.472</v>
+        <v>0.8517</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612760</v>
+        <v>1610612742</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612762</v>
+        <v>1610612747</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3289,52 +3289,52 @@
         <v>166</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8526</v>
+        <v>0.2614</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612742</v>
+        <v>1610612758</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3344,52 +3344,52 @@
         <v>166</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2659</v>
+        <v>0.2269</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612758</v>
+        <v>1610612744</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3399,107 +3399,107 @@
         <v>166</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2264</v>
+        <v>0.4403</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612744</v>
+        <v>1610612737</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612745</v>
+        <v>1610612752</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4678</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612737</v>
+        <v>1610612753</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612752</v>
+        <v>1610612765</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3509,52 +3509,52 @@
         <v>167</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4404</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612753</v>
+        <v>1610612763</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612765</v>
+        <v>1610612739</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3564,52 +3564,52 @@
         <v>167</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3427</v>
+        <v>0.2439</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612763</v>
+        <v>1610612759</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612739</v>
+        <v>1610612755</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3619,52 +3619,52 @@
         <v>167</v>
       </c>
       <c r="M58" t="n">
-        <v>0.253</v>
+        <v>0.7714</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612759</v>
+        <v>1610612743</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612755</v>
+        <v>1610612757</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3674,107 +3674,107 @@
         <v>167</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7681</v>
+        <v>0.7775</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612743</v>
+        <v>1610612764</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612757</v>
+        <v>1610612741</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M60" t="n">
-        <v>0.7633</v>
+        <v>0.3834</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612741</v>
+        <v>1610612766</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3784,52 +3784,52 @@
         <v>168</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3922</v>
+        <v>0.6572</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612738</v>
+        <v>1610612751</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>168</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6142</v>
+        <v>0.5069</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612751</v>
+        <v>1610612761</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,52 +3894,52 @@
         <v>168</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5966</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612761</v>
+        <v>1610612754</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3949,52 +3949,52 @@
         <v>168</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5552</v>
+        <v>0.2827</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612754</v>
+        <v>1610612740</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612750</v>
+        <v>1610612762</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4004,52 +4004,52 @@
         <v>168</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3003</v>
+        <v>0.7065</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612740</v>
+        <v>1610612744</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4059,52 +4059,52 @@
         <v>168</v>
       </c>
       <c r="M66" t="n">
-        <v>0.716</v>
+        <v>0.7785</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612744</v>
+        <v>1610612747</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612758</v>
+        <v>1610612760</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4114,52 +4114,52 @@
         <v>168</v>
       </c>
       <c r="M67" t="n">
-        <v>0.787</v>
+        <v>0.4703</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612760</v>
+        <v>1610612742</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4169,52 +4169,52 @@
         <v>168</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4265</v>
+        <v>0.8365</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612746</v>
+        <v>1610612756</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612742</v>
+        <v>1610612745</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4224,107 +4224,107 @@
         <v>168</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8303</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612756</v>
+        <v>1610612739</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612745</v>
+        <v>1610612737</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5392</v>
+        <v>0.6701</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612739</v>
+        <v>1610612753</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612737</v>
+        <v>1610612750</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4334,52 +4334,52 @@
         <v>169</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6664</v>
+        <v>0.4898</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612753</v>
+        <v>1610612765</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612750</v>
+        <v>1610612749</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4389,52 +4389,52 @@
         <v>169</v>
       </c>
       <c r="M72" t="n">
-        <v>0.5377</v>
+        <v>0.8134</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612765</v>
+        <v>1610612759</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612749</v>
+        <v>1610612757</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4444,52 +4444,52 @@
         <v>169</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8629</v>
+        <v>0.7913</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612759</v>
+        <v>1610612743</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612757</v>
+        <v>1610612763</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4499,52 +4499,52 @@
         <v>169</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7762</v>
+        <v>0.8524</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612743</v>
+        <v>1610612746</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612763</v>
+        <v>1610612760</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>169</v>
       </c>
       <c r="M75" t="n">
-        <v>0.8489</v>
+        <v>0.4087</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612746</v>
+        <v>1610612756</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612760</v>
+        <v>1610612742</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,107 +4609,107 @@
         <v>169</v>
       </c>
       <c r="M76" t="n">
-        <v>0.3882</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612756</v>
+        <v>1610612761</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612742</v>
+        <v>1610612748</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.5963000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612761</v>
+        <v>1610612764</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,52 +4719,52 @@
         <v>170</v>
       </c>
       <c r="M78" t="n">
-        <v>0.555</v>
+        <v>0.3832</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612741</v>
+        <v>1610612754</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4774,52 +4774,52 @@
         <v>170</v>
       </c>
       <c r="M79" t="n">
-        <v>0.3919</v>
+        <v>0.5175999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612751</v>
+        <v>1610612752</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612754</v>
+        <v>1610612738</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4829,52 +4829,52 @@
         <v>170</v>
       </c>
       <c r="M80" t="n">
-        <v>0.4681</v>
+        <v>0.5292</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612752</v>
+        <v>1610612745</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612738</v>
+        <v>1610612755</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -4884,52 +4884,52 @@
         <v>170</v>
       </c>
       <c r="M81" t="n">
-        <v>0.5966</v>
+        <v>0.6479</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612745</v>
+        <v>1610612744</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612755</v>
+        <v>1610612747</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -4939,107 +4939,107 @@
         <v>170</v>
       </c>
       <c r="M82" t="n">
-        <v>0.6059</v>
+        <v>0.3986</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M83" t="n">
-        <v>0.4075</v>
+        <v>0.5583</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612766</v>
+        <v>1610612764</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612765</v>
+        <v>1610612748</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5049,52 +5049,52 @@
         <v>171</v>
       </c>
       <c r="M84" t="n">
-        <v>0.4946</v>
+        <v>0.2687</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612764</v>
+        <v>1610612737</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612748</v>
+        <v>1610612739</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5104,52 +5104,52 @@
         <v>171</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2757</v>
+        <v>0.4916</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612737</v>
+        <v>1610612738</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612739</v>
+        <v>1610612740</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -5159,52 +5159,52 @@
         <v>171</v>
       </c>
       <c r="M86" t="n">
-        <v>0.4926</v>
+        <v>0.7833</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612740</v>
+        <v>1610612755</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -5214,52 +5214,52 @@
         <v>171</v>
       </c>
       <c r="M87" t="n">
-        <v>0.7368</v>
+        <v>0.3507</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612754</v>
+        <v>1610612752</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -5269,52 +5269,52 @@
         <v>171</v>
       </c>
       <c r="M88" t="n">
-        <v>0.3726</v>
+        <v>0.6974</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612752</v>
+        <v>1610612741</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -5324,52 +5324,52 @@
         <v>171</v>
       </c>
       <c r="M89" t="n">
-        <v>0.778</v>
+        <v>0.4334</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612741</v>
+        <v>1610612745</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612753</v>
+        <v>1610612750</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5379,52 +5379,52 @@
         <v>171</v>
       </c>
       <c r="M90" t="n">
-        <v>0.3892</v>
+        <v>0.5344</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612750</v>
+        <v>1610612751</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5434,52 +5434,52 @@
         <v>171</v>
       </c>
       <c r="M91" t="n">
-        <v>0.4984</v>
+        <v>0.7167</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612749</v>
+        <v>1610612759</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612751</v>
+        <v>1610612742</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5489,52 +5489,52 @@
         <v>171</v>
       </c>
       <c r="M92" t="n">
-        <v>0.696</v>
+        <v>0.8504</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612759</v>
+        <v>1610612762</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5544,52 +5544,52 @@
         <v>171</v>
       </c>
       <c r="M93" t="n">
-        <v>0.8487</v>
+        <v>0.5029</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612762</v>
+        <v>1610612743</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612763</v>
+        <v>1610612760</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5599,52 +5599,52 @@
         <v>171</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5032</v>
+        <v>0.5397</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612743</v>
+        <v>1610612757</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -5654,52 +5654,52 @@
         <v>171</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4626</v>
+        <v>0.4728</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612757</v>
+        <v>1610612758</v>
       </c>
       <c r="D96" t="n">
-        <v>1610612746</v>
+        <v>1610612744</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -5709,52 +5709,52 @@
         <v>171</v>
       </c>
       <c r="M96" t="n">
-        <v>0.4951</v>
+        <v>0.3786</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612758</v>
+        <v>1610612747</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5764,107 +5764,107 @@
         <v>171</v>
       </c>
       <c r="M97" t="n">
-        <v>0.3759</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C98" t="n">
-        <v>1610612747</v>
+        <v>1610612738</v>
       </c>
       <c r="D98" t="n">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K98" t="n">
         <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M98" t="n">
-        <v>0.6782</v>
+        <v>0.8026</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C99" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="D99" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5874,52 +5874,52 @@
         <v>173</v>
       </c>
       <c r="M99" t="n">
-        <v>0.7432</v>
+        <v>0.8532999999999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C100" t="n">
-        <v>1610612739</v>
+        <v>1610612754</v>
       </c>
       <c r="D100" t="n">
-        <v>1610612764</v>
+        <v>1610612765</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -5929,52 +5929,52 @@
         <v>173</v>
       </c>
       <c r="M100" t="n">
-        <v>0.845</v>
+        <v>0.2913</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C101" t="n">
-        <v>1610612754</v>
+        <v>1610612748</v>
       </c>
       <c r="D101" t="n">
-        <v>1610612765</v>
+        <v>1610612737</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -5984,52 +5984,52 @@
         <v>173</v>
       </c>
       <c r="M101" t="n">
-        <v>0.2735</v>
+        <v>0.5325</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C102" t="n">
-        <v>1610612748</v>
+        <v>1610612752</v>
       </c>
       <c r="D102" t="n">
-        <v>1610612737</v>
+        <v>1610612766</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6039,52 +6039,52 @@
         <v>173</v>
       </c>
       <c r="M102" t="n">
-        <v>0.5347</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C103" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="D103" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6094,52 +6094,52 @@
         <v>173</v>
       </c>
       <c r="M103" t="n">
-        <v>0.6496</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C104" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="D104" t="n">
-        <v>1610612749</v>
+        <v>1610612751</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -6149,52 +6149,52 @@
         <v>173</v>
       </c>
       <c r="M104" t="n">
-        <v>0.8013</v>
+        <v>0.8354</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C105" t="n">
-        <v>1610612761</v>
+        <v>1610612742</v>
       </c>
       <c r="D105" t="n">
-        <v>1610612751</v>
+        <v>1610612741</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -6204,52 +6204,52 @@
         <v>173</v>
       </c>
       <c r="M105" t="n">
-        <v>0.8314</v>
+        <v>0.5194</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C106" t="n">
-        <v>1610612742</v>
+        <v>1610612745</v>
       </c>
       <c r="D106" t="n">
-        <v>1610612741</v>
+        <v>1610612763</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -6259,52 +6259,52 @@
         <v>173</v>
       </c>
       <c r="M106" t="n">
-        <v>0.5189</v>
+        <v>0.8196</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C107" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="D107" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -6314,52 +6314,52 @@
         <v>173</v>
       </c>
       <c r="M107" t="n">
-        <v>0.8069</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0022501195</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C108" t="n">
-        <v>1610612750</v>
+        <v>1610612760</v>
       </c>
       <c r="D108" t="n">
-        <v>1610612740</v>
+        <v>1610612756</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -6369,52 +6369,52 @@
         <v>173</v>
       </c>
       <c r="M108" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7754</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0022501196</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C109" t="n">
-        <v>1610612760</v>
+        <v>1610612759</v>
       </c>
       <c r="D109" t="n">
-        <v>1610612756</v>
+        <v>1610612743</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -6424,52 +6424,52 @@
         <v>173</v>
       </c>
       <c r="M109" t="n">
-        <v>0.7962</v>
+        <v>0.6166</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0022501197</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C110" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="D110" t="n">
-        <v>1610612743</v>
+        <v>1610612762</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -6479,52 +6479,52 @@
         <v>173</v>
       </c>
       <c r="M110" t="n">
-        <v>0.6325</v>
+        <v>0.8601</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0022501198</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C111" t="n">
-        <v>1610612747</v>
+        <v>1610612746</v>
       </c>
       <c r="D111" t="n">
-        <v>1610612762</v>
+        <v>1610612744</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -6534,52 +6534,52 @@
         <v>173</v>
       </c>
       <c r="M111" t="n">
-        <v>0.8599</v>
+        <v>0.7346</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0022501199</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C112" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="D112" t="n">
-        <v>1610612744</v>
+        <v>1610612758</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -6589,62 +6589,7 @@
         <v>173</v>
       </c>
       <c r="M112" t="n">
-        <v>0.7069</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C113" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" t="n">
-        <v>173</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7822</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,516 +490,516 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501091</t>
+          <t>0022501003</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612748</v>
+        <v>1610612763</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612755</v>
+        <v>1610612752</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M2" t="n">
-        <v>0.522</v>
+        <v>0.2584</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501092</t>
+          <t>0022501105</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612737</v>
+        <v>1610612764</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612738</v>
+        <v>1610612755</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.2399</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501093</t>
+          <t>0022501106</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612763</v>
+        <v>1610612748</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612756</v>
+        <v>1610612738</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3776</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501094</t>
+          <t>0022501107</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612759</v>
+        <v>1610612753</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612741</v>
+        <v>1610612737</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8423</v>
+        <v>0.4176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501095</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612742</v>
+        <v>1610612761</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612750</v>
+        <v>1610612758</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3162</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501096</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612762</v>
+        <v>1610612741</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612739</v>
+        <v>1610612754</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2092</v>
+        <v>0.6159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501097</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612760</v>
+        <v>1610612745</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612765</v>
+        <v>1610612749</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6926</v>
+        <v>0.8313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501098</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612747</v>
+        <v>1610612762</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612764</v>
+        <v>1610612743</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M9" t="n">
-        <v>0.888</v>
+        <v>0.1983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022500652</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612749</v>
+        <v>1610612744</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612742</v>
+        <v>1610612759</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M10" t="n">
-        <v>0.603</v>
+        <v>0.2573</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501099</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="D11" t="n">
         <v>1610612756</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1019,258 +1019,258 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5474</v>
+        <v>0.6619</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501100</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612751</v>
+        <v>1610612765</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2216</v>
+        <v>0.5851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501101</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612765</v>
+        <v>1610612760</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5839</v>
+        <v>0.6382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501102</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612745</v>
+        <v>1610612744</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4887</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501103</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612747</v>
+        <v>1610612757</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612739</v>
+        <v>1610612740</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5876</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501104</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C16" t="n">
         <v>1610612746</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612757</v>
+        <v>1610612759</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1306,1075 +1306,1075 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7236</v>
+        <v>0.4431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612763</v>
+        <v>1610612766</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612752</v>
+        <v>1610612754</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M17" t="n">
-        <v>0.288</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612764</v>
+        <v>1610612755</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2477</v>
+        <v>0.4929</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612748</v>
+        <v>1610612751</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612738</v>
+        <v>1610612737</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4124</v>
+        <v>0.2527</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612753</v>
+        <v>1610612752</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612737</v>
+        <v>1610612741</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4239</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612761</v>
+        <v>1610612745</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7996</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612741</v>
+        <v>1610612763</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612754</v>
+        <v>1610612761</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6574</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612749</v>
+        <v>1610612738</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.2104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612762</v>
+        <v>1610612742</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612743</v>
+        <v>1610612753</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2082</v>
+        <v>0.4062</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612744</v>
+        <v>1610612758</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612759</v>
+        <v>1610612740</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2927</v>
+        <v>0.4607</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612756</v>
+        <v>1610612764</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6189</v>
+        <v>0.8063</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612765</v>
+        <v>1610612743</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612750</v>
+        <v>1610612759</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6297</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612760</v>
+        <v>1610612755</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6283</v>
+        <v>0.4255</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46114</v>
+        <v>46117</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612744</v>
+        <v>1610612738</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3385</v>
+        <v>0.7554</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46114</v>
+        <v>46117</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612757</v>
+        <v>1610612751</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612740</v>
+        <v>1610612764</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6332</v>
+        <v>0.6526</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46114</v>
+        <v>46117</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612746</v>
+        <v>1610612741</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612759</v>
+        <v>1610612756</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4484</v>
+        <v>0.4233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612754</v>
+        <v>1610612763</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8034</v>
+        <v>0.6404</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612755</v>
+        <v>1610612739</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612750</v>
+        <v>1610612754</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5615</v>
+        <v>0.8206</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612751</v>
+        <v>1610612750</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612737</v>
+        <v>1610612766</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2449</v>
+        <v>0.5544</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612752</v>
+        <v>1610612740</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612741</v>
+        <v>1610612753</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8101</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612745</v>
+        <v>1610612760</v>
       </c>
       <c r="D36" t="n">
         <v>1610612762</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2394,753 +2394,753 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8302</v>
+        <v>0.8601</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3706</v>
+        <v>0.2554</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612749</v>
+        <v>1610612758</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612738</v>
+        <v>1610612746</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2194</v>
+        <v>0.2165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612742</v>
+        <v>1610612744</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612753</v>
+        <v>1610612745</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4333</v>
+        <v>0.3916</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612758</v>
+        <v>1610612737</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612740</v>
+        <v>1610612752</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4645</v>
+        <v>0.4628</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612764</v>
+        <v>1610612765</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8253</v>
+        <v>0.3821</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612743</v>
+        <v>1610612763</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612759</v>
+        <v>1610612739</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5097</v>
+        <v>0.2298</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="C43" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="D43" t="n">
         <v>1610612755</v>
       </c>
-      <c r="D43" t="n">
-        <v>1610612765</v>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Spurs</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>76ers</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Pistons</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4423</v>
+        <v>0.7816</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612738</v>
+        <v>1610612743</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612761</v>
+        <v>1610612757</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7163</v>
+        <v>0.7655</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612764</v>
+        <v>1610612741</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6559</v>
+        <v>0.3966</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612741</v>
+        <v>1610612738</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4068</v>
+        <v>0.6309</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C47" t="n">
+        <v>1610612751</v>
+      </c>
+      <c r="D47" t="n">
         <v>1610612749</v>
       </c>
-      <c r="D47" t="n">
-        <v>1610612763</v>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Nets</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Bucks</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Grizzlies</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5608</v>
+        <v>0.4487</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612754</v>
+        <v>1610612748</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M48" t="n">
-        <v>0.831</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C49" t="n">
+        <v>1610612754</v>
+      </c>
+      <c r="D49" t="n">
         <v>1610612750</v>
       </c>
-      <c r="D49" t="n">
-        <v>1610612766</v>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Pacers</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Timberwolves</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Hornets</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C50" t="n">
         <v>1610612740</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612753</v>
+        <v>1610612762</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3176,195 +3176,195 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4829</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8517</v>
+        <v>0.7484</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612742</v>
+        <v>1610612747</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612747</v>
+        <v>1610612760</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2614</v>
+        <v>0.4419</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612758</v>
+        <v>1610612746</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612746</v>
+        <v>1610612742</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2269</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="D54" t="n">
         <v>1610612745</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3384,93 +3384,93 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4403</v>
+        <v>0.4736</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C55" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="D55" t="n">
         <v>1610612737</v>
       </c>
-      <c r="D55" t="n">
-        <v>1610612752</v>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Cavaliers</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>Hawks</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Knicks</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M55" t="n">
-        <v>0.457</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C56" t="n">
         <v>1610612753</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612765</v>
+        <v>1610612750</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3506,81 +3506,81 @@
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3883</v>
+        <v>0.4612</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612763</v>
+        <v>1610612765</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612739</v>
+        <v>1610612749</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2439</v>
+        <v>0.8193</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C58" t="n">
         <v>1610612759</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612755</v>
+        <v>1610612757</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3616,26 +3616,26 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7714</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C59" t="n">
         <v>1610612743</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612757</v>
+        <v>1610612763</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3671,2010 +3671,2010 @@
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7775</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612764</v>
+        <v>1610612746</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612741</v>
+        <v>1610612760</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3834</v>
+        <v>0.4015</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612738</v>
+        <v>1610612756</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612766</v>
+        <v>1610612742</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M61" t="n">
-        <v>0.6572</v>
+        <v>0.8208</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612751</v>
+        <v>1610612761</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M62" t="n">
-        <v>0.5069</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612761</v>
+        <v>1610612764</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5966</v>
+        <v>0.3966</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C64" t="n">
+        <v>1610612751</v>
+      </c>
+      <c r="D64" t="n">
         <v>1610612754</v>
       </c>
-      <c r="D64" t="n">
-        <v>1610612750</v>
-      </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Nets</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Pacers</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M64" t="n">
-        <v>0.2827</v>
+        <v>0.5142</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612740</v>
+        <v>1610612752</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612762</v>
+        <v>1610612738</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M65" t="n">
-        <v>0.7065</v>
+        <v>0.5268</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612744</v>
+        <v>1610612745</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612758</v>
+        <v>1610612755</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M66" t="n">
-        <v>0.7785</v>
+        <v>0.6848</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C67" t="n">
+        <v>1610612744</v>
+      </c>
+      <c r="D67" t="n">
         <v>1610612747</v>
       </c>
-      <c r="D67" t="n">
-        <v>1610612760</v>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>Warriors</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>Lakers</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>LAL</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4703</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612746</v>
+        <v>1610612766</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612742</v>
+        <v>1610612765</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8365</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612756</v>
+        <v>1610612764</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612745</v>
+        <v>1610612748</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5011</v>
+        <v>0.2784</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C70" t="n">
+        <v>1610612737</v>
+      </c>
+      <c r="D70" t="n">
         <v>1610612739</v>
       </c>
-      <c r="D70" t="n">
-        <v>1610612737</v>
-      </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Hawks</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Cavaliers</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Hawks</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6701</v>
+        <v>0.4476</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612753</v>
+        <v>1610612738</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612750</v>
+        <v>1610612740</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4898</v>
+        <v>0.8023</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612765</v>
+        <v>1610612754</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612749</v>
+        <v>1610612755</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M72" t="n">
-        <v>0.8134</v>
+        <v>0.3819</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612759</v>
+        <v>1610612752</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612757</v>
+        <v>1610612761</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7913</v>
+        <v>0.7467</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612743</v>
+        <v>1610612741</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612763</v>
+        <v>1610612753</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8524</v>
+        <v>0.4217</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612760</v>
+        <v>1610612750</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M75" t="n">
-        <v>0.4087</v>
+        <v>0.5168</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612756</v>
+        <v>1610612749</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612742</v>
+        <v>1610612751</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7975</v>
+        <v>0.7445000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612748</v>
+        <v>1610612742</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M77" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.8489</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612764</v>
+        <v>1610612762</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612741</v>
+        <v>1610612763</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M78" t="n">
-        <v>0.3832</v>
+        <v>0.5102</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612751</v>
+        <v>1610612743</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612754</v>
+        <v>1610612760</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M79" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5154</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612752</v>
+        <v>1610612757</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612738</v>
+        <v>1610612746</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M80" t="n">
-        <v>0.5292</v>
+        <v>0.4771</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612745</v>
+        <v>1610612758</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612755</v>
+        <v>1610612744</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M81" t="n">
-        <v>0.6479</v>
+        <v>0.3732</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612744</v>
+        <v>1610612747</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612747</v>
+        <v>1610612756</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M82" t="n">
-        <v>0.3986</v>
+        <v>0.6657999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612766</v>
+        <v>1610612738</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612765</v>
+        <v>1610612753</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M83" t="n">
-        <v>0.5583</v>
+        <v>0.8043</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C84" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="D84" t="n">
         <v>1610612764</v>
       </c>
-      <c r="D84" t="n">
-        <v>1610612748</v>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>Cavaliers</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>Wizards</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Heat</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>WAS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K84" t="n">
         <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M84" t="n">
-        <v>0.2687</v>
+        <v>0.8624000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612737</v>
+        <v>1610612754</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612739</v>
+        <v>1610612765</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K85" t="n">
         <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M85" t="n">
-        <v>0.4916</v>
+        <v>0.2866</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612738</v>
+        <v>1610612748</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612740</v>
+        <v>1610612737</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M86" t="n">
-        <v>0.7833</v>
+        <v>0.4992</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612754</v>
+        <v>1610612752</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612755</v>
+        <v>1610612766</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M87" t="n">
-        <v>0.3507</v>
+        <v>0.6062</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612761</v>
+        <v>1610612749</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K88" t="n">
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M88" t="n">
-        <v>0.6974</v>
+        <v>0.7429</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612741</v>
+        <v>1610612761</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M89" t="n">
-        <v>0.4334</v>
+        <v>0.8154</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612745</v>
+        <v>1610612742</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612750</v>
+        <v>1610612741</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M90" t="n">
-        <v>0.5344</v>
+        <v>0.5155</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612749</v>
+        <v>1610612745</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K91" t="n">
         <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7167</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612759</v>
+        <v>1610612750</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M92" t="n">
-        <v>0.8504</v>
+        <v>0.7829</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612762</v>
+        <v>1610612760</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612763</v>
+        <v>1610612756</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K93" t="n">
         <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M93" t="n">
-        <v>0.5029</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C94" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="D94" t="n">
         <v>1610612743</v>
       </c>
-      <c r="D94" t="n">
-        <v>1610612760</v>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>Spurs</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Nuggets</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5397</v>
+        <v>0.5974</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C95" t="n">
-        <v>1610612757</v>
+        <v>1610612747</v>
       </c>
       <c r="D95" t="n">
-        <v>1610612746</v>
+        <v>1610612762</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4728</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C96" t="n">
-        <v>1610612758</v>
+        <v>1610612746</v>
       </c>
       <c r="D96" t="n">
         <v>1610612744</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5694,902 +5694,77 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M96" t="n">
-        <v>0.3786</v>
+        <v>0.7634</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C97" t="n">
-        <v>1610612747</v>
+        <v>1610612757</v>
       </c>
       <c r="D97" t="n">
-        <v>1610612756</v>
+        <v>1610612758</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M97" t="n">
-        <v>0.6881</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>0022501186</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1610612738</v>
-      </c>
-      <c r="D98" t="n">
-        <v>1610612753</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Celtics</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>ORL</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>TD Garden</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" t="n">
-        <v>173</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0.8026</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>0022501187</t>
-        </is>
-      </c>
-      <c r="B99" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C99" t="n">
-        <v>1610612739</v>
-      </c>
-      <c r="D99" t="n">
-        <v>1610612764</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Cavaliers</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Wizards</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Rocket Arena</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" t="n">
-        <v>173</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0.8532999999999999</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>0022501188</t>
-        </is>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C100" t="n">
-        <v>1610612754</v>
-      </c>
-      <c r="D100" t="n">
-        <v>1610612765</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Pacers</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Pistons</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Gainbridge Fieldhouse</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" t="n">
-        <v>173</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0.2913</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0022501189</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C101" t="n">
-        <v>1610612748</v>
-      </c>
-      <c r="D101" t="n">
-        <v>1610612737</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Hawks</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Kaseya Center</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" t="n">
-        <v>173</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0.5325</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>0022501190</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C102" t="n">
-        <v>1610612752</v>
-      </c>
-      <c r="D102" t="n">
-        <v>1610612766</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Knicks</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Hornets</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>NYK</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Madison Square Garden</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" t="n">
-        <v>173</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0.6187</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>0022501191</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C103" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1610612749</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Bucks</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Xfinity Mobile Arena</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" t="n">
-        <v>173</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>0022501192</t>
-        </is>
-      </c>
-      <c r="B104" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C104" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="D104" t="n">
-        <v>1610612751</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Nets</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Scotiabank Arena</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" t="n">
-        <v>173</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0.8354</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>0022501193</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C105" t="n">
-        <v>1610612742</v>
-      </c>
-      <c r="D105" t="n">
-        <v>1610612741</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Mavericks</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Bulls</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>CHI</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>American Airlines Center</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" t="n">
-        <v>173</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0.5194</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>0022501194</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C106" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="D106" t="n">
-        <v>1610612763</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Grizzlies</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Toyota Center</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" t="n">
-        <v>173</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0.8196</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>0022501195</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C107" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="D107" t="n">
-        <v>1610612740</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Pelicans</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Target Center</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>173</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0.728</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C108" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" t="n">
-        <v>173</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0.7754</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C109" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D109" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" t="n">
-        <v>173</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0.6166</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C110" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" t="n">
-        <v>173</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0.8601</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C111" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" t="n">
-        <v>173</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0.7346</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C112" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D112" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" t="n">
-        <v>173</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0.7822</v>
+        <v>0.7893</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -539,7 +539,7 @@
         <v>162</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2584</v>
+        <v>0.2617</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>162</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2399</v>
+        <v>0.2567</v>
       </c>
     </row>
     <row r="4">
@@ -649,7 +649,7 @@
         <v>162</v>
       </c>
       <c r="M4" t="n">
-        <v>0.384</v>
+        <v>0.3857</v>
       </c>
     </row>
     <row r="5">
@@ -704,7 +704,7 @@
         <v>162</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4176</v>
+        <v>0.4423</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         <v>162</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7875</v>
+        <v>0.8055</v>
       </c>
     </row>
     <row r="7">
@@ -814,7 +814,7 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6159</v>
+        <v>0.6284</v>
       </c>
     </row>
     <row r="8">
@@ -869,7 +869,7 @@
         <v>162</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8313</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
         <v>162</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1983</v>
+        <v>0.2204</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>162</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2573</v>
+        <v>0.2913</v>
       </c>
     </row>
     <row r="11">
@@ -1034,7 +1034,7 @@
         <v>163</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6619</v>
+        <v>0.6374</v>
       </c>
     </row>
     <row r="12">
@@ -1089,7 +1089,7 @@
         <v>163</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5851</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="13">
@@ -1144,7 +1144,7 @@
         <v>163</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6382</v>
+        <v>0.6349</v>
       </c>
     </row>
     <row r="14">
@@ -1199,7 +1199,7 @@
         <v>163</v>
       </c>
       <c r="M14" t="n">
-        <v>0.29</v>
+        <v>0.3256</v>
       </c>
     </row>
     <row r="15">
@@ -1254,7 +1254,7 @@
         <v>163</v>
       </c>
       <c r="M15" t="n">
-        <v>0.62</v>
+        <v>0.6326000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1309,7 +1309,7 @@
         <v>163</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4431</v>
+        <v>0.4332</v>
       </c>
     </row>
     <row r="17">
@@ -1364,7 +1364,7 @@
         <v>164</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8113</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="18">
@@ -1419,7 +1419,7 @@
         <v>164</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4929</v>
+        <v>0.5008</v>
       </c>
     </row>
     <row r="19">
@@ -1474,7 +1474,7 @@
         <v>164</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2527</v>
+        <v>0.2655</v>
       </c>
     </row>
     <row r="20">
@@ -1529,7 +1529,7 @@
         <v>164</v>
       </c>
       <c r="M20" t="n">
-        <v>0.827</v>
+        <v>0.8279</v>
       </c>
     </row>
     <row r="21">
@@ -1584,7 +1584,7 @@
         <v>164</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8472</v>
+        <v>0.8365</v>
       </c>
     </row>
     <row r="22">
@@ -1639,7 +1639,7 @@
         <v>164</v>
       </c>
       <c r="M22" t="n">
-        <v>0.361</v>
+        <v>0.3516</v>
       </c>
     </row>
     <row r="23">
@@ -1694,7 +1694,7 @@
         <v>164</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2104</v>
+        <v>0.2252</v>
       </c>
     </row>
     <row r="24">
@@ -1749,7 +1749,7 @@
         <v>164</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4062</v>
+        <v>0.4054</v>
       </c>
     </row>
     <row r="25">
@@ -1804,7 +1804,7 @@
         <v>164</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4607</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="26">
@@ -1859,7 +1859,7 @@
         <v>165</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8063</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="27">
@@ -1914,7 +1914,7 @@
         <v>165</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5185</v>
+        <v>0.5111</v>
       </c>
     </row>
     <row r="28">
@@ -1969,7 +1969,7 @@
         <v>165</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4255</v>
+        <v>0.3993</v>
       </c>
     </row>
     <row r="29">
@@ -2024,7 +2024,7 @@
         <v>166</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7554</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="30">
@@ -2079,7 +2079,7 @@
         <v>166</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6526</v>
+        <v>0.6522</v>
       </c>
     </row>
     <row r="31">
@@ -2134,7 +2134,7 @@
         <v>166</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4233</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="32">
@@ -2189,7 +2189,7 @@
         <v>166</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6404</v>
+        <v>0.5969</v>
       </c>
     </row>
     <row r="33">
@@ -2244,7 +2244,7 @@
         <v>166</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8206</v>
+        <v>0.8161</v>
       </c>
     </row>
     <row r="34">
@@ -2299,7 +2299,7 @@
         <v>166</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5544</v>
+        <v>0.5785</v>
       </c>
     </row>
     <row r="35">
@@ -2354,7 +2354,7 @@
         <v>166</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4545</v>
+        <v>0.4845</v>
       </c>
     </row>
     <row r="36">
@@ -2409,7 +2409,7 @@
         <v>166</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8601</v>
+        <v>0.8542999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2464,7 +2464,7 @@
         <v>166</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2554</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="38">
@@ -2519,7 +2519,7 @@
         <v>166</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2165</v>
+        <v>0.2532</v>
       </c>
     </row>
     <row r="39">
@@ -2574,7 +2574,7 @@
         <v>166</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3916</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="40">
@@ -2629,7 +2629,7 @@
         <v>167</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4628</v>
+        <v>0.4533</v>
       </c>
     </row>
     <row r="41">
@@ -2684,7 +2684,7 @@
         <v>167</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3821</v>
+        <v>0.3559</v>
       </c>
     </row>
     <row r="42">
@@ -2739,7 +2739,7 @@
         <v>167</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2298</v>
+        <v>0.2339</v>
       </c>
     </row>
     <row r="43">
@@ -2794,7 +2794,7 @@
         <v>167</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7816</v>
+        <v>0.7623</v>
       </c>
     </row>
     <row r="44">
@@ -2849,7 +2849,7 @@
         <v>167</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7655</v>
+        <v>0.7638</v>
       </c>
     </row>
     <row r="45">
@@ -2904,7 +2904,7 @@
         <v>168</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3966</v>
+        <v>0.4021</v>
       </c>
     </row>
     <row r="46">
@@ -2959,7 +2959,7 @@
         <v>168</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6309</v>
+        <v>0.6389</v>
       </c>
     </row>
     <row r="47">
@@ -3014,7 +3014,7 @@
         <v>168</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4487</v>
+        <v>0.4696</v>
       </c>
     </row>
     <row r="48">
@@ -3069,7 +3069,7 @@
         <v>168</v>
       </c>
       <c r="M48" t="n">
-        <v>0.615</v>
+        <v>0.6005</v>
       </c>
     </row>
     <row r="49">
@@ -3124,7 +3124,7 @@
         <v>168</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2482</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="50">
@@ -3179,7 +3179,7 @@
         <v>168</v>
       </c>
       <c r="M50" t="n">
-        <v>0.713</v>
+        <v>0.6746</v>
       </c>
     </row>
     <row r="51">
@@ -3234,7 +3234,7 @@
         <v>168</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7484</v>
+        <v>0.7601</v>
       </c>
     </row>
     <row r="52">
@@ -3289,7 +3289,7 @@
         <v>168</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4419</v>
+        <v>0.4492</v>
       </c>
     </row>
     <row r="53">
@@ -3344,7 +3344,7 @@
         <v>168</v>
       </c>
       <c r="M53" t="n">
-        <v>0.83</v>
+        <v>0.8306</v>
       </c>
     </row>
     <row r="54">
@@ -3399,7 +3399,7 @@
         <v>168</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4736</v>
+        <v>0.4877</v>
       </c>
     </row>
     <row r="55">
@@ -3454,7 +3454,7 @@
         <v>169</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6866</v>
+        <v>0.6901</v>
       </c>
     </row>
     <row r="56">
@@ -3509,7 +3509,7 @@
         <v>169</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4612</v>
+        <v>0.4684</v>
       </c>
     </row>
     <row r="57">
@@ -3564,7 +3564,7 @@
         <v>169</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8193</v>
+        <v>0.8353</v>
       </c>
     </row>
     <row r="58">
@@ -3619,7 +3619,7 @@
         <v>169</v>
       </c>
       <c r="M58" t="n">
-        <v>0.794</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="59">
@@ -3674,7 +3674,7 @@
         <v>169</v>
       </c>
       <c r="M59" t="n">
-        <v>0.854</v>
+        <v>0.8574000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -3729,7 +3729,7 @@
         <v>169</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4015</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="61">
@@ -3784,7 +3784,7 @@
         <v>169</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8208</v>
+        <v>0.8192</v>
       </c>
     </row>
     <row r="62">
@@ -3839,7 +3839,7 @@
         <v>170</v>
       </c>
       <c r="M62" t="n">
-        <v>0.615</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="63">
@@ -3894,7 +3894,7 @@
         <v>170</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3966</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="64">
@@ -3949,7 +3949,7 @@
         <v>170</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5142</v>
+        <v>0.5078</v>
       </c>
     </row>
     <row r="65">
@@ -4004,7 +4004,7 @@
         <v>170</v>
       </c>
       <c r="M65" t="n">
-        <v>0.5268</v>
+        <v>0.5132</v>
       </c>
     </row>
     <row r="66">
@@ -4059,7 +4059,7 @@
         <v>170</v>
       </c>
       <c r="M66" t="n">
-        <v>0.6848</v>
+        <v>0.6654</v>
       </c>
     </row>
     <row r="67">
@@ -4114,7 +4114,7 @@
         <v>170</v>
       </c>
       <c r="M67" t="n">
-        <v>0.386</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="68">
@@ -4169,7 +4169,7 @@
         <v>171</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5455</v>
+        <v>0.5394</v>
       </c>
     </row>
     <row r="69">
@@ -4224,7 +4224,7 @@
         <v>171</v>
       </c>
       <c r="M69" t="n">
-        <v>0.2784</v>
+        <v>0.2914</v>
       </c>
     </row>
     <row r="70">
@@ -4279,7 +4279,7 @@
         <v>171</v>
       </c>
       <c r="M70" t="n">
-        <v>0.4476</v>
+        <v>0.4738</v>
       </c>
     </row>
     <row r="71">
@@ -4334,7 +4334,7 @@
         <v>171</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8023</v>
+        <v>0.8138</v>
       </c>
     </row>
     <row r="72">
@@ -4389,7 +4389,7 @@
         <v>171</v>
       </c>
       <c r="M72" t="n">
-        <v>0.3819</v>
+        <v>0.3712</v>
       </c>
     </row>
     <row r="73">
@@ -4444,7 +4444,7 @@
         <v>171</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7467</v>
+        <v>0.7448</v>
       </c>
     </row>
     <row r="74">
@@ -4499,7 +4499,7 @@
         <v>171</v>
       </c>
       <c r="M74" t="n">
-        <v>0.4217</v>
+        <v>0.4195</v>
       </c>
     </row>
     <row r="75">
@@ -4554,7 +4554,7 @@
         <v>171</v>
       </c>
       <c r="M75" t="n">
-        <v>0.5168</v>
+        <v>0.4832</v>
       </c>
     </row>
     <row r="76">
@@ -4609,7 +4609,7 @@
         <v>171</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="77">
@@ -4664,7 +4664,7 @@
         <v>171</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8489</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="78">
@@ -4719,7 +4719,7 @@
         <v>171</v>
       </c>
       <c r="M78" t="n">
-        <v>0.5102</v>
+        <v>0.5082</v>
       </c>
     </row>
     <row r="79">
@@ -4774,7 +4774,7 @@
         <v>171</v>
       </c>
       <c r="M79" t="n">
-        <v>0.5154</v>
+        <v>0.4937</v>
       </c>
     </row>
     <row r="80">
@@ -4829,7 +4829,7 @@
         <v>171</v>
       </c>
       <c r="M80" t="n">
-        <v>0.4771</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="81">
@@ -4884,7 +4884,7 @@
         <v>171</v>
       </c>
       <c r="M81" t="n">
-        <v>0.3732</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="82">
@@ -4939,7 +4939,7 @@
         <v>171</v>
       </c>
       <c r="M82" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6843</v>
       </c>
     </row>
     <row r="83">
@@ -4994,7 +4994,7 @@
         <v>173</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8043</v>
+        <v>0.8062</v>
       </c>
     </row>
     <row r="84">
@@ -5049,7 +5049,7 @@
         <v>173</v>
       </c>
       <c r="M84" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8524</v>
       </c>
     </row>
     <row r="85">
@@ -5104,7 +5104,7 @@
         <v>173</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2866</v>
+        <v>0.2813</v>
       </c>
     </row>
     <row r="86">
@@ -5159,7 +5159,7 @@
         <v>173</v>
       </c>
       <c r="M86" t="n">
-        <v>0.4992</v>
+        <v>0.5207000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5214,7 +5214,7 @@
         <v>173</v>
       </c>
       <c r="M87" t="n">
-        <v>0.6062</v>
+        <v>0.6074000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5269,7 +5269,7 @@
         <v>173</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7429</v>
+        <v>0.7481</v>
       </c>
     </row>
     <row r="89">
@@ -5324,7 +5324,7 @@
         <v>173</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8154</v>
+        <v>0.8300999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5379,7 +5379,7 @@
         <v>173</v>
       </c>
       <c r="M90" t="n">
-        <v>0.5155</v>
+        <v>0.5177</v>
       </c>
     </row>
     <row r="91">
@@ -5434,7 +5434,7 @@
         <v>173</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8487</v>
+        <v>0.8401</v>
       </c>
     </row>
     <row r="92">
@@ -5489,7 +5489,7 @@
         <v>173</v>
       </c>
       <c r="M92" t="n">
-        <v>0.7829</v>
+        <v>0.7802</v>
       </c>
     </row>
     <row r="93">
@@ -5544,7 +5544,7 @@
         <v>173</v>
       </c>
       <c r="M93" t="n">
-        <v>0.786</v>
+        <v>0.7723</v>
       </c>
     </row>
     <row r="94">
@@ -5599,7 +5599,7 @@
         <v>173</v>
       </c>
       <c r="M94" t="n">
-        <v>0.5974</v>
+        <v>0.6264</v>
       </c>
     </row>
     <row r="95">
@@ -5654,7 +5654,7 @@
         <v>173</v>
       </c>
       <c r="M95" t="n">
-        <v>0.868</v>
+        <v>0.8675</v>
       </c>
     </row>
     <row r="96">
@@ -5709,7 +5709,7 @@
         <v>173</v>
       </c>
       <c r="M96" t="n">
-        <v>0.7634</v>
+        <v>0.7131999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -5764,7 +5764,7 @@
         <v>173</v>
       </c>
       <c r="M97" t="n">
-        <v>0.7893</v>
+        <v>0.7571</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,52 +539,52 @@
         <v>162</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2617</v>
+        <v>0.2809</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501105</t>
+          <t>0022501108</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612764</v>
+        <v>1610612761</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612755</v>
+        <v>1610612758</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -594,52 +594,52 @@
         <v>162</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2567</v>
+        <v>0.8108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501106</t>
+          <t>0022501109</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -649,52 +649,52 @@
         <v>162</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3857</v>
+        <v>0.6433</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501107</t>
+          <t>0022501110</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612753</v>
+        <v>1610612745</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612737</v>
+        <v>1610612749</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -704,52 +704,52 @@
         <v>162</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4423</v>
+        <v>0.8431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501112</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612761</v>
+        <v>1610612762</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612758</v>
+        <v>1610612743</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -759,52 +759,52 @@
         <v>162</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8055</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501113</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612741</v>
+        <v>1610612744</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612754</v>
+        <v>1610612759</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -814,217 +814,217 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6284</v>
+        <v>0.2955</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612749</v>
+        <v>1610612756</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M8" t="n">
-        <v>0.841</v>
+        <v>0.6738</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612762</v>
+        <v>1610612765</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612743</v>
+        <v>1610612750</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2204</v>
+        <v>0.6118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612744</v>
+        <v>1610612760</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612759</v>
+        <v>1610612747</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2913</v>
+        <v>0.6456</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612766</v>
+        <v>1610612744</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612756</v>
+        <v>1610612739</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1034,52 +1034,52 @@
         <v>163</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6374</v>
+        <v>0.3258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612765</v>
+        <v>1610612757</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612750</v>
+        <v>1610612740</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1089,52 +1089,52 @@
         <v>163</v>
       </c>
       <c r="M12" t="n">
-        <v>0.61</v>
+        <v>0.6238</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>46114</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612747</v>
+        <v>1610612759</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1144,217 +1144,217 @@
         <v>163</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6349</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612739</v>
+        <v>1610612754</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3256</v>
+        <v>0.8083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612757</v>
+        <v>1610612755</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612740</v>
+        <v>1610612750</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.4968</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612746</v>
+        <v>1610612751</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612759</v>
+        <v>1610612737</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4332</v>
+        <v>0.2613</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1364,52 +1364,52 @@
         <v>164</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8005</v>
+        <v>0.8309</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612755</v>
+        <v>1610612745</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612750</v>
+        <v>1610612762</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1419,52 +1419,52 @@
         <v>164</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5008</v>
+        <v>0.8465</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1474,52 +1474,52 @@
         <v>164</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2655</v>
+        <v>0.3437</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612752</v>
+        <v>1610612749</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612741</v>
+        <v>1610612738</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1529,52 +1529,52 @@
         <v>164</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8279</v>
+        <v>0.2414</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612745</v>
+        <v>1610612742</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612762</v>
+        <v>1610612753</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1584,52 +1584,52 @@
         <v>164</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8365</v>
+        <v>0.4126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612763</v>
+        <v>1610612758</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612761</v>
+        <v>1610612740</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1639,382 +1639,382 @@
         <v>164</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3516</v>
+        <v>0.4512</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612738</v>
+        <v>1610612764</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2252</v>
+        <v>0.8145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612742</v>
+        <v>1610612743</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612753</v>
+        <v>1610612759</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4054</v>
+        <v>0.5407</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612758</v>
+        <v>1610612755</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612740</v>
+        <v>1610612765</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M25" t="n">
-        <v>0.477</v>
+        <v>0.4314</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612748</v>
+        <v>1610612738</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612764</v>
+        <v>1610612761</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M26" t="n">
-        <v>0.805</v>
+        <v>0.7509</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612759</v>
+        <v>1610612764</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5111</v>
+        <v>0.6414</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612755</v>
+        <v>1610612741</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612765</v>
+        <v>1610612756</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3993</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612738</v>
+        <v>1610612749</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612761</v>
+        <v>1610612763</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2024,52 +2024,52 @@
         <v>166</v>
       </c>
       <c r="M29" t="n">
-        <v>0.734</v>
+        <v>0.5809</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612751</v>
+        <v>1610612739</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612764</v>
+        <v>1610612754</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,52 +2079,52 @@
         <v>166</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6522</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612741</v>
+        <v>1610612750</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612756</v>
+        <v>1610612766</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2134,52 +2134,52 @@
         <v>166</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3958</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612749</v>
+        <v>1610612740</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612763</v>
+        <v>1610612753</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2189,52 +2189,52 @@
         <v>166</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5969</v>
+        <v>0.4825</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612739</v>
+        <v>1610612760</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2244,52 +2244,52 @@
         <v>166</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8161</v>
+        <v>0.8764999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612750</v>
+        <v>1610612742</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612766</v>
+        <v>1610612747</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2299,52 +2299,52 @@
         <v>166</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5785</v>
+        <v>0.2375</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612740</v>
+        <v>1610612758</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612753</v>
+        <v>1610612746</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2354,52 +2354,52 @@
         <v>166</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4845</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612762</v>
+        <v>1610612745</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2409,217 +2409,217 @@
         <v>166</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.4271</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612742</v>
+        <v>1610612737</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612747</v>
+        <v>1610612752</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2472</v>
+        <v>0.4818</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612758</v>
+        <v>1610612753</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612746</v>
+        <v>1610612765</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2532</v>
+        <v>0.3578</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612744</v>
+        <v>1610612763</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612745</v>
+        <v>1610612739</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M39" t="n">
-        <v>0.42</v>
+        <v>0.2417</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612737</v>
+        <v>1610612759</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612752</v>
+        <v>1610612755</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2629,52 +2629,52 @@
         <v>167</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4533</v>
+        <v>0.7973</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612753</v>
+        <v>1610612743</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612765</v>
+        <v>1610612757</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2684,217 +2684,217 @@
         <v>167</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3559</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612763</v>
+        <v>1610612764</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612739</v>
+        <v>1610612741</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2339</v>
+        <v>0.3973</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612759</v>
+        <v>1610612738</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612755</v>
+        <v>1610612766</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7623</v>
+        <v>0.6497000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612757</v>
+        <v>1610612749</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7638</v>
+        <v>0.4517</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612764</v>
+        <v>1610612761</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612741</v>
+        <v>1610612748</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2904,52 +2904,52 @@
         <v>168</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4021</v>
+        <v>0.5928</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612766</v>
+        <v>1610612750</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2959,52 +2959,52 @@
         <v>168</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6389</v>
+        <v>0.2912</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612751</v>
+        <v>1610612740</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612749</v>
+        <v>1610612762</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3014,52 +3014,52 @@
         <v>168</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4696</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612761</v>
+        <v>1610612744</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612748</v>
+        <v>1610612758</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3069,52 +3069,52 @@
         <v>168</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6005</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612750</v>
+        <v>1610612760</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3124,52 +3124,52 @@
         <v>168</v>
       </c>
       <c r="M49" t="n">
-        <v>0.269</v>
+        <v>0.4938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612740</v>
+        <v>1610612746</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612762</v>
+        <v>1610612742</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3179,52 +3179,52 @@
         <v>168</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6746</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612744</v>
+        <v>1610612756</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612758</v>
+        <v>1610612745</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3234,217 +3234,217 @@
         <v>168</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7601</v>
+        <v>0.4974</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612760</v>
+        <v>1610612737</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4492</v>
+        <v>0.7433999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612746</v>
+        <v>1610612753</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612742</v>
+        <v>1610612750</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8306</v>
+        <v>0.4481</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612756</v>
+        <v>1610612765</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4877</v>
+        <v>0.8486</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612739</v>
+        <v>1610612759</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612737</v>
+        <v>1610612757</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3454,52 +3454,52 @@
         <v>169</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6901</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612753</v>
+        <v>1610612743</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612750</v>
+        <v>1610612763</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3509,52 +3509,52 @@
         <v>169</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4684</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612765</v>
+        <v>1610612746</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612749</v>
+        <v>1610612760</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3564,52 +3564,52 @@
         <v>169</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8353</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612759</v>
+        <v>1610612756</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612757</v>
+        <v>1610612742</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3619,217 +3619,217 @@
         <v>169</v>
       </c>
       <c r="M58" t="n">
-        <v>0.787</v>
+        <v>0.8232</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612743</v>
+        <v>1610612761</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612763</v>
+        <v>1610612748</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M59" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.5928</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612746</v>
+        <v>1610612764</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612760</v>
+        <v>1610612741</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M60" t="n">
-        <v>0.376</v>
+        <v>0.3973</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612756</v>
+        <v>1610612751</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612742</v>
+        <v>1610612754</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8192</v>
+        <v>0.4649</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612761</v>
+        <v>1610612752</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612748</v>
+        <v>1610612738</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>170</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6004</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612741</v>
+        <v>1610612755</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,52 +3894,52 @@
         <v>170</v>
       </c>
       <c r="M63" t="n">
-        <v>0.402</v>
+        <v>0.6674</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612751</v>
+        <v>1610612744</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3949,217 +3949,217 @@
         <v>170</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5078</v>
+        <v>0.3879</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612752</v>
+        <v>1610612766</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M65" t="n">
-        <v>0.5132</v>
+        <v>0.5704</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612745</v>
+        <v>1610612764</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M66" t="n">
-        <v>0.6654</v>
+        <v>0.3052</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612744</v>
+        <v>1610612737</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M67" t="n">
-        <v>0.399</v>
+        <v>0.4694</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612766</v>
+        <v>1610612738</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612765</v>
+        <v>1610612740</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4169,52 +4169,52 @@
         <v>171</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5394</v>
+        <v>0.8102</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612764</v>
+        <v>1610612754</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4224,52 +4224,52 @@
         <v>171</v>
       </c>
       <c r="M69" t="n">
-        <v>0.2914</v>
+        <v>0.3781</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612737</v>
+        <v>1610612752</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612739</v>
+        <v>1610612761</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4279,52 +4279,52 @@
         <v>171</v>
       </c>
       <c r="M70" t="n">
-        <v>0.4738</v>
+        <v>0.7537</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612738</v>
+        <v>1610612741</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4334,52 +4334,52 @@
         <v>171</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8138</v>
+        <v>0.4311</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612754</v>
+        <v>1610612745</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4389,52 +4389,52 @@
         <v>171</v>
       </c>
       <c r="M72" t="n">
-        <v>0.3712</v>
+        <v>0.4918</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612752</v>
+        <v>1610612749</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612761</v>
+        <v>1610612751</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4444,52 +4444,52 @@
         <v>171</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7448</v>
+        <v>0.7552</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612741</v>
+        <v>1610612759</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612753</v>
+        <v>1610612742</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4499,52 +4499,52 @@
         <v>171</v>
       </c>
       <c r="M74" t="n">
-        <v>0.4195</v>
+        <v>0.8698</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612745</v>
+        <v>1610612762</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612750</v>
+        <v>1610612763</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>171</v>
       </c>
       <c r="M75" t="n">
-        <v>0.4832</v>
+        <v>0.4986</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612751</v>
+        <v>1610612760</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,52 +4609,52 @@
         <v>171</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7473</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612759</v>
+        <v>1610612757</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612742</v>
+        <v>1610612746</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4664,52 +4664,52 @@
         <v>171</v>
       </c>
       <c r="M77" t="n">
-        <v>0.8547</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612763</v>
+        <v>1610612744</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,52 +4719,52 @@
         <v>171</v>
       </c>
       <c r="M78" t="n">
-        <v>0.5082</v>
+        <v>0.3572</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612760</v>
+        <v>1610612756</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4774,217 +4774,217 @@
         <v>171</v>
       </c>
       <c r="M79" t="n">
-        <v>0.4937</v>
+        <v>0.6856</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612757</v>
+        <v>1610612738</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612746</v>
+        <v>1610612753</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M80" t="n">
-        <v>0.486</v>
+        <v>0.8224</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612758</v>
+        <v>1610612739</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M81" t="n">
-        <v>0.3736</v>
+        <v>0.8779</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612747</v>
+        <v>1610612754</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612756</v>
+        <v>1610612765</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M82" t="n">
-        <v>0.6843</v>
+        <v>0.2897</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612738</v>
+        <v>1610612748</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612753</v>
+        <v>1610612737</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4994,52 +4994,52 @@
         <v>173</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8062</v>
+        <v>0.5279</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5049,52 +5049,52 @@
         <v>173</v>
       </c>
       <c r="M84" t="n">
-        <v>0.8524</v>
+        <v>0.6431</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612754</v>
+        <v>1610612755</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612765</v>
+        <v>1610612749</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5104,52 +5104,52 @@
         <v>173</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2813</v>
+        <v>0.7427</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612748</v>
+        <v>1610612761</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612737</v>
+        <v>1610612751</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -5159,52 +5159,52 @@
         <v>173</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.8403</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612752</v>
+        <v>1610612742</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612766</v>
+        <v>1610612741</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -5214,52 +5214,52 @@
         <v>173</v>
       </c>
       <c r="M87" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5276</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612755</v>
+        <v>1610612745</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -5269,52 +5269,52 @@
         <v>173</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7481</v>
+        <v>0.8522</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C89" t="n">
-        <v>1610612761</v>
+        <v>1610612750</v>
       </c>
       <c r="D89" t="n">
-        <v>1610612751</v>
+        <v>1610612740</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -5324,52 +5324,52 @@
         <v>173</v>
       </c>
       <c r="M89" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.7965</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C90" t="n">
-        <v>1610612742</v>
+        <v>1610612760</v>
       </c>
       <c r="D90" t="n">
-        <v>1610612741</v>
+        <v>1610612756</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5379,52 +5379,52 @@
         <v>173</v>
       </c>
       <c r="M90" t="n">
-        <v>0.5177</v>
+        <v>0.8072</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C91" t="n">
-        <v>1610612745</v>
+        <v>1610612759</v>
       </c>
       <c r="D91" t="n">
-        <v>1610612763</v>
+        <v>1610612743</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -5434,52 +5434,52 @@
         <v>173</v>
       </c>
       <c r="M91" t="n">
-        <v>0.8401</v>
+        <v>0.6308</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0022501195</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C92" t="n">
-        <v>1610612750</v>
+        <v>1610612747</v>
       </c>
       <c r="D92" t="n">
-        <v>1610612740</v>
+        <v>1610612762</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -5489,52 +5489,52 @@
         <v>173</v>
       </c>
       <c r="M92" t="n">
-        <v>0.7802</v>
+        <v>0.8852</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0022501196</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C93" t="n">
-        <v>1610612760</v>
+        <v>1610612746</v>
       </c>
       <c r="D93" t="n">
-        <v>1610612756</v>
+        <v>1610612744</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -5544,52 +5544,52 @@
         <v>173</v>
       </c>
       <c r="M93" t="n">
-        <v>0.7723</v>
+        <v>0.7237</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0022501197</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C94" t="n">
-        <v>1610612759</v>
+        <v>1610612757</v>
       </c>
       <c r="D94" t="n">
-        <v>1610612743</v>
+        <v>1610612758</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -5599,172 +5599,7 @@
         <v>173</v>
       </c>
       <c r="M94" t="n">
-        <v>0.6264</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C95" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D95" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>173</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0.8675</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C96" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D96" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" t="n">
-        <v>173</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0.7131999999999999</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C97" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D97" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" t="n">
-        <v>173</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0.7571</v>
+        <v>0.7925</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,296 +490,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501003</t>
+          <t>0022501114</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612763</v>
+        <v>1610612766</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612752</v>
+        <v>1610612756</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2809</v>
+        <v>0.6563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501108</t>
+          <t>0022501115</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612761</v>
+        <v>1610612765</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612758</v>
+        <v>1610612750</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8108</v>
+        <v>0.6156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501109</t>
+          <t>0022501116</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612741</v>
+        <v>1610612760</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612754</v>
+        <v>1610612747</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6433</v>
+        <v>0.6505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501110</t>
+          <t>0022501117</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612745</v>
+        <v>1610612744</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612749</v>
+        <v>1610612739</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8431</v>
+        <v>0.3286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501112</t>
+          <t>0022501118</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612762</v>
+        <v>1610612757</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612743</v>
+        <v>1610612740</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M6" t="n">
-        <v>0.215</v>
+        <v>0.6238</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501113</t>
+          <t>0022501119</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612744</v>
+        <v>1610612746</v>
       </c>
       <c r="D7" t="n">
         <v>1610612759</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -799,38 +799,38 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2955</v>
+        <v>0.4406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C8" t="n">
         <v>1610612766</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612756</v>
+        <v>1610612754</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -866,30 +866,30 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6738</v>
+        <v>0.8094</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612765</v>
+        <v>1610612755</v>
       </c>
       <c r="D9" t="n">
         <v>1610612750</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -909,287 +909,287 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6118</v>
+        <v>0.4997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612760</v>
+        <v>1610612751</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612747</v>
+        <v>1610612737</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6456</v>
+        <v>0.2408</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612744</v>
+        <v>1610612752</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612739</v>
+        <v>1610612741</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3258</v>
+        <v>0.8353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612757</v>
+        <v>1610612745</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612740</v>
+        <v>1610612762</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6238</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612746</v>
+        <v>1610612763</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="n">
-        <v>0.433</v>
+        <v>0.3404</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612754</v>
+        <v>1610612738</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1199,52 +1199,52 @@
         <v>164</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8083</v>
+        <v>0.2364</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612755</v>
+        <v>1610612742</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612750</v>
+        <v>1610612753</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1254,52 +1254,52 @@
         <v>164</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4968</v>
+        <v>0.4283</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612751</v>
+        <v>1610612758</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1309,547 +1309,547 @@
         <v>164</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2613</v>
+        <v>0.4517</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612752</v>
+        <v>1610612748</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612741</v>
+        <v>1610612764</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8309</v>
+        <v>0.8227</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612745</v>
+        <v>1610612743</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612762</v>
+        <v>1610612759</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8465</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612763</v>
+        <v>1610612755</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612761</v>
+        <v>1610612765</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3437</v>
+        <v>0.4208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612749</v>
+        <v>1610612738</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2414</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612742</v>
+        <v>1610612751</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4126</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612758</v>
+        <v>1610612741</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612740</v>
+        <v>1610612756</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4512</v>
+        <v>0.4187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612748</v>
+        <v>1610612749</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612764</v>
+        <v>1610612763</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8145</v>
+        <v>0.5956</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5407</v>
+        <v>0.8391999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4314</v>
+        <v>0.5869</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612738</v>
+        <v>1610612740</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1859,52 +1859,52 @@
         <v>166</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7509</v>
+        <v>0.4869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612751</v>
+        <v>1610612760</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612764</v>
+        <v>1610612762</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1914,52 +1914,52 @@
         <v>166</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6414</v>
+        <v>0.8756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612741</v>
+        <v>1610612742</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612756</v>
+        <v>1610612747</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1969,52 +1969,52 @@
         <v>166</v>
       </c>
       <c r="M28" t="n">
-        <v>0.405</v>
+        <v>0.2509</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612749</v>
+        <v>1610612758</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612763</v>
+        <v>1610612746</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2024,52 +2024,52 @@
         <v>166</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5809</v>
+        <v>0.2654</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612739</v>
+        <v>1610612744</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612754</v>
+        <v>1610612745</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,657 +2079,657 @@
         <v>166</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8425</v>
+        <v>0.4182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5987</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612753</v>
+        <v>1610612765</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4825</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612760</v>
+        <v>1610612763</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612762</v>
+        <v>1610612739</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612742</v>
+        <v>1610612759</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2375</v>
+        <v>0.7842</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612758</v>
+        <v>1610612743</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2659</v>
+        <v>0.7934</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4271</v>
+        <v>0.3683</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612737</v>
+        <v>1610612738</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612752</v>
+        <v>1610612766</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4818</v>
+        <v>0.6617</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612765</v>
+        <v>1610612749</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3578</v>
+        <v>0.4631</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612763</v>
+        <v>1610612761</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612739</v>
+        <v>1610612748</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2417</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7973</v>
+        <v>0.3038</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612743</v>
+        <v>1610612740</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612757</v>
+        <v>1610612762</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7998</v>
+        <v>0.7101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612764</v>
+        <v>1610612744</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612741</v>
+        <v>1610612758</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2739,52 +2739,52 @@
         <v>168</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3973</v>
+        <v>0.7705</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612738</v>
+        <v>1610612747</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612766</v>
+        <v>1610612760</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2794,52 +2794,52 @@
         <v>168</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.4923</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612751</v>
+        <v>1610612746</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2849,52 +2849,52 @@
         <v>168</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4517</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612748</v>
+        <v>1610612745</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2904,382 +2904,382 @@
         <v>168</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5928</v>
+        <v>0.4786</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612754</v>
+        <v>1610612739</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2912</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612762</v>
+        <v>1610612750</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7075</v>
+        <v>0.4498</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612744</v>
+        <v>1610612765</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612758</v>
+        <v>1610612749</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7734</v>
+        <v>0.8466</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612747</v>
+        <v>1610612759</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612760</v>
+        <v>1610612757</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4938</v>
+        <v>0.7968</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612746</v>
+        <v>1610612743</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M50" t="n">
-        <v>0.831</v>
+        <v>0.8696</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612756</v>
+        <v>1610612746</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612745</v>
+        <v>1610612760</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4974</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612739</v>
+        <v>1610612756</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612737</v>
+        <v>1610612742</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3289,408 +3289,408 @@
         <v>169</v>
       </c>
       <c r="M52" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612750</v>
+        <v>1610612748</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4481</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8486</v>
+        <v>0.3683</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612759</v>
+        <v>1610612751</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612757</v>
+        <v>1610612754</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M55" t="n">
-        <v>0.794</v>
+        <v>0.4745</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612763</v>
+        <v>1610612738</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8667</v>
+        <v>0.5072</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612760</v>
+        <v>1610612755</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3901</v>
+        <v>0.6521</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612756</v>
+        <v>1610612744</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612742</v>
+        <v>1610612747</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8232</v>
+        <v>0.3962</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612748</v>
+        <v>1610612765</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M59" t="n">
-        <v>0.5928</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C60" t="n">
         <v>1610612764</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612741</v>
+        <v>1610612748</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3726,140 +3726,140 @@
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3973</v>
+        <v>0.2848</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612751</v>
+        <v>1610612737</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612754</v>
+        <v>1610612739</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4649</v>
+        <v>0.4789</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612738</v>
+        <v>1610612740</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M62" t="n">
-        <v>0.521</v>
+        <v>0.8145</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612745</v>
+        <v>1610612754</v>
       </c>
       <c r="D63" t="n">
         <v>1610612755</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3879,122 +3879,122 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M63" t="n">
-        <v>0.6674</v>
+        <v>0.3755</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612744</v>
+        <v>1610612752</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3879</v>
+        <v>0.7599</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612766</v>
+        <v>1610612741</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612765</v>
+        <v>1610612753</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4004,52 +4004,52 @@
         <v>171</v>
       </c>
       <c r="M65" t="n">
-        <v>0.5704</v>
+        <v>0.4289</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4059,52 +4059,52 @@
         <v>171</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3052</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612737</v>
+        <v>1610612749</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612739</v>
+        <v>1610612751</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4114,52 +4114,52 @@
         <v>171</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4694</v>
+        <v>0.7513</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612738</v>
+        <v>1610612759</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4169,52 +4169,52 @@
         <v>171</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8102</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612755</v>
+        <v>1610612763</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4224,52 +4224,52 @@
         <v>171</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3781</v>
+        <v>0.5028</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612752</v>
+        <v>1610612743</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612761</v>
+        <v>1610612760</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4279,52 +4279,52 @@
         <v>171</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7537</v>
+        <v>0.5199</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612741</v>
+        <v>1610612757</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612753</v>
+        <v>1610612746</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4334,52 +4334,52 @@
         <v>171</v>
       </c>
       <c r="M71" t="n">
-        <v>0.4311</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612745</v>
+        <v>1610612758</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612750</v>
+        <v>1610612744</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4389,52 +4389,52 @@
         <v>171</v>
       </c>
       <c r="M72" t="n">
-        <v>0.4918</v>
+        <v>0.3684</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612749</v>
+        <v>1610612747</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612751</v>
+        <v>1610612756</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4444,382 +4444,382 @@
         <v>171</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7552</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612759</v>
+        <v>1610612738</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612742</v>
+        <v>1610612753</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8698</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612762</v>
+        <v>1610612739</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612763</v>
+        <v>1610612764</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M75" t="n">
-        <v>0.4986</v>
+        <v>0.8774</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612743</v>
+        <v>1610612754</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612760</v>
+        <v>1610612765</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M76" t="n">
-        <v>0.525</v>
+        <v>0.2845</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612757</v>
+        <v>1610612748</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612746</v>
+        <v>1610612737</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M77" t="n">
-        <v>0.471</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612758</v>
+        <v>1610612752</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M78" t="n">
-        <v>0.3572</v>
+        <v>0.6337</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612756</v>
+        <v>1610612749</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M79" t="n">
-        <v>0.6856</v>
+        <v>0.7655</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4829,52 +4829,52 @@
         <v>173</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8224</v>
+        <v>0.8372000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612739</v>
+        <v>1610612742</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612764</v>
+        <v>1610612741</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -4884,52 +4884,52 @@
         <v>173</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8779</v>
+        <v>0.5312</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612754</v>
+        <v>1610612745</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612765</v>
+        <v>1610612763</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -4939,52 +4939,52 @@
         <v>173</v>
       </c>
       <c r="M82" t="n">
-        <v>0.2897</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C83" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="D83" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4994,52 +4994,52 @@
         <v>173</v>
       </c>
       <c r="M83" t="n">
-        <v>0.5279</v>
+        <v>0.7959000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C84" t="n">
-        <v>1610612752</v>
+        <v>1610612760</v>
       </c>
       <c r="D84" t="n">
-        <v>1610612766</v>
+        <v>1610612756</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5049,52 +5049,52 @@
         <v>173</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6431</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C85" t="n">
-        <v>1610612755</v>
+        <v>1610612759</v>
       </c>
       <c r="D85" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5104,52 +5104,52 @@
         <v>173</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7427</v>
+        <v>0.6418</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C86" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="D86" t="n">
-        <v>1610612751</v>
+        <v>1610612762</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -5159,52 +5159,52 @@
         <v>173</v>
       </c>
       <c r="M86" t="n">
-        <v>0.8403</v>
+        <v>0.8854</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C87" t="n">
-        <v>1610612742</v>
+        <v>1610612746</v>
       </c>
       <c r="D87" t="n">
-        <v>1610612741</v>
+        <v>1610612744</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -5214,52 +5214,52 @@
         <v>173</v>
       </c>
       <c r="M87" t="n">
-        <v>0.5276</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C88" t="n">
-        <v>1610612745</v>
+        <v>1610612757</v>
       </c>
       <c r="D88" t="n">
-        <v>1610612763</v>
+        <v>1610612758</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -5269,337 +5269,7 @@
         <v>173</v>
       </c>
       <c r="M88" t="n">
-        <v>0.8522</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>0022501195</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C89" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="D89" t="n">
-        <v>1610612740</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Pelicans</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Target Center</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>173</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0.7965</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C90" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D90" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>173</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0.8072</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C91" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>173</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0.6308</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C92" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D92" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>173</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0.8852</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B93" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C93" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D93" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>173</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0.7237</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C94" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D94" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>173</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0.7925</v>
+        <v>0.7869</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,17 +490,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501114</t>
+          <t>0022501120</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C2" t="n">
         <v>1610612766</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612756</v>
+        <v>1610612754</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,30 +536,30 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6563</v>
+        <v>0.7909</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501115</t>
+          <t>0022501121</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612765</v>
+        <v>1610612755</v>
       </c>
       <c r="D3" t="n">
         <v>1610612750</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,287 +579,287 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6156</v>
+        <v>0.4966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501116</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612760</v>
+        <v>1610612751</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612747</v>
+        <v>1610612737</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6505</v>
+        <v>0.2408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501117</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612744</v>
+        <v>1610612752</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612739</v>
+        <v>1610612741</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3286</v>
+        <v>0.8353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501118</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612757</v>
+        <v>1610612745</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612740</v>
+        <v>1610612762</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6238</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501119</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612746</v>
+        <v>1610612763</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4406</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612766</v>
+        <v>1610612749</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612754</v>
+        <v>1610612738</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -869,52 +869,52 @@
         <v>164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8094</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612755</v>
+        <v>1610612742</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612750</v>
+        <v>1610612753</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -924,52 +924,52 @@
         <v>164</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4997</v>
+        <v>0.4283</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612751</v>
+        <v>1610612758</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -979,547 +979,547 @@
         <v>164</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2408</v>
+        <v>0.4394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612752</v>
+        <v>1610612748</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612741</v>
+        <v>1610612764</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8353</v>
+        <v>0.8227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612745</v>
+        <v>1610612743</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612762</v>
+        <v>1610612759</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8608</v>
+        <v>0.5317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612763</v>
+        <v>1610612755</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612761</v>
+        <v>1610612765</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3404</v>
+        <v>0.4262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612749</v>
+        <v>1610612738</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2364</v>
+        <v>0.7649</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612742</v>
+        <v>1610612751</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4283</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612758</v>
+        <v>1610612741</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612740</v>
+        <v>1610612756</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4517</v>
+        <v>0.4165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612748</v>
+        <v>1610612749</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612764</v>
+        <v>1610612763</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8227</v>
+        <v>0.5796</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612743</v>
+        <v>1610612739</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M18" t="n">
-        <v>0.531</v>
+        <v>0.8366</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4208</v>
+        <v>0.6048</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612738</v>
+        <v>1610612740</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1529,52 +1529,52 @@
         <v>166</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7668</v>
+        <v>0.4877</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612751</v>
+        <v>1610612760</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612764</v>
+        <v>1610612762</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1584,52 +1584,52 @@
         <v>166</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6531</v>
+        <v>0.8764999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612741</v>
+        <v>1610612742</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612756</v>
+        <v>1610612747</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1639,52 +1639,52 @@
         <v>166</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4187</v>
+        <v>0.2566</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612749</v>
+        <v>1610612758</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612763</v>
+        <v>1610612746</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1694,52 +1694,52 @@
         <v>166</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5956</v>
+        <v>0.2752</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612739</v>
+        <v>1610612744</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612754</v>
+        <v>1610612745</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1749,657 +1749,657 @@
         <v>166</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.4171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5869</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612753</v>
+        <v>1610612765</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4869</v>
+        <v>0.3793</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612760</v>
+        <v>1610612763</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612762</v>
+        <v>1610612739</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8756</v>
+        <v>0.2399</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612742</v>
+        <v>1610612759</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2509</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612758</v>
+        <v>1610612743</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2654</v>
+        <v>0.7914</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46117</v>
+        <v>46119</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612745</v>
+        <v>1610612741</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4182</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612737</v>
+        <v>1610612738</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612752</v>
+        <v>1610612766</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4839</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612765</v>
+        <v>1610612749</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M32" t="n">
-        <v>0.383</v>
+        <v>0.4767</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612763</v>
+        <v>1610612761</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612739</v>
+        <v>1610612748</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2329</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612759</v>
+        <v>1610612754</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612755</v>
+        <v>1610612750</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7842</v>
+        <v>0.3052</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612743</v>
+        <v>1610612740</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612757</v>
+        <v>1610612762</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7934</v>
+        <v>0.7009</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612764</v>
+        <v>1610612744</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612741</v>
+        <v>1610612758</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2409,52 +2409,52 @@
         <v>168</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3683</v>
+        <v>0.7764</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612738</v>
+        <v>1610612747</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612766</v>
+        <v>1610612760</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2464,52 +2464,52 @@
         <v>168</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6617</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612751</v>
+        <v>1610612746</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2519,52 +2519,52 @@
         <v>168</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4631</v>
+        <v>0.8181</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612748</v>
+        <v>1610612745</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2574,382 +2574,382 @@
         <v>168</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6151</v>
+        <v>0.4713</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612754</v>
+        <v>1610612739</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612750</v>
+        <v>1610612737</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3038</v>
+        <v>0.7281</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612740</v>
+        <v>1610612753</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612762</v>
+        <v>1610612750</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7101</v>
+        <v>0.4509</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612744</v>
+        <v>1610612765</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612758</v>
+        <v>1610612749</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7705</v>
+        <v>0.8626</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612747</v>
+        <v>1610612759</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612760</v>
+        <v>1610612757</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4923</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612746</v>
+        <v>1610612743</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8696</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612756</v>
+        <v>1610612746</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612745</v>
+        <v>1610612760</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4786</v>
+        <v>0.3838</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612739</v>
+        <v>1610612756</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612737</v>
+        <v>1610612742</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2959,408 +2959,408 @@
         <v>169</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7337</v>
+        <v>0.8035</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612750</v>
+        <v>1610612748</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4498</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8466</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612759</v>
+        <v>1610612751</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612757</v>
+        <v>1610612754</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7968</v>
+        <v>0.4698</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612743</v>
+        <v>1610612752</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612763</v>
+        <v>1610612738</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8696</v>
+        <v>0.5072</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612746</v>
+        <v>1610612745</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612760</v>
+        <v>1610612755</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3901</v>
+        <v>0.6521</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612756</v>
+        <v>1610612744</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612742</v>
+        <v>1610612747</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8095</v>
+        <v>0.4121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612748</v>
+        <v>1610612765</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6151</v>
+        <v>0.5456</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C54" t="n">
         <v>1610612764</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612741</v>
+        <v>1610612748</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3396,140 +3396,140 @@
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3683</v>
+        <v>0.2848</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612751</v>
+        <v>1610612737</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612754</v>
+        <v>1610612739</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4745</v>
+        <v>0.4766</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612738</v>
+        <v>1610612740</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5072</v>
+        <v>0.8076</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612745</v>
+        <v>1610612754</v>
       </c>
       <c r="D57" t="n">
         <v>1610612755</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3549,122 +3549,122 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M57" t="n">
-        <v>0.6521</v>
+        <v>0.3835</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612744</v>
+        <v>1610612752</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612747</v>
+        <v>1610612761</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3962</v>
+        <v>0.7599</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612766</v>
+        <v>1610612741</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612765</v>
+        <v>1610612753</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3674,52 +3674,52 @@
         <v>171</v>
       </c>
       <c r="M59" t="n">
-        <v>0.5647</v>
+        <v>0.4289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612764</v>
+        <v>1610612745</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3729,52 +3729,52 @@
         <v>171</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2848</v>
+        <v>0.5078</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612737</v>
+        <v>1610612749</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612739</v>
+        <v>1610612751</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3784,52 +3784,52 @@
         <v>171</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4789</v>
+        <v>0.7073</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612738</v>
+        <v>1610612759</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>171</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8145</v>
+        <v>0.8675</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612754</v>
+        <v>1610612762</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612755</v>
+        <v>1610612763</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,52 +3894,52 @@
         <v>171</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3755</v>
+        <v>0.5236</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612752</v>
+        <v>1610612743</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612761</v>
+        <v>1610612760</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3949,52 +3949,52 @@
         <v>171</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7599</v>
+        <v>0.4834</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612741</v>
+        <v>1610612757</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612753</v>
+        <v>1610612746</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4004,52 +4004,52 @@
         <v>171</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4289</v>
+        <v>0.4885</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612745</v>
+        <v>1610612758</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612750</v>
+        <v>1610612744</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4059,52 +4059,52 @@
         <v>171</v>
       </c>
       <c r="M66" t="n">
-        <v>0.5125</v>
+        <v>0.3708</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612749</v>
+        <v>1610612747</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612751</v>
+        <v>1610612756</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4114,382 +4114,382 @@
         <v>171</v>
       </c>
       <c r="M67" t="n">
-        <v>0.7513</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612759</v>
+        <v>1610612738</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612742</v>
+        <v>1610612753</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8676</v>
+        <v>0.8280999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612762</v>
+        <v>1610612739</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612763</v>
+        <v>1610612764</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5028</v>
+        <v>0.8808</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612743</v>
+        <v>1610612754</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612760</v>
+        <v>1610612765</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5199</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612757</v>
+        <v>1610612748</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612746</v>
+        <v>1610612737</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M71" t="n">
-        <v>0.471</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612758</v>
+        <v>1610612752</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612744</v>
+        <v>1610612766</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M72" t="n">
-        <v>0.3684</v>
+        <v>0.6487000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612756</v>
+        <v>1610612749</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M73" t="n">
-        <v>0.6829</v>
+        <v>0.7801</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4499,52 +4499,52 @@
         <v>173</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8302</v>
+        <v>0.8378</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612739</v>
+        <v>1610612742</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612764</v>
+        <v>1610612741</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>173</v>
       </c>
       <c r="M75" t="n">
-        <v>0.8774</v>
+        <v>0.5291</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612754</v>
+        <v>1610612745</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612765</v>
+        <v>1610612763</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,52 +4609,52 @@
         <v>173</v>
       </c>
       <c r="M76" t="n">
-        <v>0.2845</v>
+        <v>0.8663</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612748</v>
+        <v>1610612750</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612737</v>
+        <v>1610612740</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4664,52 +4664,52 @@
         <v>173</v>
       </c>
       <c r="M77" t="n">
-        <v>0.5011</v>
+        <v>0.7988</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612752</v>
+        <v>1610612760</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612766</v>
+        <v>1610612756</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,52 +4719,52 @@
         <v>173</v>
       </c>
       <c r="M78" t="n">
-        <v>0.6337</v>
+        <v>0.8250999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612755</v>
+        <v>1610612759</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612749</v>
+        <v>1610612743</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4774,52 +4774,52 @@
         <v>173</v>
       </c>
       <c r="M79" t="n">
-        <v>0.7655</v>
+        <v>0.6569</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612761</v>
+        <v>1610612747</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612751</v>
+        <v>1610612762</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4829,52 +4829,52 @@
         <v>173</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.8748</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C81" t="n">
-        <v>1610612742</v>
+        <v>1610612746</v>
       </c>
       <c r="D81" t="n">
-        <v>1610612741</v>
+        <v>1610612744</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -4884,52 +4884,52 @@
         <v>173</v>
       </c>
       <c r="M81" t="n">
-        <v>0.5312</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C82" t="n">
-        <v>1610612745</v>
+        <v>1610612757</v>
       </c>
       <c r="D82" t="n">
-        <v>1610612763</v>
+        <v>1610612758</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -4939,337 +4939,7 @@
         <v>173</v>
       </c>
       <c r="M82" t="n">
-        <v>0.864</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>0022501195</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C83" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1610612740</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Pelicans</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>NOP</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Target Center</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Minneapolis</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>173</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0.7959000000000001</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>0022501196</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C84" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="D84" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Paycom Center</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="n">
-        <v>173</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0.803</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>0022501197</t>
-        </is>
-      </c>
-      <c r="B85" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C85" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Frost Bank Center</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" t="n">
-        <v>173</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0.6418</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>0022501198</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C86" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Crypto.com Arena</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" t="n">
-        <v>173</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0.8854</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B87" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C87" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D87" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>173</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0.7236</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C88" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>173</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0.7869</v>
+        <v>0.7923</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,46 +490,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501120</t>
+          <t>0022501122</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612766</v>
+        <v>1610612751</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612754</v>
+        <v>1610612737</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -539,52 +539,52 @@
         <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7909</v>
+        <v>0.2408</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501121</t>
+          <t>0022501123</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612755</v>
+        <v>1610612752</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612750</v>
+        <v>1610612741</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -594,52 +594,52 @@
         <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4966</v>
+        <v>0.8217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501124</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612751</v>
+        <v>1610612745</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612737</v>
+        <v>1610612762</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -649,52 +649,52 @@
         <v>164</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2408</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501125</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612752</v>
+        <v>1610612763</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612741</v>
+        <v>1610612761</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -704,52 +704,52 @@
         <v>164</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8353</v>
+        <v>0.3404</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501126</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612745</v>
+        <v>1610612749</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612762</v>
+        <v>1610612738</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -759,52 +759,52 @@
         <v>164</v>
       </c>
       <c r="M6" t="n">
-        <v>0.858</v>
+        <v>0.2187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612761</v>
+        <v>1610612753</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -814,52 +814,52 @@
         <v>164</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3338</v>
+        <v>0.4283</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612749</v>
+        <v>1610612758</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612738</v>
+        <v>1610612740</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -869,162 +869,162 @@
         <v>164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2218</v>
+        <v>0.4394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612742</v>
+        <v>1610612748</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612753</v>
+        <v>1610612764</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4283</v>
+        <v>0.8239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612758</v>
+        <v>1610612743</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612740</v>
+        <v>1610612759</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4394</v>
+        <v>0.5317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612764</v>
+        <v>1610612765</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1034,162 +1034,162 @@
         <v>165</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8227</v>
+        <v>0.4629</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5317</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612755</v>
+        <v>1610612751</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612765</v>
+        <v>1610612764</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4262</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612738</v>
+        <v>1610612741</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612761</v>
+        <v>1610612756</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1199,52 +1199,52 @@
         <v>166</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7649</v>
+        <v>0.4165</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612751</v>
+        <v>1610612749</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612764</v>
+        <v>1610612763</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1254,52 +1254,52 @@
         <v>166</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6531</v>
+        <v>0.5717</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612741</v>
+        <v>1610612739</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612756</v>
+        <v>1610612754</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1309,52 +1309,52 @@
         <v>166</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4165</v>
+        <v>0.8366</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612749</v>
+        <v>1610612750</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612763</v>
+        <v>1610612766</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1364,52 +1364,52 @@
         <v>166</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5796</v>
+        <v>0.6048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612739</v>
+        <v>1610612740</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612754</v>
+        <v>1610612753</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1419,52 +1419,52 @@
         <v>166</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8366</v>
+        <v>0.4877</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612750</v>
+        <v>1610612760</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612766</v>
+        <v>1610612762</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1474,52 +1474,52 @@
         <v>166</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6048</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612740</v>
+        <v>1610612742</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612753</v>
+        <v>1610612747</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1529,52 +1529,52 @@
         <v>166</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4877</v>
+        <v>0.2566</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612760</v>
+        <v>1610612758</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612762</v>
+        <v>1610612746</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1584,52 +1584,52 @@
         <v>166</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.2725</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612742</v>
+        <v>1610612744</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612747</v>
+        <v>1610612745</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1639,162 +1639,162 @@
         <v>166</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2566</v>
+        <v>0.4125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612758</v>
+        <v>1610612737</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612746</v>
+        <v>1610612752</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2752</v>
+        <v>0.5056</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612745</v>
+        <v>1610612765</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4171</v>
+        <v>0.3793</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612737</v>
+        <v>1610612763</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612752</v>
+        <v>1610612739</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1804,52 +1804,52 @@
         <v>167</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4839</v>
+        <v>0.2399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612753</v>
+        <v>1610612759</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612765</v>
+        <v>1610612755</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1859,52 +1859,52 @@
         <v>167</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3793</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612763</v>
+        <v>1610612743</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612739</v>
+        <v>1610612757</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1914,162 +1914,162 @@
         <v>167</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2399</v>
+        <v>0.7914</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612759</v>
+        <v>1610612764</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612755</v>
+        <v>1610612741</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7985</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612743</v>
+        <v>1610612738</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612757</v>
+        <v>1610612766</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7914</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612741</v>
+        <v>1610612749</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,52 +2079,52 @@
         <v>168</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3652</v>
+        <v>0.4767</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612738</v>
+        <v>1610612761</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2134,52 +2134,52 @@
         <v>168</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6915</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612749</v>
+        <v>1610612750</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2189,52 +2189,52 @@
         <v>168</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4767</v>
+        <v>0.3033</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612761</v>
+        <v>1610612740</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612748</v>
+        <v>1610612762</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2244,52 +2244,52 @@
         <v>168</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6151</v>
+        <v>0.7009</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612754</v>
+        <v>1610612744</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612750</v>
+        <v>1610612758</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2299,52 +2299,52 @@
         <v>168</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3052</v>
+        <v>0.7771</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612740</v>
+        <v>1610612747</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612762</v>
+        <v>1610612760</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2354,52 +2354,52 @@
         <v>168</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7009</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612744</v>
+        <v>1610612746</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612758</v>
+        <v>1610612742</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2409,52 +2409,52 @@
         <v>168</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7764</v>
+        <v>0.8211000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612747</v>
+        <v>1610612756</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612760</v>
+        <v>1610612745</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2464,162 +2464,162 @@
         <v>168</v>
       </c>
       <c r="M37" t="n">
-        <v>0.483</v>
+        <v>0.4713</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612746</v>
+        <v>1610612739</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612742</v>
+        <v>1610612737</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8181</v>
+        <v>0.7281</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612756</v>
+        <v>1610612753</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4713</v>
+        <v>0.4514</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612739</v>
+        <v>1610612765</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612737</v>
+        <v>1610612749</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2629,52 +2629,52 @@
         <v>169</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7281</v>
+        <v>0.8626</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612753</v>
+        <v>1610612759</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612750</v>
+        <v>1610612757</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2684,52 +2684,52 @@
         <v>169</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4509</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612765</v>
+        <v>1610612743</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612749</v>
+        <v>1610612763</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2739,52 +2739,52 @@
         <v>169</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8626</v>
+        <v>0.8696</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612759</v>
+        <v>1610612746</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612757</v>
+        <v>1610612760</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2794,52 +2794,52 @@
         <v>169</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.3838</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612743</v>
+        <v>1610612756</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2849,162 +2849,162 @@
         <v>169</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8696</v>
+        <v>0.8061</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612746</v>
+        <v>1610612761</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612760</v>
+        <v>1610612748</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3838</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612756</v>
+        <v>1610612764</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612742</v>
+        <v>1610612741</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8035</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612761</v>
+        <v>1610612751</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612748</v>
+        <v>1610612754</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3014,52 +3014,52 @@
         <v>170</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6151</v>
+        <v>0.4698</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612764</v>
+        <v>1610612752</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612741</v>
+        <v>1610612738</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3069,52 +3069,52 @@
         <v>170</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3652</v>
+        <v>0.4961</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612751</v>
+        <v>1610612745</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612754</v>
+        <v>1610612755</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3124,52 +3124,52 @@
         <v>170</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4698</v>
+        <v>0.6545</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612752</v>
+        <v>1610612744</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612738</v>
+        <v>1610612747</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3179,162 +3179,162 @@
         <v>170</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5072</v>
+        <v>0.4078</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612745</v>
+        <v>1610612766</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612755</v>
+        <v>1610612765</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6521</v>
+        <v>0.5456</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612744</v>
+        <v>1610612764</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612747</v>
+        <v>1610612748</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4121</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C53" t="n">
-        <v>1610612766</v>
+        <v>1610612737</v>
       </c>
       <c r="D53" t="n">
-        <v>1610612765</v>
+        <v>1610612739</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3344,52 +3344,52 @@
         <v>171</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5456</v>
+        <v>0.4766</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C54" t="n">
-        <v>1610612764</v>
+        <v>1610612738</v>
       </c>
       <c r="D54" t="n">
-        <v>1610612748</v>
+        <v>1610612740</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3399,52 +3399,52 @@
         <v>171</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2848</v>
+        <v>0.8076</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022501173</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C55" t="n">
-        <v>1610612737</v>
+        <v>1610612754</v>
       </c>
       <c r="D55" t="n">
-        <v>1610612739</v>
+        <v>1610612755</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3454,52 +3454,52 @@
         <v>171</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4766</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0022501174</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C56" t="n">
-        <v>1610612738</v>
+        <v>1610612752</v>
       </c>
       <c r="D56" t="n">
-        <v>1610612740</v>
+        <v>1610612761</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3509,52 +3509,52 @@
         <v>171</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8076</v>
+        <v>0.7149</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0022501175</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C57" t="n">
-        <v>1610612754</v>
+        <v>1610612741</v>
       </c>
       <c r="D57" t="n">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3564,52 +3564,52 @@
         <v>171</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3835</v>
+        <v>0.4289</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0022501176</t>
+          <t>0022501178</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C58" t="n">
-        <v>1610612752</v>
+        <v>1610612745</v>
       </c>
       <c r="D58" t="n">
-        <v>1610612761</v>
+        <v>1610612750</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3619,52 +3619,52 @@
         <v>171</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7599</v>
+        <v>0.5078</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022501177</t>
+          <t>0022501179</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C59" t="n">
-        <v>1610612741</v>
+        <v>1610612749</v>
       </c>
       <c r="D59" t="n">
-        <v>1610612753</v>
+        <v>1610612751</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3674,52 +3674,52 @@
         <v>171</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4289</v>
+        <v>0.7073</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022501178</t>
+          <t>0022501180</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C60" t="n">
-        <v>1610612745</v>
+        <v>1610612759</v>
       </c>
       <c r="D60" t="n">
-        <v>1610612750</v>
+        <v>1610612742</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3729,52 +3729,52 @@
         <v>171</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5078</v>
+        <v>0.8675</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0022501179</t>
+          <t>0022501181</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C61" t="n">
-        <v>1610612749</v>
+        <v>1610612762</v>
       </c>
       <c r="D61" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Delta Center</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3784,52 +3784,52 @@
         <v>171</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7073</v>
+        <v>0.5168</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0022501180</t>
+          <t>0022501182</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C62" t="n">
-        <v>1610612759</v>
+        <v>1610612743</v>
       </c>
       <c r="D62" t="n">
-        <v>1610612742</v>
+        <v>1610612760</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3839,52 +3839,52 @@
         <v>171</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8675</v>
+        <v>0.4834</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0022501181</t>
+          <t>0022501183</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C63" t="n">
-        <v>1610612762</v>
+        <v>1610612757</v>
       </c>
       <c r="D63" t="n">
-        <v>1610612763</v>
+        <v>1610612746</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Delta Center</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Salt Lake City</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3894,52 +3894,52 @@
         <v>171</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5236</v>
+        <v>0.4885</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0022501182</t>
+          <t>0022501184</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C64" t="n">
-        <v>1610612743</v>
+        <v>1610612758</v>
       </c>
       <c r="D64" t="n">
-        <v>1610612760</v>
+        <v>1610612744</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3949,52 +3949,52 @@
         <v>171</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4834</v>
+        <v>0.3708</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0022501183</t>
+          <t>0022501185</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C65" t="n">
-        <v>1610612757</v>
+        <v>1610612747</v>
       </c>
       <c r="D65" t="n">
-        <v>1610612746</v>
+        <v>1610612756</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Moda Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4004,162 +4004,162 @@
         <v>171</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4885</v>
+        <v>0.6776</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0022501184</t>
+          <t>0022501186</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C66" t="n">
-        <v>1610612758</v>
+        <v>1610612738</v>
       </c>
       <c r="D66" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3708</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022501185</t>
+          <t>0022501187</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="C67" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="D67" t="n">
-        <v>1610612756</v>
+        <v>1610612764</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M67" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.8808</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0022501186</t>
+          <t>0022501188</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C68" t="n">
-        <v>1610612738</v>
+        <v>1610612754</v>
       </c>
       <c r="D68" t="n">
-        <v>1610612753</v>
+        <v>1610612765</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4169,52 +4169,52 @@
         <v>173</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0022501187</t>
+          <t>0022501189</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C69" t="n">
-        <v>1610612739</v>
+        <v>1610612748</v>
       </c>
       <c r="D69" t="n">
-        <v>1610612764</v>
+        <v>1610612737</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4224,52 +4224,52 @@
         <v>173</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8808</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022501188</t>
+          <t>0022501190</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C70" t="n">
-        <v>1610612754</v>
+        <v>1610612752</v>
       </c>
       <c r="D70" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4279,52 +4279,52 @@
         <v>173</v>
       </c>
       <c r="M70" t="n">
-        <v>0.309</v>
+        <v>0.6089</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0022501189</t>
+          <t>0022501191</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C71" t="n">
-        <v>1610612748</v>
+        <v>1610612755</v>
       </c>
       <c r="D71" t="n">
-        <v>1610612737</v>
+        <v>1610612749</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4334,52 +4334,52 @@
         <v>173</v>
       </c>
       <c r="M71" t="n">
-        <v>0.5011</v>
+        <v>0.7801</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0022501190</t>
+          <t>0022501192</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C72" t="n">
-        <v>1610612752</v>
+        <v>1610612761</v>
       </c>
       <c r="D72" t="n">
-        <v>1610612766</v>
+        <v>1610612751</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4389,52 +4389,52 @@
         <v>173</v>
       </c>
       <c r="M72" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.8378</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0022501191</t>
+          <t>0022501193</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C73" t="n">
-        <v>1610612755</v>
+        <v>1610612742</v>
       </c>
       <c r="D73" t="n">
-        <v>1610612749</v>
+        <v>1610612741</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -4444,52 +4444,52 @@
         <v>173</v>
       </c>
       <c r="M73" t="n">
-        <v>0.7801</v>
+        <v>0.5291</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0022501192</t>
+          <t>0022501194</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C74" t="n">
-        <v>1610612761</v>
+        <v>1610612745</v>
       </c>
       <c r="D74" t="n">
-        <v>1610612751</v>
+        <v>1610612763</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -4499,52 +4499,52 @@
         <v>173</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8378</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022501193</t>
+          <t>0022501195</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C75" t="n">
-        <v>1610612742</v>
+        <v>1610612750</v>
       </c>
       <c r="D75" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4554,52 +4554,52 @@
         <v>173</v>
       </c>
       <c r="M75" t="n">
-        <v>0.5291</v>
+        <v>0.7988</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0022501194</t>
+          <t>0022501196</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C76" t="n">
-        <v>1610612745</v>
+        <v>1610612760</v>
       </c>
       <c r="D76" t="n">
-        <v>1610612763</v>
+        <v>1610612756</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4609,52 +4609,52 @@
         <v>173</v>
       </c>
       <c r="M76" t="n">
-        <v>0.8663</v>
+        <v>0.8250999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0022501195</t>
+          <t>0022501197</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C77" t="n">
-        <v>1610612750</v>
+        <v>1610612759</v>
       </c>
       <c r="D77" t="n">
-        <v>1610612740</v>
+        <v>1610612743</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4664,52 +4664,52 @@
         <v>173</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7988</v>
+        <v>0.6569</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0022501196</t>
+          <t>0022501198</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C78" t="n">
-        <v>1610612760</v>
+        <v>1610612747</v>
       </c>
       <c r="D78" t="n">
-        <v>1610612756</v>
+        <v>1610612762</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4719,52 +4719,52 @@
         <v>173</v>
       </c>
       <c r="M78" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8748</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0022501197</t>
+          <t>0022501199</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C79" t="n">
-        <v>1610612759</v>
+        <v>1610612746</v>
       </c>
       <c r="D79" t="n">
-        <v>1610612743</v>
+        <v>1610612744</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -4774,52 +4774,52 @@
         <v>173</v>
       </c>
       <c r="M79" t="n">
-        <v>0.6569</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0022501198</t>
+          <t>0022501200</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="C80" t="n">
-        <v>1610612747</v>
+        <v>1610612757</v>
       </c>
       <c r="D80" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Moda Center</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4829,117 +4829,7 @@
         <v>173</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8748</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>0022501199</t>
-        </is>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C81" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Warriors</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>LAC</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Intuit Dome</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Inglewood</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>173</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0.7128</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>0022501200</t>
-        </is>
-      </c>
-      <c r="B82" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C82" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>SAC</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Moda Center</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Portland</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" t="n">
-        <v>173</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0.7923</v>
+        <v>0.792</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -539,7 +539,7 @@
         <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2408</v>
+        <v>0.2358</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8217</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="4">
@@ -704,7 +704,7 @@
         <v>164</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3404</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="6">
@@ -869,7 +869,7 @@
         <v>164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4394</v>
+        <v>0.4372</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
         <v>165</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8239</v>
+        <v>0.8307</v>
       </c>
     </row>
     <row r="10">
@@ -1034,7 +1034,7 @@
         <v>165</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4629</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="12">
@@ -1089,7 +1089,7 @@
         <v>166</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7668</v>
+        <v>0.7714</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         <v>166</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8366</v>
+        <v>0.8442</v>
       </c>
     </row>
     <row r="17">
@@ -1364,7 +1364,7 @@
         <v>166</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6048</v>
+        <v>0.6025</v>
       </c>
     </row>
     <row r="18">
@@ -1529,7 +1529,7 @@
         <v>166</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2566</v>
+        <v>0.3145</v>
       </c>
     </row>
     <row r="21">
@@ -1584,7 +1584,7 @@
         <v>166</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2725</v>
+        <v>0.2697</v>
       </c>
     </row>
     <row r="22">
@@ -1859,7 +1859,7 @@
         <v>167</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7985</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="27">
@@ -1914,7 +1914,7 @@
         <v>167</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7914</v>
+        <v>0.7861</v>
       </c>
     </row>
     <row r="28">
@@ -1969,7 +1969,7 @@
         <v>168</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3652</v>
+        <v>0.3582</v>
       </c>
     </row>
     <row r="29">
@@ -2134,7 +2134,7 @@
         <v>168</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6151</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="32">
@@ -2189,7 +2189,7 @@
         <v>168</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3033</v>
+        <v>0.2992</v>
       </c>
     </row>
     <row r="33">
@@ -2244,7 +2244,7 @@
         <v>168</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7009</v>
+        <v>0.7053</v>
       </c>
     </row>
     <row r="34">
@@ -2299,7 +2299,7 @@
         <v>168</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7771</v>
+        <v>0.7788</v>
       </c>
     </row>
     <row r="35">
@@ -2354,7 +2354,7 @@
         <v>168</v>
       </c>
       <c r="M35" t="n">
-        <v>0.483</v>
+        <v>0.3596</v>
       </c>
     </row>
     <row r="36">
@@ -2409,7 +2409,7 @@
         <v>168</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2519,7 +2519,7 @@
         <v>169</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7281</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="39">
@@ -2574,7 +2574,7 @@
         <v>169</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4514</v>
+        <v>0.4457</v>
       </c>
     </row>
     <row r="40">
@@ -2629,7 +2629,7 @@
         <v>169</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8626</v>
+        <v>0.8663999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2684,7 +2684,7 @@
         <v>169</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8066</v>
       </c>
     </row>
     <row r="42">
@@ -2904,7 +2904,7 @@
         <v>170</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6151</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="46">
@@ -2959,7 +2959,7 @@
         <v>170</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3652</v>
+        <v>0.3582</v>
       </c>
     </row>
     <row r="47">
@@ -3014,7 +3014,7 @@
         <v>170</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4698</v>
+        <v>0.4685</v>
       </c>
     </row>
     <row r="48">
@@ -3179,7 +3179,7 @@
         <v>170</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4078</v>
+        <v>0.4746</v>
       </c>
     </row>
     <row r="51">
@@ -3234,7 +3234,7 @@
         <v>171</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5456</v>
+        <v>0.5466</v>
       </c>
     </row>
     <row r="52">
@@ -3344,7 +3344,7 @@
         <v>171</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4766</v>
+        <v>0.4719</v>
       </c>
     </row>
     <row r="54">
@@ -3399,7 +3399,7 @@
         <v>171</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8076</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -3454,7 +3454,7 @@
         <v>171</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3776</v>
+        <v>0.3786</v>
       </c>
     </row>
     <row r="56">
@@ -3729,7 +3729,7 @@
         <v>171</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8675</v>
+        <v>0.8698</v>
       </c>
     </row>
     <row r="61">
@@ -3894,7 +3894,7 @@
         <v>171</v>
       </c>
       <c r="M63" t="n">
-        <v>0.4885</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="64">
@@ -3949,7 +3949,7 @@
         <v>171</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3708</v>
+        <v>0.3662</v>
       </c>
     </row>
     <row r="65">
@@ -4004,7 +4004,7 @@
         <v>171</v>
       </c>
       <c r="M65" t="n">
-        <v>0.6776</v>
+        <v>0.5568</v>
       </c>
     </row>
     <row r="66">
@@ -4059,7 +4059,7 @@
         <v>173</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8302</v>
+        <v>0.8347</v>
       </c>
     </row>
     <row r="67">
@@ -4169,7 +4169,7 @@
         <v>173</v>
       </c>
       <c r="M68" t="n">
-        <v>0.309</v>
+        <v>0.3004</v>
       </c>
     </row>
     <row r="69">
@@ -4279,7 +4279,7 @@
         <v>173</v>
       </c>
       <c r="M70" t="n">
-        <v>0.6089</v>
+        <v>0.6098</v>
       </c>
     </row>
     <row r="71">
@@ -4334,7 +4334,7 @@
         <v>173</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7801</v>
+        <v>0.7862</v>
       </c>
     </row>
     <row r="72">
@@ -4499,7 +4499,7 @@
         <v>173</v>
       </c>
       <c r="M74" t="n">
-        <v>0.864</v>
+        <v>0.8663</v>
       </c>
     </row>
     <row r="75">
@@ -4719,7 +4719,7 @@
         <v>173</v>
       </c>
       <c r="M78" t="n">
-        <v>0.8748</v>
+        <v>0.8444</v>
       </c>
     </row>
     <row r="79">
@@ -4829,7 +4829,7 @@
         <v>173</v>
       </c>
       <c r="M80" t="n">
-        <v>0.792</v>
+        <v>0.8033</v>
       </c>
     </row>
   </sheetData>

--- a/nba/public/data/nba_schedule_remaining.xlsx
+++ b/nba/public/data/nba_schedule_remaining.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,46 +490,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0022501122</t>
+          <t>0022501127</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C2" t="n">
-        <v>1610612751</v>
+        <v>1610612742</v>
       </c>
       <c r="D2" t="n">
-        <v>1610612737</v>
+        <v>1610612753</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -539,52 +539,52 @@
         <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2358</v>
+        <v>0.4283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0022501123</t>
+          <t>0022501128</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="C3" t="n">
-        <v>1610612752</v>
+        <v>1610612758</v>
       </c>
       <c r="D3" t="n">
-        <v>1610612741</v>
+        <v>1610612740</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -594,492 +594,492 @@
         <v>164</v>
       </c>
       <c r="M3" t="n">
-        <v>0.825</v>
+        <v>0.4372</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022501124</t>
+          <t>0022501129</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C4" t="n">
-        <v>1610612745</v>
+        <v>1610612748</v>
       </c>
       <c r="D4" t="n">
-        <v>1610612762</v>
+        <v>1610612764</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>Kaseya Center</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Miami</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8608</v>
+        <v>0.8215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0022501125</t>
+          <t>0022501130</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C5" t="n">
-        <v>1610612763</v>
+        <v>1610612743</v>
       </c>
       <c r="D5" t="n">
-        <v>1610612761</v>
+        <v>1610612759</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3338</v>
+        <v>0.5317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0022501126</t>
+          <t>0022501131</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C6" t="n">
-        <v>1610612749</v>
+        <v>1610612755</v>
       </c>
       <c r="D6" t="n">
-        <v>1610612738</v>
+        <v>1610612765</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>Xfinity Mobile Arena</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2187</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0022501127</t>
+          <t>0022501132</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C7" t="n">
-        <v>1610612742</v>
+        <v>1610612738</v>
       </c>
       <c r="D7" t="n">
-        <v>1610612753</v>
+        <v>1610612761</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4283</v>
+        <v>0.7832</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0022501128</t>
+          <t>0022501133</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="C8" t="n">
-        <v>1610612758</v>
+        <v>1610612751</v>
       </c>
       <c r="D8" t="n">
-        <v>1610612740</v>
+        <v>1610612764</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4372</v>
+        <v>0.6232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0022501129</t>
+          <t>0022501134</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C9" t="n">
-        <v>1610612748</v>
+        <v>1610612741</v>
       </c>
       <c r="D9" t="n">
-        <v>1610612764</v>
+        <v>1610612756</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Kaseya Center</t>
+          <t>United Center</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8307</v>
+        <v>0.4131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0022501130</t>
+          <t>0022501135</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C10" t="n">
-        <v>1610612743</v>
+        <v>1610612749</v>
       </c>
       <c r="D10" t="n">
-        <v>1610612759</v>
+        <v>1610612763</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Fiserv Forum</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5317</v>
+        <v>0.5909</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0022501131</t>
+          <t>0022501136</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="C11" t="n">
-        <v>1610612755</v>
+        <v>1610612739</v>
       </c>
       <c r="D11" t="n">
-        <v>1610612765</v>
+        <v>1610612754</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Xfinity Mobile Arena</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4674</v>
+        <v>0.8407</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0022501132</t>
+          <t>0022501137</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C12" t="n">
-        <v>1610612738</v>
+        <v>1610612750</v>
       </c>
       <c r="D12" t="n">
-        <v>1610612761</v>
+        <v>1610612766</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Target Center</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1089,52 +1089,52 @@
         <v>166</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7714</v>
+        <v>0.6034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0022501133</t>
+          <t>0022501138</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C13" t="n">
-        <v>1610612751</v>
+        <v>1610612740</v>
       </c>
       <c r="D13" t="n">
-        <v>1610612764</v>
+        <v>1610612753</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1144,52 +1144,52 @@
         <v>166</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6531</v>
+        <v>0.4877</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0022501134</t>
+          <t>0022501139</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C14" t="n">
-        <v>1610612741</v>
+        <v>1610612760</v>
       </c>
       <c r="D14" t="n">
-        <v>1610612756</v>
+        <v>1610612762</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>United Center</t>
+          <t>Paycom Center</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Oklahoma City</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1199,52 +1199,52 @@
         <v>166</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4165</v>
+        <v>0.8719</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0022501135</t>
+          <t>0022501140</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C15" t="n">
-        <v>1610612749</v>
+        <v>1610612742</v>
       </c>
       <c r="D15" t="n">
-        <v>1610612763</v>
+        <v>1610612747</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fiserv Forum</t>
+          <t>American Airlines Center</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1254,52 +1254,52 @@
         <v>166</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5717</v>
+        <v>0.3147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0022501136</t>
+          <t>0022501141</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C16" t="n">
-        <v>1610612739</v>
+        <v>1610612758</v>
       </c>
       <c r="D16" t="n">
-        <v>1610612754</v>
+        <v>1610612746</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Golden 1 Center</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1309,52 +1309,52 @@
         <v>166</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8442</v>
+        <v>0.2697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022501137</t>
+          <t>0022501142</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>46117</v>
       </c>
       <c r="C17" t="n">
-        <v>1610612750</v>
+        <v>1610612744</v>
       </c>
       <c r="D17" t="n">
-        <v>1610612766</v>
+        <v>1610612745</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Target Center</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1364,602 +1364,602 @@
         <v>166</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6025</v>
+        <v>0.4628</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0022501138</t>
+          <t>0022501143</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C18" t="n">
-        <v>1610612740</v>
+        <v>1610612737</v>
       </c>
       <c r="D18" t="n">
-        <v>1610612753</v>
+        <v>1610612752</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4877</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0022501139</t>
+          <t>0022501144</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C19" t="n">
-        <v>1610612760</v>
+        <v>1610612753</v>
       </c>
       <c r="D19" t="n">
-        <v>1610612762</v>
+        <v>1610612765</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Paycom Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Oklahoma City</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8781</v>
+        <v>0.3824</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0022501140</t>
+          <t>0022501145</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C20" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="D20" t="n">
-        <v>1610612747</v>
+        <v>1610612739</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>American Airlines Center</t>
+          <t>FedExForum</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3145</v>
+        <v>0.2587</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0022501141</t>
+          <t>0022501146</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C21" t="n">
-        <v>1610612758</v>
+        <v>1610612759</v>
       </c>
       <c r="D21" t="n">
-        <v>1610612746</v>
+        <v>1610612755</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Golden 1 Center</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2697</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022501142</t>
+          <t>0022501147</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C22" t="n">
-        <v>1610612744</v>
+        <v>1610612743</v>
       </c>
       <c r="D22" t="n">
-        <v>1610612745</v>
+        <v>1610612757</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4125</v>
+        <v>0.7766999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022501143</t>
+          <t>0022501148</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C23" t="n">
-        <v>1610612737</v>
+        <v>1610612764</v>
       </c>
       <c r="D23" t="n">
-        <v>1610612752</v>
+        <v>1610612741</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>State Farm Arena</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5056</v>
+        <v>0.4152</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022501144</t>
+          <t>0022501149</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C24" t="n">
-        <v>1610612753</v>
+        <v>1610612738</v>
       </c>
       <c r="D24" t="n">
-        <v>1610612765</v>
+        <v>1610612766</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3793</v>
+        <v>0.7010999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0022501145</t>
+          <t>0022501150</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C25" t="n">
-        <v>1610612763</v>
+        <v>1610612751</v>
       </c>
       <c r="D25" t="n">
-        <v>1610612739</v>
+        <v>1610612749</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FedExForum</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2399</v>
+        <v>0.4215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0022501146</t>
+          <t>0022501151</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C26" t="n">
-        <v>1610612759</v>
+        <v>1610612761</v>
       </c>
       <c r="D26" t="n">
-        <v>1610612755</v>
+        <v>1610612748</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7998</v>
+        <v>0.6449</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0022501147</t>
+          <t>0022501152</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="C27" t="n">
-        <v>1610612743</v>
+        <v>1610612754</v>
       </c>
       <c r="D27" t="n">
-        <v>1610612757</v>
+        <v>1610612750</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7861</v>
+        <v>0.3033</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0022501148</t>
+          <t>0022501153</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C28" t="n">
-        <v>1610612764</v>
+        <v>1610612740</v>
       </c>
       <c r="D28" t="n">
-        <v>1610612741</v>
+        <v>1610612762</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Smoothie King Center</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1969,52 +1969,52 @@
         <v>168</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3582</v>
+        <v>0.6973</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0022501149</t>
+          <t>0022501154</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C29" t="n">
-        <v>1610612738</v>
+        <v>1610612744</v>
       </c>
       <c r="D29" t="n">
-        <v>1610612766</v>
+        <v>1610612758</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TD Garden</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2024,52 +2024,52 @@
         <v>168</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6915</v>
+        <v>0.8037</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022501150</t>
+          <t>0022501155</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C30" t="n">
-        <v>1610612751</v>
+        <v>1610612747</v>
       </c>
       <c r="D30" t="n">
-        <v>1610612749</v>
+        <v>1610612760</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Crypto.com Arena</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2079,52 +2079,52 @@
         <v>168</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4767</v>
+        <v>0.3535</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0022501151</t>
+          <t>0022501156</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C31" t="n">
-        <v>1610612761</v>
+        <v>1610612746</v>
       </c>
       <c r="D31" t="n">
-        <v>1610612748</v>
+        <v>1610612742</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2134,52 +2134,52 @@
         <v>168</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6162</v>
+        <v>0.8279</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0022501152</t>
+          <t>0022501157</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="C32" t="n">
-        <v>1610612754</v>
+        <v>1610612756</v>
       </c>
       <c r="D32" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Gainbridge Fieldhouse</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2189,327 +2189,327 @@
         <v>168</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2992</v>
+        <v>0.4608</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022501153</t>
+          <t>0022501158</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C33" t="n">
-        <v>1610612740</v>
+        <v>1610612739</v>
       </c>
       <c r="D33" t="n">
-        <v>1610612762</v>
+        <v>1610612737</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Smoothie King Center</t>
+          <t>Rocket Arena</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7053</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0022501154</t>
+          <t>0022501159</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C34" t="n">
-        <v>1610612744</v>
+        <v>1610612753</v>
       </c>
       <c r="D34" t="n">
-        <v>1610612758</v>
+        <v>1610612750</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Kia Center</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7788</v>
+        <v>0.4472</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0022501155</t>
+          <t>0022501160</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C35" t="n">
-        <v>1610612747</v>
+        <v>1610612765</v>
       </c>
       <c r="D35" t="n">
-        <v>1610612760</v>
+        <v>1610612749</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Crypto.com Arena</t>
+          <t>Little Caesars Arena</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3596</v>
+        <v>0.8084</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0022501156</t>
+          <t>0022501161</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C36" t="n">
-        <v>1610612746</v>
+        <v>1610612759</v>
       </c>
       <c r="D36" t="n">
-        <v>1610612742</v>
+        <v>1610612757</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Frost Bank Center</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8038</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022501157</t>
+          <t>0022501162</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C37" t="n">
-        <v>1610612756</v>
+        <v>1610612743</v>
       </c>
       <c r="D37" t="n">
-        <v>1610612745</v>
+        <v>1610612763</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Ball Arena</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4713</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0022501158</t>
+          <t>0022501163</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C38" t="n">
-        <v>1610612739</v>
+        <v>1610612746</v>
       </c>
       <c r="D38" t="n">
-        <v>1610612737</v>
+        <v>1610612760</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Rocket Arena</t>
+          <t>Intuit Dome</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Inglewood</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2519,52 +2519,52 @@
         <v>169</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7315</v>
+        <v>0.3838</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0022501159</t>
+          <t>0022501164</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="C39" t="n">
-        <v>1610612753</v>
+        <v>1610612756</v>
       </c>
       <c r="D39" t="n">
-        <v>1610612750</v>
+        <v>1610612742</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kia Center</t>
+          <t>Mortgage Matchup Center</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2574,327 +2574,327 @@
         <v>169</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4457</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0022501160</t>
+          <t>0022501165</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C40" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="D40" t="n">
-        <v>1610612749</v>
+        <v>1610612748</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Little Caesars Arena</t>
+          <t>Scotiabank Arena</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.6449</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0022501161</t>
+          <t>0022501166</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C41" t="n">
-        <v>1610612759</v>
+        <v>1610612764</v>
       </c>
       <c r="D41" t="n">
-        <v>1610612757</v>
+        <v>1610612741</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Frost Bank Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8066</v>
+        <v>0.4152</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0022501162</t>
+          <t>0022501167</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C42" t="n">
-        <v>1610612743</v>
+        <v>1610612751</v>
       </c>
       <c r="D42" t="n">
-        <v>1610612763</v>
+        <v>1610612754</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Ball Arena</t>
+          <t>Barclays Center</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8696</v>
+        <v>0.4558</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0022501163</t>
+          <t>0022501168</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C43" t="n">
-        <v>1610612746</v>
+        <v>1610612752</v>
       </c>
       <c r="D43" t="n">
-        <v>1610612760</v>
+        <v>1610612738</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Intuit Dome</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Inglewood</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3838</v>
+        <v>0.4961</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0022501164</t>
+          <t>0022501169</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="C44" t="n">
-        <v>1610612756</v>
+        <v>1610612745</v>
       </c>
       <c r="D44" t="n">
-        <v>1610612742</v>
+        <v>1610612755</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mortgage Matchup Center</t>
+          <t>Toyota Center</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8061</v>
+        <v>0.6545</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0022501165</t>
+          <t>0022501170</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="C45" t="n">
-        <v>1610612761</v>
+        <v>1610612744</v>
       </c>
       <c r="D45" t="n">
-        <v>1610612748</v>
+        <v>1610612747</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>Chase Center</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2904,327 +2904,327 @@
         <v>170</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6162</v>
+        <v>0.5489000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0022501166</t>
+          <t>0022501171</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C46" t="n">
-        <v>1610612764</v>
+        <v>1610612766</v>
       </c>
       <c r="D46" t="n">
-        <v>1610612741</v>
+        <v>1610612765</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Capital One Arena</t>
+          <t>Spectrum Center</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3582</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0022501167</t>
+          <t>0022501172</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C47" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="D47" t="n">
-        <v>1610612754</v>
+        <v>1610612748</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>Capital One Arena</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4685</v>
+        <v>0.2919</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022501168</t>
+          <t>0022501173</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C48" t="n">
-        <v>1610612752</v>
+        <v>1610612737</v>
       </c>
       <c r="D48" t="n">
-        <v>1610612738</v>
+        <v>1610612739</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Madison Square Garden</t>
+          <t>State Farm Arena</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4961</v>
+        <v>0.4719</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0022501169</t>
+          <t>0022501174</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C49" t="n">
-        <v>1610612745</v>
+        <v>1610612738</v>
       </c>
       <c r="D49" t="n">
-        <v>1610612755</v>
+        <v>1610612740</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Toyota Center</t>
+          <t>TD Garden</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M49" t="n">
-        <v>0.6545</v>
+        <v>0.8188</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0022501170</t>
+          <t>0022501175</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C50" t="n">
-        <v>1610612744</v>
+        <v>1610612754</v>
       </c>
       <c r="D50" t="n">
-        <v>1610612747</v>
+        <v>1610612755</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>Gainbridge Fieldhouse</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4746</v>
+        <v>0.3835</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022501171</t>
+          <t>0022501176</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C51" t="n">
-        <v>1610612766</v>
+        <v>1610612752</v>
       </c>
       <c r="D51" t="n">
-        <v>1610612765</v>
+        <v>1610612761</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Spectrum Center</t>
+          <t>Madison Square Garden</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3234,52 +3234,52 @@
         <v>171</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5466</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0022501172</t>
+          <t>0022501177</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="C52" t="n">
-        <v>1610612764</v>
+        <v>1610612741</v>
       </c>
       <c r="D52" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wizards</t>
+